--- a/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI317"/>
+  <dimension ref="A1:AI329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38207,6 +38207,1434 @@
       </c>
       <c r="AI317" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B318" t="n">
+        <v>24</v>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E318" t="n">
+        <v>200</v>
+      </c>
+      <c r="F318" t="n">
+        <v>70</v>
+      </c>
+      <c r="G318" t="n">
+        <v>23</v>
+      </c>
+      <c r="H318" t="n">
+        <v>53</v>
+      </c>
+      <c r="I318" t="n">
+        <v>3</v>
+      </c>
+      <c r="J318" t="n">
+        <v>16</v>
+      </c>
+      <c r="K318" t="n">
+        <v>15</v>
+      </c>
+      <c r="L318" t="n">
+        <v>25</v>
+      </c>
+      <c r="M318" t="n">
+        <v>11</v>
+      </c>
+      <c r="N318" t="n">
+        <v>25</v>
+      </c>
+      <c r="O318" t="n">
+        <v>15</v>
+      </c>
+      <c r="P318" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>12</v>
+      </c>
+      <c r="R318" t="n">
+        <v>20</v>
+      </c>
+      <c r="S318" t="n">
+        <v>18</v>
+      </c>
+      <c r="T318" t="n">
+        <v>3</v>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V318" t="n">
+        <v>95</v>
+      </c>
+      <c r="W318" t="n">
+        <v>92</v>
+      </c>
+      <c r="X318" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="Y318" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z318" t="n">
+        <v>86.41975308641975</v>
+      </c>
+      <c r="AA318" t="n">
+        <v>1.026361279170268</v>
+      </c>
+      <c r="AB318" t="n">
+        <v>113.6907611297271</v>
+      </c>
+      <c r="AC318" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD318" t="n">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="AE318" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="AF318" t="n">
+        <v>-27.27100804330739</v>
+      </c>
+      <c r="AG318" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI318" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B319" t="n">
+        <v>24</v>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="E319" t="n">
+        <v>200</v>
+      </c>
+      <c r="F319" t="n">
+        <v>64</v>
+      </c>
+      <c r="G319" t="n">
+        <v>21</v>
+      </c>
+      <c r="H319" t="n">
+        <v>41</v>
+      </c>
+      <c r="I319" t="n">
+        <v>4</v>
+      </c>
+      <c r="J319" t="n">
+        <v>29</v>
+      </c>
+      <c r="K319" t="n">
+        <v>10</v>
+      </c>
+      <c r="L319" t="n">
+        <v>13</v>
+      </c>
+      <c r="M319" t="n">
+        <v>15</v>
+      </c>
+      <c r="N319" t="n">
+        <v>18</v>
+      </c>
+      <c r="O319" t="n">
+        <v>14</v>
+      </c>
+      <c r="P319" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>14</v>
+      </c>
+      <c r="R319" t="n">
+        <v>20</v>
+      </c>
+      <c r="S319" t="n">
+        <v>19</v>
+      </c>
+      <c r="T319" t="n">
+        <v>3</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>2487742</t>
+        </is>
+      </c>
+      <c r="V319" t="n">
+        <v>77</v>
+      </c>
+      <c r="W319" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="X319" t="n">
+        <v>0.7133303611234953</v>
+      </c>
+      <c r="Y319" t="n">
+        <v>74.72</v>
+      </c>
+      <c r="Z319" t="n">
+        <v>85.65310492505354</v>
+      </c>
+      <c r="AA319" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="AB319" t="n">
+        <v>107.2423398328691</v>
+      </c>
+      <c r="AC319" t="n">
+        <v>0.3658536585365854</v>
+      </c>
+      <c r="AD319" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AE319" t="n">
+        <v>0.4520547945205479</v>
+      </c>
+      <c r="AF319" t="n">
+        <v>-21.58923490781554</v>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI319" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B320" t="n">
+        <v>24</v>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="E320" t="n">
+        <v>200</v>
+      </c>
+      <c r="F320" t="n">
+        <v>75</v>
+      </c>
+      <c r="G320" t="n">
+        <v>20</v>
+      </c>
+      <c r="H320" t="n">
+        <v>43</v>
+      </c>
+      <c r="I320" t="n">
+        <v>9</v>
+      </c>
+      <c r="J320" t="n">
+        <v>26</v>
+      </c>
+      <c r="K320" t="n">
+        <v>8</v>
+      </c>
+      <c r="L320" t="n">
+        <v>16</v>
+      </c>
+      <c r="M320" t="n">
+        <v>4</v>
+      </c>
+      <c r="N320" t="n">
+        <v>27</v>
+      </c>
+      <c r="O320" t="n">
+        <v>20</v>
+      </c>
+      <c r="P320" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>9</v>
+      </c>
+      <c r="R320" t="n">
+        <v>16</v>
+      </c>
+      <c r="S320" t="n">
+        <v>14</v>
+      </c>
+      <c r="T320" t="n">
+        <v>4</v>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="V320" t="n">
+        <v>83</v>
+      </c>
+      <c r="W320" t="n">
+        <v>85.03999999999999</v>
+      </c>
+      <c r="X320" t="n">
+        <v>0.8819379115710255</v>
+      </c>
+      <c r="Y320" t="n">
+        <v>81.03999999999999</v>
+      </c>
+      <c r="Z320" t="n">
+        <v>92.54689042448175</v>
+      </c>
+      <c r="AA320" t="n">
+        <v>0.8535582064993829</v>
+      </c>
+      <c r="AB320" t="n">
+        <v>96.24304267161409</v>
+      </c>
+      <c r="AC320" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AD320" t="n">
+        <v>0.7105263157894737</v>
+      </c>
+      <c r="AE320" t="n">
+        <v>0.3974358974358974</v>
+      </c>
+      <c r="AF320" t="n">
+        <v>-3.696152247132346</v>
+      </c>
+      <c r="AG320" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AH320" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AI320" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B321" t="n">
+        <v>24</v>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E321" t="n">
+        <v>200</v>
+      </c>
+      <c r="F321" t="n">
+        <v>68</v>
+      </c>
+      <c r="G321" t="n">
+        <v>13</v>
+      </c>
+      <c r="H321" t="n">
+        <v>34</v>
+      </c>
+      <c r="I321" t="n">
+        <v>9</v>
+      </c>
+      <c r="J321" t="n">
+        <v>30</v>
+      </c>
+      <c r="K321" t="n">
+        <v>15</v>
+      </c>
+      <c r="L321" t="n">
+        <v>31</v>
+      </c>
+      <c r="M321" t="n">
+        <v>19</v>
+      </c>
+      <c r="N321" t="n">
+        <v>23</v>
+      </c>
+      <c r="O321" t="n">
+        <v>10</v>
+      </c>
+      <c r="P321" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>16</v>
+      </c>
+      <c r="R321" t="n">
+        <v>21</v>
+      </c>
+      <c r="S321" t="n">
+        <v>24</v>
+      </c>
+      <c r="T321" t="n">
+        <v>2</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>2487739</t>
+        </is>
+      </c>
+      <c r="V321" t="n">
+        <v>51</v>
+      </c>
+      <c r="W321" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="X321" t="n">
+        <v>0.7261853908586074</v>
+      </c>
+      <c r="Y321" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="Z321" t="n">
+        <v>91.10396570203645</v>
+      </c>
+      <c r="AA321" t="n">
+        <v>0.5619215513442045</v>
+      </c>
+      <c r="AB321" t="n">
+        <v>66.44085461177697</v>
+      </c>
+      <c r="AC321" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AD321" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE321" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF321" t="n">
+        <v>24.66311109025948</v>
+      </c>
+      <c r="AG321" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH321" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI321" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>24</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E322" t="n">
+        <v>200</v>
+      </c>
+      <c r="F322" t="n">
+        <v>87</v>
+      </c>
+      <c r="G322" t="n">
+        <v>29</v>
+      </c>
+      <c r="H322" t="n">
+        <v>45</v>
+      </c>
+      <c r="I322" t="n">
+        <v>8</v>
+      </c>
+      <c r="J322" t="n">
+        <v>25</v>
+      </c>
+      <c r="K322" t="n">
+        <v>5</v>
+      </c>
+      <c r="L322" t="n">
+        <v>12</v>
+      </c>
+      <c r="M322" t="n">
+        <v>9</v>
+      </c>
+      <c r="N322" t="n">
+        <v>22</v>
+      </c>
+      <c r="O322" t="n">
+        <v>19</v>
+      </c>
+      <c r="P322" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>19</v>
+      </c>
+      <c r="R322" t="n">
+        <v>15</v>
+      </c>
+      <c r="S322" t="n">
+        <v>15</v>
+      </c>
+      <c r="T322" t="n">
+        <v>1</v>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V322" t="n">
+        <v>70</v>
+      </c>
+      <c r="W322" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="X322" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="Y322" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="Z322" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AA322" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="AB322" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AC322" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD322" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="AE322" t="n">
+        <v>0.4626865671641791</v>
+      </c>
+      <c r="AF322" t="n">
+        <v>18.40484541969165</v>
+      </c>
+      <c r="AG322" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH322" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI322" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>24</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E323" t="n">
+        <v>200</v>
+      </c>
+      <c r="F323" t="n">
+        <v>51</v>
+      </c>
+      <c r="G323" t="n">
+        <v>12</v>
+      </c>
+      <c r="H323" t="n">
+        <v>35</v>
+      </c>
+      <c r="I323" t="n">
+        <v>2</v>
+      </c>
+      <c r="J323" t="n">
+        <v>24</v>
+      </c>
+      <c r="K323" t="n">
+        <v>21</v>
+      </c>
+      <c r="L323" t="n">
+        <v>29</v>
+      </c>
+      <c r="M323" t="n">
+        <v>14</v>
+      </c>
+      <c r="N323" t="n">
+        <v>21</v>
+      </c>
+      <c r="O323" t="n">
+        <v>7</v>
+      </c>
+      <c r="P323" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>19</v>
+      </c>
+      <c r="R323" t="n">
+        <v>25</v>
+      </c>
+      <c r="S323" t="n">
+        <v>20</v>
+      </c>
+      <c r="T323" t="n">
+        <v>3</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>2487739</t>
+        </is>
+      </c>
+      <c r="V323" t="n">
+        <v>68</v>
+      </c>
+      <c r="W323" t="n">
+        <v>90.75999999999999</v>
+      </c>
+      <c r="X323" t="n">
+        <v>0.5619215513442045</v>
+      </c>
+      <c r="Y323" t="n">
+        <v>76.75999999999999</v>
+      </c>
+      <c r="Z323" t="n">
+        <v>66.44085461177697</v>
+      </c>
+      <c r="AA323" t="n">
+        <v>0.7261853908586074</v>
+      </c>
+      <c r="AB323" t="n">
+        <v>91.10396570203645</v>
+      </c>
+      <c r="AC323" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD323" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AE323" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF323" t="n">
+        <v>-24.66311109025948</v>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI323" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>24</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>200</v>
+      </c>
+      <c r="F324" t="n">
+        <v>95</v>
+      </c>
+      <c r="G324" t="n">
+        <v>27</v>
+      </c>
+      <c r="H324" t="n">
+        <v>51</v>
+      </c>
+      <c r="I324" t="n">
+        <v>8</v>
+      </c>
+      <c r="J324" t="n">
+        <v>20</v>
+      </c>
+      <c r="K324" t="n">
+        <v>17</v>
+      </c>
+      <c r="L324" t="n">
+        <v>24</v>
+      </c>
+      <c r="M324" t="n">
+        <v>9</v>
+      </c>
+      <c r="N324" t="n">
+        <v>33</v>
+      </c>
+      <c r="O324" t="n">
+        <v>23</v>
+      </c>
+      <c r="P324" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>11</v>
+      </c>
+      <c r="R324" t="n">
+        <v>18</v>
+      </c>
+      <c r="S324" t="n">
+        <v>20</v>
+      </c>
+      <c r="T324" t="n">
+        <v>2</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>70</v>
+      </c>
+      <c r="W324" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="X324" t="n">
+        <v>1.026361279170268</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>113.6907611297271</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>86.41975308641975</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>27.27100804330739</v>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI324" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>24</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>200</v>
+      </c>
+      <c r="F325" t="n">
+        <v>70</v>
+      </c>
+      <c r="G325" t="n">
+        <v>25</v>
+      </c>
+      <c r="H325" t="n">
+        <v>41</v>
+      </c>
+      <c r="I325" t="n">
+        <v>4</v>
+      </c>
+      <c r="J325" t="n">
+        <v>27</v>
+      </c>
+      <c r="K325" t="n">
+        <v>8</v>
+      </c>
+      <c r="L325" t="n">
+        <v>13</v>
+      </c>
+      <c r="M325" t="n">
+        <v>12</v>
+      </c>
+      <c r="N325" t="n">
+        <v>24</v>
+      </c>
+      <c r="O325" t="n">
+        <v>13</v>
+      </c>
+      <c r="P325" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>22</v>
+      </c>
+      <c r="R325" t="n">
+        <v>15</v>
+      </c>
+      <c r="S325" t="n">
+        <v>15</v>
+      </c>
+      <c r="T325" t="n">
+        <v>2</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>87</v>
+      </c>
+      <c r="W325" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="X325" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>-18.40484541969165</v>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI325" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>24</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>200</v>
+      </c>
+      <c r="F326" t="n">
+        <v>53</v>
+      </c>
+      <c r="G326" t="n">
+        <v>12</v>
+      </c>
+      <c r="H326" t="n">
+        <v>29</v>
+      </c>
+      <c r="I326" t="n">
+        <v>6</v>
+      </c>
+      <c r="J326" t="n">
+        <v>21</v>
+      </c>
+      <c r="K326" t="n">
+        <v>11</v>
+      </c>
+      <c r="L326" t="n">
+        <v>15</v>
+      </c>
+      <c r="M326" t="n">
+        <v>4</v>
+      </c>
+      <c r="N326" t="n">
+        <v>27</v>
+      </c>
+      <c r="O326" t="n">
+        <v>13</v>
+      </c>
+      <c r="P326" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>27</v>
+      </c>
+      <c r="R326" t="n">
+        <v>21</v>
+      </c>
+      <c r="S326" t="n">
+        <v>20</v>
+      </c>
+      <c r="T326" t="n">
+        <v>1</v>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
+        <v>81</v>
+      </c>
+      <c r="W326" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X326" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>0.4696969696969697</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>-35.07371193315976</v>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI326" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>24</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>200</v>
+      </c>
+      <c r="F327" t="n">
+        <v>77</v>
+      </c>
+      <c r="G327" t="n">
+        <v>24</v>
+      </c>
+      <c r="H327" t="n">
+        <v>43</v>
+      </c>
+      <c r="I327" t="n">
+        <v>6</v>
+      </c>
+      <c r="J327" t="n">
+        <v>19</v>
+      </c>
+      <c r="K327" t="n">
+        <v>11</v>
+      </c>
+      <c r="L327" t="n">
+        <v>20</v>
+      </c>
+      <c r="M327" t="n">
+        <v>14</v>
+      </c>
+      <c r="N327" t="n">
+        <v>26</v>
+      </c>
+      <c r="O327" t="n">
+        <v>13</v>
+      </c>
+      <c r="P327" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>15</v>
+      </c>
+      <c r="R327" t="n">
+        <v>20</v>
+      </c>
+      <c r="S327" t="n">
+        <v>20</v>
+      </c>
+      <c r="T327" t="n">
+        <v>3</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>2487742</t>
+        </is>
+      </c>
+      <c r="V327" t="n">
+        <v>64</v>
+      </c>
+      <c r="W327" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="X327" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>107.2423398328691</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>0.7133303611234953</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>85.65310492505354</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>21.58923490781554</v>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI327" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>24</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>200</v>
+      </c>
+      <c r="F328" t="n">
+        <v>81</v>
+      </c>
+      <c r="G328" t="n">
+        <v>19</v>
+      </c>
+      <c r="H328" t="n">
+        <v>39</v>
+      </c>
+      <c r="I328" t="n">
+        <v>9</v>
+      </c>
+      <c r="J328" t="n">
+        <v>23</v>
+      </c>
+      <c r="K328" t="n">
+        <v>16</v>
+      </c>
+      <c r="L328" t="n">
+        <v>22</v>
+      </c>
+      <c r="M328" t="n">
+        <v>8</v>
+      </c>
+      <c r="N328" t="n">
+        <v>27</v>
+      </c>
+      <c r="O328" t="n">
+        <v>24</v>
+      </c>
+      <c r="P328" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>16</v>
+      </c>
+      <c r="R328" t="n">
+        <v>20</v>
+      </c>
+      <c r="S328" t="n">
+        <v>21</v>
+      </c>
+      <c r="T328" t="n">
+        <v>0</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>53</v>
+      </c>
+      <c r="W328" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="X328" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>35.07371193315976</v>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>24</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>200</v>
+      </c>
+      <c r="F329" t="n">
+        <v>83</v>
+      </c>
+      <c r="G329" t="n">
+        <v>21</v>
+      </c>
+      <c r="H329" t="n">
+        <v>39</v>
+      </c>
+      <c r="I329" t="n">
+        <v>9</v>
+      </c>
+      <c r="J329" t="n">
+        <v>30</v>
+      </c>
+      <c r="K329" t="n">
+        <v>14</v>
+      </c>
+      <c r="L329" t="n">
+        <v>21</v>
+      </c>
+      <c r="M329" t="n">
+        <v>11</v>
+      </c>
+      <c r="N329" t="n">
+        <v>36</v>
+      </c>
+      <c r="O329" t="n">
+        <v>10</v>
+      </c>
+      <c r="P329" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>19</v>
+      </c>
+      <c r="R329" t="n">
+        <v>15</v>
+      </c>
+      <c r="S329" t="n">
+        <v>16</v>
+      </c>
+      <c r="T329" t="n">
+        <v>3</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487740</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>75</v>
+      </c>
+      <c r="W329" t="n">
+        <v>97.24000000000001</v>
+      </c>
+      <c r="X329" t="n">
+        <v>0.8535582064993829</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>86.24000000000001</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>96.24304267161409</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.8819379115710255</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>92.54689042448175</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.6025641025641025</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>3.696152247132346</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI329"/>
+  <dimension ref="A1:AI333"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37625,108 +37625,108 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E313" t="n">
         <v>200</v>
       </c>
       <c r="F313" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G313" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H313" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="I313" t="n">
+        <v>11</v>
+      </c>
+      <c r="J313" t="n">
+        <v>32</v>
+      </c>
+      <c r="K313" t="n">
+        <v>29</v>
+      </c>
+      <c r="L313" t="n">
+        <v>37</v>
+      </c>
+      <c r="M313" t="n">
+        <v>11</v>
+      </c>
+      <c r="N313" t="n">
+        <v>26</v>
+      </c>
+      <c r="O313" t="n">
+        <v>11</v>
+      </c>
+      <c r="P313" t="n">
         <v>6</v>
       </c>
-      <c r="J313" t="n">
-        <v>22</v>
-      </c>
-      <c r="K313" t="n">
-        <v>19</v>
-      </c>
-      <c r="L313" t="n">
-        <v>23</v>
-      </c>
-      <c r="M313" t="n">
-        <v>8</v>
-      </c>
-      <c r="N313" t="n">
-        <v>21</v>
-      </c>
-      <c r="O313" t="n">
-        <v>18</v>
-      </c>
-      <c r="P313" t="n">
-        <v>21</v>
-      </c>
       <c r="Q313" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R313" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S313" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="T313" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487736</t>
         </is>
       </c>
       <c r="V313" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="W313" t="n">
-        <v>100.12</v>
+        <v>93.28</v>
       </c>
       <c r="X313" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.9862778730703259</v>
       </c>
       <c r="Y313" t="n">
-        <v>92.12</v>
+        <v>82.28</v>
       </c>
       <c r="Z313" t="n">
-        <v>94.44203213200173</v>
+        <v>111.8133203694701</v>
       </c>
       <c r="AA313" t="n">
-        <v>0.7657500870170554</v>
+        <v>1.01843910806175</v>
       </c>
       <c r="AB313" t="n">
-        <v>91.74311926605505</v>
+        <v>119.8284561049445</v>
       </c>
       <c r="AC313" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.275</v>
       </c>
       <c r="AD313" t="n">
-        <v>0.525</v>
+        <v>0.65</v>
       </c>
       <c r="AE313" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.4625</v>
       </c>
       <c r="AF313" t="n">
-        <v>2.698912865946681</v>
+        <v>-8.015135735474388</v>
       </c>
       <c r="AG313" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AI313" t="b">
@@ -37744,55 +37744,55 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="E314" t="n">
         <v>200</v>
       </c>
       <c r="F314" t="n">
-        <v>75</v>
+        <v>95</v>
       </c>
       <c r="G314" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H314" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I314" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J314" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="K314" t="n">
+        <v>25</v>
+      </c>
+      <c r="L314" t="n">
+        <v>37</v>
+      </c>
+      <c r="M314" t="n">
+        <v>14</v>
+      </c>
+      <c r="N314" t="n">
         <v>29</v>
       </c>
-      <c r="L314" t="n">
-        <v>40</v>
-      </c>
-      <c r="M314" t="n">
-        <v>8</v>
-      </c>
-      <c r="N314" t="n">
-        <v>27</v>
-      </c>
       <c r="O314" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="P314" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q314" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="R314" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="S314" t="n">
         <v>25</v>
@@ -37802,54 +37802,54 @@
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>2487731</t>
+          <t>2487736</t>
         </is>
       </c>
       <c r="V314" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="W314" t="n">
-        <v>88.59999999999999</v>
+        <v>93.28</v>
       </c>
       <c r="X314" t="n">
-        <v>0.8465011286681716</v>
+        <v>1.01843910806175</v>
       </c>
       <c r="Y314" t="n">
-        <v>80.59999999999999</v>
+        <v>79.28</v>
       </c>
       <c r="Z314" t="n">
-        <v>93.05210918114145</v>
+        <v>119.8284561049445</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.7302731411229135</v>
+        <v>0.9862778730703259</v>
       </c>
       <c r="AB314" t="n">
-        <v>96.92849949647533</v>
+        <v>111.8133203694701</v>
       </c>
       <c r="AC314" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="AD314" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.725</v>
       </c>
       <c r="AE314" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.5375</v>
       </c>
       <c r="AF314" t="n">
-        <v>-3.876390315333879</v>
+        <v>8.015135735474388</v>
       </c>
       <c r="AG314" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AI314" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
@@ -37863,112 +37863,112 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E315" t="n">
         <v>200</v>
       </c>
       <c r="F315" t="n">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="G315" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H315" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="I315" t="n">
         <v>6</v>
       </c>
       <c r="J315" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K315" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L315" t="n">
+        <v>23</v>
+      </c>
+      <c r="M315" t="n">
+        <v>8</v>
+      </c>
+      <c r="N315" t="n">
+        <v>21</v>
+      </c>
+      <c r="O315" t="n">
+        <v>18</v>
+      </c>
+      <c r="P315" t="n">
+        <v>21</v>
+      </c>
+      <c r="Q315" t="n">
         <v>20</v>
       </c>
-      <c r="M315" t="n">
-        <v>6</v>
-      </c>
-      <c r="N315" t="n">
-        <v>30</v>
-      </c>
-      <c r="O315" t="n">
-        <v>6</v>
-      </c>
-      <c r="P315" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q315" t="n">
-        <v>11</v>
-      </c>
       <c r="R315" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="S315" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T315" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V315" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="W315" t="n">
-        <v>71.8</v>
+        <v>100.12</v>
       </c>
       <c r="X315" t="n">
-        <v>0.7103064066852368</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="Y315" t="n">
-        <v>65.8</v>
+        <v>92.12</v>
       </c>
       <c r="Z315" t="n">
-        <v>77.50759878419453</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.935288169868554</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="AB315" t="n">
-        <v>105.5333713633771</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AC315" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="AD315" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.525</v>
       </c>
       <c r="AE315" t="n">
-        <v>0.5</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="AF315" t="n">
-        <v>-28.02577257918253</v>
+        <v>2.698912865946681</v>
       </c>
       <c r="AG315" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -37982,108 +37982,108 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>200</v>
       </c>
       <c r="F316" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G316" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H316" t="n">
+        <v>36</v>
+      </c>
+      <c r="I316" t="n">
+        <v>4</v>
+      </c>
+      <c r="J316" t="n">
+        <v>19</v>
+      </c>
+      <c r="K316" t="n">
         <v>29</v>
       </c>
-      <c r="I316" t="n">
-        <v>11</v>
-      </c>
-      <c r="J316" t="n">
-        <v>30</v>
-      </c>
-      <c r="K316" t="n">
-        <v>15</v>
-      </c>
       <c r="L316" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="M316" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N316" t="n">
         <v>27</v>
       </c>
       <c r="O316" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P316" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q316" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R316" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="S316" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T316" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487731</t>
         </is>
       </c>
       <c r="V316" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="W316" t="n">
-        <v>79.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="X316" t="n">
-        <v>0.935288169868554</v>
+        <v>0.8465011286681716</v>
       </c>
       <c r="Y316" t="n">
-        <v>70.12</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Z316" t="n">
-        <v>105.5333713633771</v>
+        <v>93.05210918114145</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.7103064066852368</v>
+        <v>0.7302731411229135</v>
       </c>
       <c r="AB316" t="n">
-        <v>77.50759878419453</v>
+        <v>96.92849949647533</v>
       </c>
       <c r="AC316" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.25</v>
       </c>
       <c r="AD316" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="AE316" t="n">
-        <v>0.5</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AF316" t="n">
-        <v>28.02577257918253</v>
+        <v>-3.876390315333879</v>
       </c>
       <c r="AG316" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AI316" t="b">
@@ -38101,108 +38101,108 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="E317" t="n">
         <v>200</v>
       </c>
       <c r="F317" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="G317" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H317" t="n">
-        <v>52</v>
+        <v>26</v>
       </c>
       <c r="I317" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J317" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K317" t="n">
         <v>13</v>
       </c>
       <c r="L317" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M317" t="n">
+        <v>6</v>
+      </c>
+      <c r="N317" t="n">
+        <v>30</v>
+      </c>
+      <c r="O317" t="n">
+        <v>6</v>
+      </c>
+      <c r="P317" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>11</v>
+      </c>
+      <c r="R317" t="n">
+        <v>24</v>
+      </c>
+      <c r="S317" t="n">
         <v>19</v>
       </c>
-      <c r="N317" t="n">
-        <v>29</v>
-      </c>
-      <c r="O317" t="n">
-        <v>18</v>
-      </c>
-      <c r="P317" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q317" t="n">
-        <v>31</v>
-      </c>
-      <c r="R317" t="n">
-        <v>19</v>
-      </c>
-      <c r="S317" t="n">
-        <v>17</v>
-      </c>
       <c r="T317" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V317" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="W317" t="n">
-        <v>114.92</v>
+        <v>71.8</v>
       </c>
       <c r="X317" t="n">
-        <v>0.7657500870170554</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="Y317" t="n">
-        <v>95.92</v>
+        <v>65.8</v>
       </c>
       <c r="Z317" t="n">
-        <v>91.74311926605505</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="AB317" t="n">
-        <v>94.44203213200173</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AC317" t="n">
-        <v>0.475</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AD317" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AE317" t="n">
-        <v>0.6233766233766234</v>
+        <v>0.5</v>
       </c>
       <c r="AF317" t="n">
-        <v>-2.698912865946681</v>
+        <v>-28.02577257918253</v>
       </c>
       <c r="AG317" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI317" t="b">
@@ -38216,112 +38216,112 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E318" t="n">
         <v>200</v>
       </c>
       <c r="F318" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="G318" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="H318" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="I318" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J318" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="K318" t="n">
         <v>15</v>
       </c>
       <c r="L318" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M318" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N318" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="O318" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P318" t="n">
         <v>6</v>
       </c>
       <c r="Q318" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R318" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="S318" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="T318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>2487741</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V318" t="n">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="W318" t="n">
-        <v>92</v>
+        <v>79.12</v>
       </c>
       <c r="X318" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="Y318" t="n">
-        <v>81</v>
+        <v>70.12</v>
       </c>
       <c r="Z318" t="n">
-        <v>86.41975308641975</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AA318" t="n">
-        <v>1.026361279170268</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="AB318" t="n">
-        <v>113.6907611297271</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AC318" t="n">
-        <v>0.25</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AD318" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="AE318" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5</v>
       </c>
       <c r="AF318" t="n">
-        <v>-27.27100804330739</v>
+        <v>28.02577257918253</v>
       </c>
       <c r="AG318" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI318" t="b">
@@ -38335,112 +38335,112 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="E319" t="n">
         <v>200</v>
       </c>
       <c r="F319" t="n">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="G319" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H319" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I319" t="n">
+        <v>5</v>
+      </c>
+      <c r="J319" t="n">
+        <v>24</v>
+      </c>
+      <c r="K319" t="n">
+        <v>13</v>
+      </c>
+      <c r="L319" t="n">
+        <v>18</v>
+      </c>
+      <c r="M319" t="n">
+        <v>19</v>
+      </c>
+      <c r="N319" t="n">
+        <v>29</v>
+      </c>
+      <c r="O319" t="n">
+        <v>18</v>
+      </c>
+      <c r="P319" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>31</v>
+      </c>
+      <c r="R319" t="n">
+        <v>19</v>
+      </c>
+      <c r="S319" t="n">
+        <v>17</v>
+      </c>
+      <c r="T319" t="n">
         <v>4</v>
       </c>
-      <c r="J319" t="n">
-        <v>29</v>
-      </c>
-      <c r="K319" t="n">
-        <v>10</v>
-      </c>
-      <c r="L319" t="n">
-        <v>13</v>
-      </c>
-      <c r="M319" t="n">
-        <v>15</v>
-      </c>
-      <c r="N319" t="n">
-        <v>18</v>
-      </c>
-      <c r="O319" t="n">
-        <v>14</v>
-      </c>
-      <c r="P319" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q319" t="n">
-        <v>14</v>
-      </c>
-      <c r="R319" t="n">
-        <v>20</v>
-      </c>
-      <c r="S319" t="n">
-        <v>19</v>
-      </c>
-      <c r="T319" t="n">
-        <v>3</v>
-      </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V319" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="W319" t="n">
-        <v>89.72</v>
+        <v>114.92</v>
       </c>
       <c r="X319" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="Y319" t="n">
-        <v>74.72</v>
+        <v>95.92</v>
       </c>
       <c r="Z319" t="n">
-        <v>85.65310492505354</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="AB319" t="n">
-        <v>107.2423398328691</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AC319" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.475</v>
       </c>
       <c r="AD319" t="n">
-        <v>0.5625</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="AE319" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="AF319" t="n">
-        <v>-21.58923490781554</v>
+        <v>-2.698912865946681</v>
       </c>
       <c r="AG319" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI319" t="b">
@@ -38458,112 +38458,112 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>ADC BOADILLA</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="E320" t="n">
         <v>200</v>
       </c>
       <c r="F320" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G320" t="n">
+        <v>23</v>
+      </c>
+      <c r="H320" t="n">
+        <v>53</v>
+      </c>
+      <c r="I320" t="n">
+        <v>3</v>
+      </c>
+      <c r="J320" t="n">
+        <v>16</v>
+      </c>
+      <c r="K320" t="n">
+        <v>15</v>
+      </c>
+      <c r="L320" t="n">
+        <v>25</v>
+      </c>
+      <c r="M320" t="n">
+        <v>11</v>
+      </c>
+      <c r="N320" t="n">
+        <v>25</v>
+      </c>
+      <c r="O320" t="n">
+        <v>15</v>
+      </c>
+      <c r="P320" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>12</v>
+      </c>
+      <c r="R320" t="n">
         <v>20</v>
       </c>
-      <c r="H320" t="n">
-        <v>43</v>
-      </c>
-      <c r="I320" t="n">
-        <v>9</v>
-      </c>
-      <c r="J320" t="n">
-        <v>26</v>
-      </c>
-      <c r="K320" t="n">
-        <v>8</v>
-      </c>
-      <c r="L320" t="n">
-        <v>16</v>
-      </c>
-      <c r="M320" t="n">
-        <v>4</v>
-      </c>
-      <c r="N320" t="n">
-        <v>27</v>
-      </c>
-      <c r="O320" t="n">
-        <v>20</v>
-      </c>
-      <c r="P320" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q320" t="n">
-        <v>9</v>
-      </c>
-      <c r="R320" t="n">
-        <v>16</v>
-      </c>
       <c r="S320" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="T320" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>2487740</t>
+          <t>2487741</t>
         </is>
       </c>
       <c r="V320" t="n">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="W320" t="n">
-        <v>85.03999999999999</v>
+        <v>92</v>
       </c>
       <c r="X320" t="n">
-        <v>0.8819379115710255</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="Y320" t="n">
-        <v>81.03999999999999</v>
+        <v>81</v>
       </c>
       <c r="Z320" t="n">
-        <v>92.54689042448175</v>
+        <v>86.41975308641975</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.8535582064993829</v>
+        <v>1.026361279170268</v>
       </c>
       <c r="AB320" t="n">
-        <v>96.24304267161409</v>
+        <v>113.6907611297271</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.1</v>
+        <v>0.25</v>
       </c>
       <c r="AD320" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="AE320" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AF320" t="n">
-        <v>-3.696152247132346</v>
+        <v>-27.27100804330739</v>
       </c>
       <c r="AG320" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>ADC BOADILLA</t>
         </is>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AI320" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
@@ -38577,108 +38577,108 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E321" t="n">
         <v>200</v>
       </c>
       <c r="F321" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G321" t="n">
+        <v>21</v>
+      </c>
+      <c r="H321" t="n">
+        <v>41</v>
+      </c>
+      <c r="I321" t="n">
+        <v>4</v>
+      </c>
+      <c r="J321" t="n">
+        <v>29</v>
+      </c>
+      <c r="K321" t="n">
+        <v>10</v>
+      </c>
+      <c r="L321" t="n">
         <v>13</v>
       </c>
-      <c r="H321" t="n">
-        <v>34</v>
-      </c>
-      <c r="I321" t="n">
-        <v>9</v>
-      </c>
-      <c r="J321" t="n">
-        <v>30</v>
-      </c>
-      <c r="K321" t="n">
+      <c r="M321" t="n">
         <v>15</v>
       </c>
-      <c r="L321" t="n">
-        <v>31</v>
-      </c>
-      <c r="M321" t="n">
+      <c r="N321" t="n">
+        <v>18</v>
+      </c>
+      <c r="O321" t="n">
+        <v>14</v>
+      </c>
+      <c r="P321" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>14</v>
+      </c>
+      <c r="R321" t="n">
+        <v>20</v>
+      </c>
+      <c r="S321" t="n">
         <v>19</v>
       </c>
-      <c r="N321" t="n">
-        <v>23</v>
-      </c>
-      <c r="O321" t="n">
-        <v>10</v>
-      </c>
-      <c r="P321" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q321" t="n">
-        <v>16</v>
-      </c>
-      <c r="R321" t="n">
-        <v>21</v>
-      </c>
-      <c r="S321" t="n">
-        <v>24</v>
-      </c>
       <c r="T321" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487742</t>
         </is>
       </c>
       <c r="V321" t="n">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="W321" t="n">
-        <v>93.64</v>
+        <v>89.72</v>
       </c>
       <c r="X321" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.7133303611234953</v>
       </c>
       <c r="Y321" t="n">
-        <v>74.64</v>
+        <v>74.72</v>
       </c>
       <c r="Z321" t="n">
-        <v>91.10396570203645</v>
+        <v>85.65310492505354</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="AB321" t="n">
-        <v>66.44085461177697</v>
+        <v>107.2423398328691</v>
       </c>
       <c r="AC321" t="n">
-        <v>0.475</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="AD321" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.5625</v>
       </c>
       <c r="AE321" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="AF321" t="n">
-        <v>24.66311109025948</v>
+        <v>-21.58923490781554</v>
       </c>
       <c r="AG321" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="AI321" t="b">
@@ -38696,22 +38696,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="E322" t="n">
         <v>200</v>
       </c>
       <c r="F322" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="G322" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="H322" t="n">
         <v>45</v>
@@ -38720,88 +38720,88 @@
         <v>8</v>
       </c>
       <c r="J322" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K322" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L322" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="M322" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N322" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O322" t="n">
+        <v>15</v>
+      </c>
+      <c r="P322" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>14</v>
+      </c>
+      <c r="R322" t="n">
+        <v>26</v>
+      </c>
+      <c r="S322" t="n">
         <v>19</v>
-      </c>
-      <c r="P322" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q322" t="n">
-        <v>19</v>
-      </c>
-      <c r="R322" t="n">
-        <v>15</v>
-      </c>
-      <c r="S322" t="n">
-        <v>15</v>
       </c>
       <c r="T322" t="n">
         <v>1</v>
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>2487744</t>
+          <t>2487738</t>
         </is>
       </c>
       <c r="V322" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="W322" t="n">
-        <v>94.28</v>
+        <v>92.92</v>
       </c>
       <c r="X322" t="n">
-        <v>0.9227831989817564</v>
+        <v>0.8179078777442962</v>
       </c>
       <c r="Y322" t="n">
-        <v>85.28</v>
+        <v>79.92</v>
       </c>
       <c r="Z322" t="n">
-        <v>102.0168855534709</v>
+        <v>95.09509509509509</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.7312996239030506</v>
+        <v>0.8848566308243727</v>
       </c>
       <c r="AB322" t="n">
-        <v>83.61204013377926</v>
+        <v>98.40558046836074</v>
       </c>
       <c r="AC322" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="AD322" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.75</v>
       </c>
       <c r="AE322" t="n">
-        <v>0.4626865671641791</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="AF322" t="n">
-        <v>18.40484541969165</v>
+        <v>-3.310485373265649</v>
       </c>
       <c r="AG322" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -38815,112 +38815,112 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E323" t="n">
         <v>200</v>
       </c>
       <c r="F323" t="n">
-        <v>51</v>
+        <v>79</v>
       </c>
       <c r="G323" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="H323" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I323" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J323" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K323" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L323" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="M323" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N323" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O323" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="P323" t="n">
         <v>9</v>
       </c>
       <c r="Q323" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R323" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S323" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T323" t="n">
         <v>3</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487738</t>
         </is>
       </c>
       <c r="V323" t="n">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="W323" t="n">
-        <v>90.75999999999999</v>
+        <v>89.28</v>
       </c>
       <c r="X323" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.8848566308243727</v>
       </c>
       <c r="Y323" t="n">
-        <v>76.75999999999999</v>
+        <v>80.28</v>
       </c>
       <c r="Z323" t="n">
-        <v>66.44085461177697</v>
+        <v>98.40558046836074</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.8179078777442962</v>
       </c>
       <c r="AB323" t="n">
-        <v>91.10396570203645</v>
+        <v>95.09509509509509</v>
       </c>
       <c r="AC323" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.25</v>
       </c>
       <c r="AD323" t="n">
-        <v>0.525</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="AE323" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="AF323" t="n">
-        <v>-24.66311109025948</v>
+        <v>3.310485373265649</v>
       </c>
       <c r="AG323" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -38934,108 +38934,108 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E324" t="n">
         <v>200</v>
       </c>
       <c r="F324" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="G324" t="n">
+        <v>20</v>
+      </c>
+      <c r="H324" t="n">
+        <v>43</v>
+      </c>
+      <c r="I324" t="n">
+        <v>9</v>
+      </c>
+      <c r="J324" t="n">
+        <v>26</v>
+      </c>
+      <c r="K324" t="n">
+        <v>8</v>
+      </c>
+      <c r="L324" t="n">
+        <v>16</v>
+      </c>
+      <c r="M324" t="n">
+        <v>4</v>
+      </c>
+      <c r="N324" t="n">
         <v>27</v>
       </c>
-      <c r="H324" t="n">
-        <v>51</v>
-      </c>
-      <c r="I324" t="n">
-        <v>8</v>
-      </c>
-      <c r="J324" t="n">
+      <c r="O324" t="n">
         <v>20</v>
       </c>
-      <c r="K324" t="n">
-        <v>17</v>
-      </c>
-      <c r="L324" t="n">
-        <v>24</v>
-      </c>
-      <c r="M324" t="n">
+      <c r="P324" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q324" t="n">
         <v>9</v>
       </c>
-      <c r="N324" t="n">
-        <v>33</v>
-      </c>
-      <c r="O324" t="n">
-        <v>23</v>
-      </c>
-      <c r="P324" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q324" t="n">
-        <v>11</v>
-      </c>
       <c r="R324" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="S324" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T324" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U324" t="inlineStr">
         <is>
-          <t>2487741</t>
+          <t>2487740</t>
         </is>
       </c>
       <c r="V324" t="n">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="W324" t="n">
-        <v>92.56</v>
+        <v>85.03999999999999</v>
       </c>
       <c r="X324" t="n">
-        <v>1.026361279170268</v>
+        <v>0.8819379115710255</v>
       </c>
       <c r="Y324" t="n">
-        <v>83.56</v>
+        <v>81.03999999999999</v>
       </c>
       <c r="Z324" t="n">
-        <v>113.6907611297271</v>
+        <v>92.54689042448175</v>
       </c>
       <c r="AA324" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.8535582064993829</v>
       </c>
       <c r="AB324" t="n">
-        <v>86.41975308641975</v>
+        <v>96.24304267161409</v>
       </c>
       <c r="AC324" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.1</v>
       </c>
       <c r="AD324" t="n">
-        <v>0.75</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="AE324" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="AF324" t="n">
-        <v>27.27100804330739</v>
+        <v>-3.696152247132346</v>
       </c>
       <c r="AG324" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AH324" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AI324" t="b">
@@ -39053,112 +39053,112 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E325" t="n">
         <v>200</v>
       </c>
       <c r="F325" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G325" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="H325" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="I325" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J325" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K325" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L325" t="n">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="M325" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="N325" t="n">
+        <v>23</v>
+      </c>
+      <c r="O325" t="n">
+        <v>10</v>
+      </c>
+      <c r="P325" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>16</v>
+      </c>
+      <c r="R325" t="n">
+        <v>21</v>
+      </c>
+      <c r="S325" t="n">
         <v>24</v>
-      </c>
-      <c r="O325" t="n">
-        <v>13</v>
-      </c>
-      <c r="P325" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q325" t="n">
-        <v>22</v>
-      </c>
-      <c r="R325" t="n">
-        <v>15</v>
-      </c>
-      <c r="S325" t="n">
-        <v>15</v>
       </c>
       <c r="T325" t="n">
         <v>2</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>2487744</t>
+          <t>2487739</t>
         </is>
       </c>
       <c r="V325" t="n">
-        <v>87</v>
+        <v>51</v>
       </c>
       <c r="W325" t="n">
-        <v>95.72</v>
+        <v>93.64</v>
       </c>
       <c r="X325" t="n">
-        <v>0.7312996239030506</v>
+        <v>0.7261853908586074</v>
       </c>
       <c r="Y325" t="n">
-        <v>83.72</v>
+        <v>74.64</v>
       </c>
       <c r="Z325" t="n">
-        <v>83.61204013377926</v>
+        <v>91.10396570203645</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.9227831989817564</v>
+        <v>0.5619215513442045</v>
       </c>
       <c r="AB325" t="n">
-        <v>102.0168855534709</v>
+        <v>66.44085461177697</v>
       </c>
       <c r="AC325" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.475</v>
       </c>
       <c r="AD325" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="AE325" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AF325" t="n">
-        <v>-18.40484541969165</v>
+        <v>24.66311109025948</v>
       </c>
       <c r="AG325" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AI325" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -39172,112 +39172,112 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="E326" t="n">
         <v>200</v>
       </c>
       <c r="F326" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="G326" t="n">
+        <v>29</v>
+      </c>
+      <c r="H326" t="n">
+        <v>45</v>
+      </c>
+      <c r="I326" t="n">
+        <v>8</v>
+      </c>
+      <c r="J326" t="n">
+        <v>25</v>
+      </c>
+      <c r="K326" t="n">
+        <v>5</v>
+      </c>
+      <c r="L326" t="n">
         <v>12</v>
       </c>
-      <c r="H326" t="n">
-        <v>29</v>
-      </c>
-      <c r="I326" t="n">
-        <v>6</v>
-      </c>
-      <c r="J326" t="n">
-        <v>21</v>
-      </c>
-      <c r="K326" t="n">
-        <v>11</v>
-      </c>
-      <c r="L326" t="n">
+      <c r="M326" t="n">
+        <v>9</v>
+      </c>
+      <c r="N326" t="n">
+        <v>22</v>
+      </c>
+      <c r="O326" t="n">
+        <v>19</v>
+      </c>
+      <c r="P326" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>19</v>
+      </c>
+      <c r="R326" t="n">
         <v>15</v>
       </c>
-      <c r="M326" t="n">
-        <v>4</v>
-      </c>
-      <c r="N326" t="n">
-        <v>27</v>
-      </c>
-      <c r="O326" t="n">
-        <v>13</v>
-      </c>
-      <c r="P326" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q326" t="n">
-        <v>27</v>
-      </c>
-      <c r="R326" t="n">
-        <v>21</v>
-      </c>
       <c r="S326" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T326" t="n">
         <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>2487743</t>
+          <t>2487744</t>
         </is>
       </c>
       <c r="V326" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="W326" t="n">
-        <v>83.59999999999999</v>
+        <v>94.28</v>
       </c>
       <c r="X326" t="n">
-        <v>0.6339712918660287</v>
+        <v>0.9227831989817564</v>
       </c>
       <c r="Y326" t="n">
-        <v>79.59999999999999</v>
+        <v>85.28</v>
       </c>
       <c r="Z326" t="n">
-        <v>66.58291457286433</v>
+        <v>102.0168855534709</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.9238138686131386</v>
+        <v>0.7312996239030506</v>
       </c>
       <c r="AB326" t="n">
-        <v>101.6566265060241</v>
+        <v>83.61204013377926</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AD326" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AE326" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.4626865671641791</v>
       </c>
       <c r="AF326" t="n">
-        <v>-35.07371193315976</v>
+        <v>18.40484541969165</v>
       </c>
       <c r="AG326" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AI326" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
@@ -39291,55 +39291,55 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="E327" t="n">
         <v>200</v>
       </c>
       <c r="F327" t="n">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="G327" t="n">
+        <v>12</v>
+      </c>
+      <c r="H327" t="n">
+        <v>35</v>
+      </c>
+      <c r="I327" t="n">
+        <v>2</v>
+      </c>
+      <c r="J327" t="n">
         <v>24</v>
       </c>
-      <c r="H327" t="n">
-        <v>43</v>
-      </c>
-      <c r="I327" t="n">
-        <v>6</v>
-      </c>
-      <c r="J327" t="n">
-        <v>19</v>
-      </c>
       <c r="K327" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L327" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="M327" t="n">
         <v>14</v>
       </c>
       <c r="N327" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="O327" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="P327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q327" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R327" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="S327" t="n">
         <v>20</v>
@@ -39349,50 +39349,50 @@
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487739</t>
         </is>
       </c>
       <c r="V327" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="W327" t="n">
-        <v>85.8</v>
+        <v>90.75999999999999</v>
       </c>
       <c r="X327" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.5619215513442045</v>
       </c>
       <c r="Y327" t="n">
-        <v>71.8</v>
+        <v>76.75999999999999</v>
       </c>
       <c r="Z327" t="n">
-        <v>107.2423398328691</v>
+        <v>66.44085461177697</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.7261853908586074</v>
       </c>
       <c r="AB327" t="n">
-        <v>85.65310492505354</v>
+        <v>91.10396570203645</v>
       </c>
       <c r="AC327" t="n">
-        <v>0.4375</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="AD327" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.525</v>
       </c>
       <c r="AE327" t="n">
-        <v>0.547945205479452</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AF327" t="n">
-        <v>21.58923490781554</v>
+        <v>-24.66311109025948</v>
       </c>
       <c r="AG327" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AI327" t="b">
@@ -39410,108 +39410,108 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>ADC BOADILLA</t>
         </is>
       </c>
       <c r="E328" t="n">
         <v>200</v>
       </c>
       <c r="F328" t="n">
-        <v>81</v>
+        <v>95</v>
       </c>
       <c r="G328" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="H328" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="I328" t="n">
+        <v>8</v>
+      </c>
+      <c r="J328" t="n">
+        <v>20</v>
+      </c>
+      <c r="K328" t="n">
+        <v>17</v>
+      </c>
+      <c r="L328" t="n">
+        <v>24</v>
+      </c>
+      <c r="M328" t="n">
         <v>9</v>
       </c>
-      <c r="J328" t="n">
+      <c r="N328" t="n">
+        <v>33</v>
+      </c>
+      <c r="O328" t="n">
         <v>23</v>
       </c>
-      <c r="K328" t="n">
-        <v>16</v>
-      </c>
-      <c r="L328" t="n">
-        <v>22</v>
-      </c>
-      <c r="M328" t="n">
+      <c r="P328" t="n">
         <v>8</v>
       </c>
-      <c r="N328" t="n">
-        <v>27</v>
-      </c>
-      <c r="O328" t="n">
-        <v>24</v>
-      </c>
-      <c r="P328" t="n">
+      <c r="Q328" t="n">
+        <v>11</v>
+      </c>
+      <c r="R328" t="n">
+        <v>18</v>
+      </c>
+      <c r="S328" t="n">
         <v>20</v>
       </c>
-      <c r="Q328" t="n">
-        <v>16</v>
-      </c>
-      <c r="R328" t="n">
-        <v>20</v>
-      </c>
-      <c r="S328" t="n">
-        <v>21</v>
-      </c>
       <c r="T328" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>2487743</t>
+          <t>2487741</t>
         </is>
       </c>
       <c r="V328" t="n">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="W328" t="n">
-        <v>87.68000000000001</v>
+        <v>92.56</v>
       </c>
       <c r="X328" t="n">
-        <v>0.9238138686131386</v>
+        <v>1.026361279170268</v>
       </c>
       <c r="Y328" t="n">
-        <v>79.68000000000001</v>
+        <v>83.56</v>
       </c>
       <c r="Z328" t="n">
-        <v>101.6566265060241</v>
+        <v>113.6907611297271</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.6339712918660287</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="AB328" t="n">
-        <v>66.58291457286433</v>
+        <v>86.41975308641975</v>
       </c>
       <c r="AC328" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="AD328" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.75</v>
       </c>
       <c r="AE328" t="n">
-        <v>0.5303030303030303</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="AF328" t="n">
-        <v>35.07371193315976</v>
+        <v>27.27100804330739</v>
       </c>
       <c r="AG328" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>ADC BOADILLA</t>
         </is>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AI328" t="b">
@@ -39529,111 +39529,587 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="E329" t="n">
         <v>200</v>
       </c>
       <c r="F329" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="G329" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H329" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="I329" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J329" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="K329" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L329" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="M329" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N329" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="O329" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="P329" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Q329" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="R329" t="n">
         <v>15</v>
       </c>
       <c r="S329" t="n">
+        <v>15</v>
+      </c>
+      <c r="T329" t="n">
+        <v>2</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>87</v>
+      </c>
+      <c r="W329" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="X329" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>-18.40484541969165</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>24</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>200</v>
+      </c>
+      <c r="F330" t="n">
+        <v>53</v>
+      </c>
+      <c r="G330" t="n">
+        <v>12</v>
+      </c>
+      <c r="H330" t="n">
+        <v>29</v>
+      </c>
+      <c r="I330" t="n">
+        <v>6</v>
+      </c>
+      <c r="J330" t="n">
+        <v>21</v>
+      </c>
+      <c r="K330" t="n">
+        <v>11</v>
+      </c>
+      <c r="L330" t="n">
+        <v>15</v>
+      </c>
+      <c r="M330" t="n">
+        <v>4</v>
+      </c>
+      <c r="N330" t="n">
+        <v>27</v>
+      </c>
+      <c r="O330" t="n">
+        <v>13</v>
+      </c>
+      <c r="P330" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>27</v>
+      </c>
+      <c r="R330" t="n">
+        <v>21</v>
+      </c>
+      <c r="S330" t="n">
+        <v>20</v>
+      </c>
+      <c r="T330" t="n">
+        <v>1</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>81</v>
+      </c>
+      <c r="W330" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>0.4696969696969697</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>-35.07371193315976</v>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>24</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" t="n">
+        <v>77</v>
+      </c>
+      <c r="G331" t="n">
+        <v>24</v>
+      </c>
+      <c r="H331" t="n">
+        <v>43</v>
+      </c>
+      <c r="I331" t="n">
+        <v>6</v>
+      </c>
+      <c r="J331" t="n">
+        <v>19</v>
+      </c>
+      <c r="K331" t="n">
+        <v>11</v>
+      </c>
+      <c r="L331" t="n">
+        <v>20</v>
+      </c>
+      <c r="M331" t="n">
+        <v>14</v>
+      </c>
+      <c r="N331" t="n">
+        <v>26</v>
+      </c>
+      <c r="O331" t="n">
+        <v>13</v>
+      </c>
+      <c r="P331" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>15</v>
+      </c>
+      <c r="R331" t="n">
+        <v>20</v>
+      </c>
+      <c r="S331" t="n">
+        <v>20</v>
+      </c>
+      <c r="T331" t="n">
+        <v>3</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2487742</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>64</v>
+      </c>
+      <c r="W331" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>107.2423398328691</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>0.7133303611234953</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>85.65310492505354</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>21.58923490781554</v>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI331" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>24</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>200</v>
+      </c>
+      <c r="F332" t="n">
+        <v>81</v>
+      </c>
+      <c r="G332" t="n">
+        <v>19</v>
+      </c>
+      <c r="H332" t="n">
+        <v>39</v>
+      </c>
+      <c r="I332" t="n">
+        <v>9</v>
+      </c>
+      <c r="J332" t="n">
+        <v>23</v>
+      </c>
+      <c r="K332" t="n">
         <v>16</v>
       </c>
-      <c r="T329" t="n">
+      <c r="L332" t="n">
+        <v>22</v>
+      </c>
+      <c r="M332" t="n">
+        <v>8</v>
+      </c>
+      <c r="N332" t="n">
+        <v>27</v>
+      </c>
+      <c r="O332" t="n">
+        <v>24</v>
+      </c>
+      <c r="P332" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>16</v>
+      </c>
+      <c r="R332" t="n">
+        <v>20</v>
+      </c>
+      <c r="S332" t="n">
+        <v>21</v>
+      </c>
+      <c r="T332" t="n">
+        <v>0</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>53</v>
+      </c>
+      <c r="W332" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="X332" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>35.07371193315976</v>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>24</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>83</v>
+      </c>
+      <c r="G333" t="n">
+        <v>21</v>
+      </c>
+      <c r="H333" t="n">
+        <v>39</v>
+      </c>
+      <c r="I333" t="n">
+        <v>9</v>
+      </c>
+      <c r="J333" t="n">
+        <v>30</v>
+      </c>
+      <c r="K333" t="n">
+        <v>14</v>
+      </c>
+      <c r="L333" t="n">
+        <v>21</v>
+      </c>
+      <c r="M333" t="n">
+        <v>11</v>
+      </c>
+      <c r="N333" t="n">
+        <v>36</v>
+      </c>
+      <c r="O333" t="n">
+        <v>10</v>
+      </c>
+      <c r="P333" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>19</v>
+      </c>
+      <c r="R333" t="n">
+        <v>15</v>
+      </c>
+      <c r="S333" t="n">
+        <v>16</v>
+      </c>
+      <c r="T333" t="n">
         <v>3</v>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="U333" t="inlineStr">
         <is>
           <t>2487740</t>
         </is>
       </c>
-      <c r="V329" t="n">
+      <c r="V333" t="n">
         <v>75</v>
       </c>
-      <c r="W329" t="n">
+      <c r="W333" t="n">
         <v>97.24000000000001</v>
       </c>
-      <c r="X329" t="n">
+      <c r="X333" t="n">
         <v>0.8535582064993829</v>
       </c>
-      <c r="Y329" t="n">
+      <c r="Y333" t="n">
         <v>86.24000000000001</v>
       </c>
-      <c r="Z329" t="n">
+      <c r="Z333" t="n">
         <v>96.24304267161409</v>
       </c>
-      <c r="AA329" t="n">
+      <c r="AA333" t="n">
         <v>0.8819379115710255</v>
       </c>
-      <c r="AB329" t="n">
+      <c r="AB333" t="n">
         <v>92.54689042448175</v>
       </c>
-      <c r="AC329" t="n">
+      <c r="AC333" t="n">
         <v>0.2894736842105263</v>
       </c>
-      <c r="AD329" t="n">
+      <c r="AD333" t="n">
         <v>0.9</v>
       </c>
-      <c r="AE329" t="n">
+      <c r="AE333" t="n">
         <v>0.6025641025641025</v>
       </c>
-      <c r="AF329" t="n">
+      <c r="AF333" t="n">
         <v>3.696152247132346</v>
       </c>
-      <c r="AG329" t="inlineStr">
+      <c r="AG333" t="inlineStr">
         <is>
           <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
-      <c r="AH329" t="inlineStr">
+      <c r="AH333" t="inlineStr">
         <is>
           <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
-      <c r="AI329" t="b">
+      <c r="AI333" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI329"/>
+  <dimension ref="A1:AI351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37625,112 +37625,112 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="E313" t="n">
         <v>200</v>
       </c>
       <c r="F313" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G313" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H313" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I313" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J313" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K313" t="n">
+        <v>16</v>
+      </c>
+      <c r="L313" t="n">
         <v>19</v>
       </c>
-      <c r="L313" t="n">
-        <v>23</v>
-      </c>
       <c r="M313" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N313" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O313" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P313" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Q313" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R313" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S313" t="n">
         <v>18</v>
       </c>
       <c r="T313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487737</t>
         </is>
       </c>
       <c r="V313" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="W313" t="n">
-        <v>100.12</v>
+        <v>89.36</v>
       </c>
       <c r="X313" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.8840644583706356</v>
       </c>
       <c r="Y313" t="n">
-        <v>92.12</v>
+        <v>79.36</v>
       </c>
       <c r="Z313" t="n">
-        <v>94.44203213200173</v>
+        <v>99.54637096774194</v>
       </c>
       <c r="AA313" t="n">
-        <v>0.7657500870170554</v>
+        <v>1.047381546134663</v>
       </c>
       <c r="AB313" t="n">
-        <v>91.74311926605505</v>
+        <v>114.7540983606557</v>
       </c>
       <c r="AC313" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="AD313" t="n">
-        <v>0.525</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="AE313" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="AF313" t="n">
-        <v>2.698912865946681</v>
+        <v>-15.2077273929138</v>
       </c>
       <c r="AG313" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI313" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -37744,108 +37744,108 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E314" t="n">
         <v>200</v>
       </c>
       <c r="F314" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G314" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H314" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I314" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J314" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K314" t="n">
         <v>29</v>
       </c>
       <c r="L314" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M314" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O314" t="n">
         <v>11</v>
       </c>
       <c r="P314" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q314" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S314" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T314" t="n">
         <v>4</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>2487731</t>
+          <t>2487736</t>
         </is>
       </c>
       <c r="V314" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="W314" t="n">
-        <v>88.59999999999999</v>
+        <v>93.28</v>
       </c>
       <c r="X314" t="n">
-        <v>0.8465011286681716</v>
+        <v>0.9862778730703259</v>
       </c>
       <c r="Y314" t="n">
-        <v>80.59999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="Z314" t="n">
-        <v>93.05210918114145</v>
+        <v>111.8133203694701</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.7302731411229135</v>
+        <v>1.01843910806175</v>
       </c>
       <c r="AB314" t="n">
-        <v>96.92849949647533</v>
+        <v>119.8284561049445</v>
       </c>
       <c r="AC314" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="AD314" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.65</v>
       </c>
       <c r="AE314" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4625</v>
       </c>
       <c r="AF314" t="n">
-        <v>-3.876390315333879</v>
+        <v>-8.015135735474388</v>
       </c>
       <c r="AG314" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AI314" t="b">
@@ -37863,112 +37863,112 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="E315" t="n">
         <v>200</v>
       </c>
       <c r="F315" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="G315" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H315" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I315" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J315" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K315" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L315" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M315" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N315" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O315" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P315" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q315" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R315" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="S315" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T315" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487737</t>
         </is>
       </c>
       <c r="V315" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W315" t="n">
-        <v>71.8</v>
+        <v>80.2</v>
       </c>
       <c r="X315" t="n">
-        <v>0.7103064066852368</v>
+        <v>1.047381546134663</v>
       </c>
       <c r="Y315" t="n">
-        <v>65.8</v>
+        <v>73.2</v>
       </c>
       <c r="Z315" t="n">
-        <v>77.50759878419453</v>
+        <v>114.7540983606557</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.935288169868554</v>
+        <v>0.8840644583706356</v>
       </c>
       <c r="AB315" t="n">
-        <v>105.5333713633771</v>
+        <v>99.54637096774194</v>
       </c>
       <c r="AC315" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="AD315" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="AE315" t="n">
-        <v>0.5</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AF315" t="n">
-        <v>-28.02577257918253</v>
+        <v>15.2077273929138</v>
       </c>
       <c r="AG315" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -37982,108 +37982,108 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>200</v>
       </c>
       <c r="F316" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G316" t="n">
+        <v>22</v>
+      </c>
+      <c r="H316" t="n">
+        <v>38</v>
+      </c>
+      <c r="I316" t="n">
+        <v>8</v>
+      </c>
+      <c r="J316" t="n">
+        <v>26</v>
+      </c>
+      <c r="K316" t="n">
+        <v>17</v>
+      </c>
+      <c r="L316" t="n">
+        <v>34</v>
+      </c>
+      <c r="M316" t="n">
         <v>13</v>
       </c>
-      <c r="H316" t="n">
-        <v>29</v>
-      </c>
-      <c r="I316" t="n">
-        <v>11</v>
-      </c>
-      <c r="J316" t="n">
-        <v>30</v>
-      </c>
-      <c r="K316" t="n">
-        <v>15</v>
-      </c>
-      <c r="L316" t="n">
-        <v>23</v>
-      </c>
-      <c r="M316" t="n">
-        <v>9</v>
-      </c>
       <c r="N316" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O316" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P316" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q316" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R316" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S316" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T316" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487732</t>
         </is>
       </c>
       <c r="V316" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="W316" t="n">
-        <v>79.12</v>
+        <v>92.96000000000001</v>
       </c>
       <c r="X316" t="n">
-        <v>0.935288169868554</v>
+        <v>0.9143717728055076</v>
       </c>
       <c r="Y316" t="n">
-        <v>70.12</v>
+        <v>79.96000000000001</v>
       </c>
       <c r="Z316" t="n">
-        <v>105.5333713633771</v>
+        <v>106.3031515757879</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.7103064066852368</v>
+        <v>1.049868766404199</v>
       </c>
       <c r="AB316" t="n">
-        <v>77.50759878419453</v>
+        <v>116.448326055313</v>
       </c>
       <c r="AC316" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="AD316" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="AE316" t="n">
-        <v>0.5</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="AF316" t="n">
-        <v>28.02577257918253</v>
+        <v>-10.14517447952508</v>
       </c>
       <c r="AG316" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="AI316" t="b">
@@ -38101,108 +38101,108 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="E317" t="n">
         <v>200</v>
       </c>
       <c r="F317" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G317" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H317" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I317" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J317" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K317" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L317" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="M317" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N317" t="n">
         <v>29</v>
       </c>
       <c r="O317" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P317" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q317" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="R317" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="S317" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T317" t="n">
         <v>4</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487736</t>
         </is>
       </c>
       <c r="V317" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="W317" t="n">
-        <v>114.92</v>
+        <v>93.28</v>
       </c>
       <c r="X317" t="n">
-        <v>0.7657500870170554</v>
+        <v>1.01843910806175</v>
       </c>
       <c r="Y317" t="n">
-        <v>95.92</v>
+        <v>79.28</v>
       </c>
       <c r="Z317" t="n">
-        <v>91.74311926605505</v>
+        <v>119.8284561049445</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.9862778730703259</v>
       </c>
       <c r="AB317" t="n">
-        <v>94.44203213200173</v>
+        <v>111.8133203694701</v>
       </c>
       <c r="AC317" t="n">
-        <v>0.475</v>
+        <v>0.35</v>
       </c>
       <c r="AD317" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.725</v>
       </c>
       <c r="AE317" t="n">
-        <v>0.6233766233766234</v>
+        <v>0.5375</v>
       </c>
       <c r="AF317" t="n">
-        <v>-2.698912865946681</v>
+        <v>8.015135735474388</v>
       </c>
       <c r="AG317" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AI317" t="b">
@@ -38216,112 +38216,112 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E318" t="n">
         <v>200</v>
       </c>
       <c r="F318" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="G318" t="n">
+        <v>25</v>
+      </c>
+      <c r="H318" t="n">
+        <v>48</v>
+      </c>
+      <c r="I318" t="n">
+        <v>6</v>
+      </c>
+      <c r="J318" t="n">
+        <v>22</v>
+      </c>
+      <c r="K318" t="n">
+        <v>19</v>
+      </c>
+      <c r="L318" t="n">
         <v>23</v>
       </c>
-      <c r="H318" t="n">
-        <v>53</v>
-      </c>
-      <c r="I318" t="n">
-        <v>3</v>
-      </c>
-      <c r="J318" t="n">
-        <v>16</v>
-      </c>
-      <c r="K318" t="n">
-        <v>15</v>
-      </c>
-      <c r="L318" t="n">
-        <v>25</v>
-      </c>
       <c r="M318" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N318" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O318" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P318" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q318" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R318" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S318" t="n">
         <v>18</v>
       </c>
       <c r="T318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>2487741</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V318" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="W318" t="n">
-        <v>92</v>
+        <v>100.12</v>
       </c>
       <c r="X318" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="Y318" t="n">
-        <v>81</v>
+        <v>92.12</v>
       </c>
       <c r="Z318" t="n">
-        <v>86.41975308641975</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AA318" t="n">
-        <v>1.026361279170268</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="AB318" t="n">
-        <v>113.6907611297271</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AC318" t="n">
-        <v>0.25</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="AD318" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.525</v>
       </c>
       <c r="AE318" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="AF318" t="n">
-        <v>-27.27100804330739</v>
+        <v>2.698912865946681</v>
       </c>
       <c r="AG318" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI318" t="b">
@@ -38335,116 +38335,116 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E319" t="n">
         <v>200</v>
       </c>
       <c r="F319" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G319" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H319" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I319" t="n">
         <v>4</v>
       </c>
       <c r="J319" t="n">
+        <v>19</v>
+      </c>
+      <c r="K319" t="n">
         <v>29</v>
       </c>
-      <c r="K319" t="n">
+      <c r="L319" t="n">
+        <v>40</v>
+      </c>
+      <c r="M319" t="n">
+        <v>8</v>
+      </c>
+      <c r="N319" t="n">
+        <v>27</v>
+      </c>
+      <c r="O319" t="n">
+        <v>11</v>
+      </c>
+      <c r="P319" t="n">
         <v>10</v>
       </c>
-      <c r="L319" t="n">
-        <v>13</v>
-      </c>
-      <c r="M319" t="n">
-        <v>15</v>
-      </c>
-      <c r="N319" t="n">
-        <v>18</v>
-      </c>
-      <c r="O319" t="n">
-        <v>14</v>
-      </c>
-      <c r="P319" t="n">
-        <v>8</v>
-      </c>
       <c r="Q319" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R319" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="S319" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T319" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487731</t>
         </is>
       </c>
       <c r="V319" t="n">
         <v>77</v>
       </c>
       <c r="W319" t="n">
-        <v>89.72</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="X319" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.8465011286681716</v>
       </c>
       <c r="Y319" t="n">
-        <v>74.72</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Z319" t="n">
-        <v>85.65310492505354</v>
+        <v>93.05210918114145</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.7302731411229135</v>
       </c>
       <c r="AB319" t="n">
-        <v>107.2423398328691</v>
+        <v>96.92849949647533</v>
       </c>
       <c r="AC319" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.25</v>
       </c>
       <c r="AD319" t="n">
-        <v>0.5625</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="AE319" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AF319" t="n">
-        <v>-21.58923490781554</v>
+        <v>-3.876390315333879</v>
       </c>
       <c r="AG319" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AI319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -38454,112 +38454,112 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="E320" t="n">
         <v>200</v>
       </c>
       <c r="F320" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G320" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H320" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I320" t="n">
+        <v>12</v>
+      </c>
+      <c r="J320" t="n">
+        <v>25</v>
+      </c>
+      <c r="K320" t="n">
+        <v>18</v>
+      </c>
+      <c r="L320" t="n">
+        <v>26</v>
+      </c>
+      <c r="M320" t="n">
         <v>9</v>
       </c>
-      <c r="J320" t="n">
+      <c r="N320" t="n">
+        <v>23</v>
+      </c>
+      <c r="O320" t="n">
+        <v>18</v>
+      </c>
+      <c r="P320" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>8</v>
+      </c>
+      <c r="R320" t="n">
         <v>26</v>
       </c>
-      <c r="K320" t="n">
-        <v>8</v>
-      </c>
-      <c r="L320" t="n">
-        <v>16</v>
-      </c>
-      <c r="M320" t="n">
-        <v>4</v>
-      </c>
-      <c r="N320" t="n">
-        <v>27</v>
-      </c>
-      <c r="O320" t="n">
-        <v>20</v>
-      </c>
-      <c r="P320" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q320" t="n">
-        <v>9</v>
-      </c>
-      <c r="R320" t="n">
-        <v>16</v>
-      </c>
       <c r="S320" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T320" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>2487740</t>
+          <t>2487732</t>
         </is>
       </c>
       <c r="V320" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="W320" t="n">
-        <v>85.03999999999999</v>
+        <v>91.44</v>
       </c>
       <c r="X320" t="n">
-        <v>0.8819379115710255</v>
+        <v>1.049868766404199</v>
       </c>
       <c r="Y320" t="n">
-        <v>81.03999999999999</v>
+        <v>82.44</v>
       </c>
       <c r="Z320" t="n">
-        <v>92.54689042448175</v>
+        <v>116.448326055313</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.8535582064993829</v>
+        <v>0.9143717728055076</v>
       </c>
       <c r="AB320" t="n">
-        <v>96.24304267161409</v>
+        <v>106.3031515757879</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.1</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="AD320" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="AE320" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.4776119402985075</v>
       </c>
       <c r="AF320" t="n">
-        <v>-3.696152247132346</v>
+        <v>10.14517447952508</v>
       </c>
       <c r="AG320" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="AI320" t="b">
@@ -38573,112 +38573,112 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="E321" t="n">
         <v>200</v>
       </c>
       <c r="F321" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="G321" t="n">
+        <v>10</v>
+      </c>
+      <c r="H321" t="n">
+        <v>26</v>
+      </c>
+      <c r="I321" t="n">
+        <v>6</v>
+      </c>
+      <c r="J321" t="n">
+        <v>26</v>
+      </c>
+      <c r="K321" t="n">
         <v>13</v>
       </c>
-      <c r="H321" t="n">
-        <v>34</v>
-      </c>
-      <c r="I321" t="n">
-        <v>9</v>
-      </c>
-      <c r="J321" t="n">
+      <c r="L321" t="n">
+        <v>20</v>
+      </c>
+      <c r="M321" t="n">
+        <v>6</v>
+      </c>
+      <c r="N321" t="n">
         <v>30</v>
       </c>
-      <c r="K321" t="n">
-        <v>15</v>
-      </c>
-      <c r="L321" t="n">
-        <v>31</v>
-      </c>
-      <c r="M321" t="n">
+      <c r="O321" t="n">
+        <v>6</v>
+      </c>
+      <c r="P321" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>11</v>
+      </c>
+      <c r="R321" t="n">
+        <v>24</v>
+      </c>
+      <c r="S321" t="n">
         <v>19</v>
-      </c>
-      <c r="N321" t="n">
-        <v>23</v>
-      </c>
-      <c r="O321" t="n">
-        <v>10</v>
-      </c>
-      <c r="P321" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q321" t="n">
-        <v>16</v>
-      </c>
-      <c r="R321" t="n">
-        <v>21</v>
-      </c>
-      <c r="S321" t="n">
-        <v>24</v>
       </c>
       <c r="T321" t="n">
         <v>2</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V321" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="W321" t="n">
-        <v>93.64</v>
+        <v>71.8</v>
       </c>
       <c r="X321" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="Y321" t="n">
-        <v>74.64</v>
+        <v>65.8</v>
       </c>
       <c r="Z321" t="n">
-        <v>91.10396570203645</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="AB321" t="n">
-        <v>66.44085461177697</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AC321" t="n">
-        <v>0.475</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AD321" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AE321" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
       <c r="AF321" t="n">
-        <v>24.66311109025948</v>
+        <v>-28.02577257918253</v>
       </c>
       <c r="AG321" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI321" t="b">
@@ -38692,116 +38692,116 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E322" t="n">
         <v>200</v>
       </c>
       <c r="F322" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G322" t="n">
+        <v>13</v>
+      </c>
+      <c r="H322" t="n">
         <v>29</v>
       </c>
-      <c r="H322" t="n">
-        <v>45</v>
-      </c>
       <c r="I322" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J322" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K322" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L322" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M322" t="n">
         <v>9</v>
       </c>
       <c r="N322" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O322" t="n">
+        <v>13</v>
+      </c>
+      <c r="P322" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>10</v>
+      </c>
+      <c r="R322" t="n">
         <v>19</v>
       </c>
-      <c r="P322" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q322" t="n">
-        <v>19</v>
-      </c>
-      <c r="R322" t="n">
-        <v>15</v>
-      </c>
       <c r="S322" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="T322" t="n">
         <v>1</v>
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>2487744</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V322" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="W322" t="n">
-        <v>94.28</v>
+        <v>79.12</v>
       </c>
       <c r="X322" t="n">
-        <v>0.9227831989817564</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="Y322" t="n">
-        <v>85.28</v>
+        <v>70.12</v>
       </c>
       <c r="Z322" t="n">
-        <v>102.0168855534709</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.7312996239030506</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="AB322" t="n">
-        <v>83.61204013377926</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AC322" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AD322" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="AE322" t="n">
-        <v>0.4626865671641791</v>
+        <v>0.5</v>
       </c>
       <c r="AF322" t="n">
-        <v>18.40484541969165</v>
+        <v>28.02577257918253</v>
       </c>
       <c r="AG322" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -38811,116 +38811,116 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="E323" t="n">
         <v>200</v>
       </c>
       <c r="F323" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="G323" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H323" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I323" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J323" t="n">
         <v>24</v>
       </c>
       <c r="K323" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L323" t="n">
+        <v>18</v>
+      </c>
+      <c r="M323" t="n">
+        <v>19</v>
+      </c>
+      <c r="N323" t="n">
         <v>29</v>
       </c>
-      <c r="M323" t="n">
-        <v>14</v>
-      </c>
-      <c r="N323" t="n">
-        <v>21</v>
-      </c>
       <c r="O323" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P323" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q323" t="n">
+        <v>31</v>
+      </c>
+      <c r="R323" t="n">
         <v>19</v>
       </c>
-      <c r="R323" t="n">
-        <v>25</v>
-      </c>
       <c r="S323" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V323" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="W323" t="n">
-        <v>90.75999999999999</v>
+        <v>114.92</v>
       </c>
       <c r="X323" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="Y323" t="n">
-        <v>76.75999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="Z323" t="n">
-        <v>66.44085461177697</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="AB323" t="n">
-        <v>91.10396570203645</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AC323" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.475</v>
       </c>
       <c r="AD323" t="n">
-        <v>0.525</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="AE323" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="AF323" t="n">
-        <v>-24.66311109025948</v>
+        <v>-2.698912865946681</v>
       </c>
       <c r="AG323" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -38934,99 +38934,99 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
           <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
         </is>
       </c>
       <c r="E324" t="n">
         <v>200</v>
       </c>
       <c r="F324" t="n">
+        <v>70</v>
+      </c>
+      <c r="G324" t="n">
+        <v>23</v>
+      </c>
+      <c r="H324" t="n">
+        <v>53</v>
+      </c>
+      <c r="I324" t="n">
+        <v>3</v>
+      </c>
+      <c r="J324" t="n">
+        <v>16</v>
+      </c>
+      <c r="K324" t="n">
+        <v>15</v>
+      </c>
+      <c r="L324" t="n">
+        <v>25</v>
+      </c>
+      <c r="M324" t="n">
+        <v>11</v>
+      </c>
+      <c r="N324" t="n">
+        <v>25</v>
+      </c>
+      <c r="O324" t="n">
+        <v>15</v>
+      </c>
+      <c r="P324" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>12</v>
+      </c>
+      <c r="R324" t="n">
+        <v>20</v>
+      </c>
+      <c r="S324" t="n">
+        <v>18</v>
+      </c>
+      <c r="T324" t="n">
+        <v>3</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
         <v>95</v>
       </c>
-      <c r="G324" t="n">
-        <v>27</v>
-      </c>
-      <c r="H324" t="n">
-        <v>51</v>
-      </c>
-      <c r="I324" t="n">
-        <v>8</v>
-      </c>
-      <c r="J324" t="n">
-        <v>20</v>
-      </c>
-      <c r="K324" t="n">
-        <v>17</v>
-      </c>
-      <c r="L324" t="n">
-        <v>24</v>
-      </c>
-      <c r="M324" t="n">
-        <v>9</v>
-      </c>
-      <c r="N324" t="n">
-        <v>33</v>
-      </c>
-      <c r="O324" t="n">
-        <v>23</v>
-      </c>
-      <c r="P324" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q324" t="n">
-        <v>11</v>
-      </c>
-      <c r="R324" t="n">
-        <v>18</v>
-      </c>
-      <c r="S324" t="n">
-        <v>20</v>
-      </c>
-      <c r="T324" t="n">
-        <v>2</v>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>2487741</t>
-        </is>
-      </c>
-      <c r="V324" t="n">
-        <v>70</v>
-      </c>
       <c r="W324" t="n">
-        <v>92.56</v>
+        <v>92</v>
       </c>
       <c r="X324" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>86.41975308641975</v>
+      </c>
+      <c r="AA324" t="n">
         <v>1.026361279170268</v>
       </c>
-      <c r="Y324" t="n">
-        <v>83.56</v>
-      </c>
-      <c r="Z324" t="n">
+      <c r="AB324" t="n">
         <v>113.6907611297271</v>
       </c>
-      <c r="AA324" t="n">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="AB324" t="n">
-        <v>86.41975308641975</v>
-      </c>
       <c r="AC324" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.25</v>
       </c>
       <c r="AD324" t="n">
-        <v>0.75</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="AE324" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AF324" t="n">
-        <v>27.27100804330739</v>
+        <v>-27.27100804330739</v>
       </c>
       <c r="AG324" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         </is>
       </c>
       <c r="AI324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -39053,22 +39053,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E325" t="n">
         <v>200</v>
       </c>
       <c r="F325" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G325" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H325" t="n">
         <v>41</v>
@@ -39077,88 +39077,88 @@
         <v>4</v>
       </c>
       <c r="J325" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K325" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L325" t="n">
         <v>13</v>
       </c>
       <c r="M325" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N325" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O325" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P325" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q325" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R325" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S325" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>2487744</t>
+          <t>2487742</t>
         </is>
       </c>
       <c r="V325" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="W325" t="n">
-        <v>95.72</v>
+        <v>89.72</v>
       </c>
       <c r="X325" t="n">
-        <v>0.7312996239030506</v>
+        <v>0.7133303611234953</v>
       </c>
       <c r="Y325" t="n">
-        <v>83.72</v>
+        <v>74.72</v>
       </c>
       <c r="Z325" t="n">
-        <v>83.61204013377926</v>
+        <v>85.65310492505354</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.9227831989817564</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="AB325" t="n">
-        <v>102.0168855534709</v>
+        <v>107.2423398328691</v>
       </c>
       <c r="AC325" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="AD325" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5625</v>
       </c>
       <c r="AE325" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="AF325" t="n">
-        <v>-18.40484541969165</v>
+        <v>-21.58923490781554</v>
       </c>
       <c r="AG325" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="AI325" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -39172,108 +39172,108 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="E326" t="n">
         <v>200</v>
       </c>
       <c r="F326" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G326" t="n">
+        <v>20</v>
+      </c>
+      <c r="H326" t="n">
+        <v>45</v>
+      </c>
+      <c r="I326" t="n">
+        <v>8</v>
+      </c>
+      <c r="J326" t="n">
+        <v>26</v>
+      </c>
+      <c r="K326" t="n">
         <v>12</v>
       </c>
-      <c r="H326" t="n">
-        <v>29</v>
-      </c>
-      <c r="I326" t="n">
-        <v>6</v>
-      </c>
-      <c r="J326" t="n">
-        <v>21</v>
-      </c>
-      <c r="K326" t="n">
-        <v>11</v>
-      </c>
       <c r="L326" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M326" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N326" t="n">
         <v>27</v>
       </c>
       <c r="O326" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P326" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q326" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R326" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="S326" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T326" t="n">
         <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>2487743</t>
+          <t>2487738</t>
         </is>
       </c>
       <c r="V326" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="W326" t="n">
-        <v>83.59999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="X326" t="n">
-        <v>0.6339712918660287</v>
+        <v>0.8179078777442962</v>
       </c>
       <c r="Y326" t="n">
-        <v>79.59999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="Z326" t="n">
-        <v>66.58291457286433</v>
+        <v>95.09509509509509</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.9238138686131386</v>
+        <v>0.8848566308243727</v>
       </c>
       <c r="AB326" t="n">
-        <v>101.6566265060241</v>
+        <v>98.40558046836074</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="AD326" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.75</v>
       </c>
       <c r="AE326" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="AF326" t="n">
-        <v>-35.07371193315976</v>
+        <v>-3.310485373265649</v>
       </c>
       <c r="AG326" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI326" t="b">
@@ -39291,112 +39291,112 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E327" t="n">
         <v>200</v>
       </c>
       <c r="F327" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G327" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H327" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I327" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J327" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K327" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L327" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M327" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N327" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O327" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q327" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R327" t="n">
         <v>20</v>
       </c>
       <c r="S327" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T327" t="n">
         <v>3</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487738</t>
         </is>
       </c>
       <c r="V327" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="W327" t="n">
-        <v>85.8</v>
+        <v>89.28</v>
       </c>
       <c r="X327" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8848566308243727</v>
       </c>
       <c r="Y327" t="n">
-        <v>71.8</v>
+        <v>80.28</v>
       </c>
       <c r="Z327" t="n">
-        <v>107.2423398328691</v>
+        <v>98.40558046836074</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.8179078777442962</v>
       </c>
       <c r="AB327" t="n">
-        <v>85.65310492505354</v>
+        <v>95.09509509509509</v>
       </c>
       <c r="AC327" t="n">
-        <v>0.4375</v>
+        <v>0.25</v>
       </c>
       <c r="AD327" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="AE327" t="n">
-        <v>0.547945205479452</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="AF327" t="n">
-        <v>21.58923490781554</v>
+        <v>3.310485373265649</v>
       </c>
       <c r="AG327" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI327" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -39410,108 +39410,108 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E328" t="n">
         <v>200</v>
       </c>
       <c r="F328" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G328" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H328" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I328" t="n">
         <v>9</v>
       </c>
       <c r="J328" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K328" t="n">
+        <v>8</v>
+      </c>
+      <c r="L328" t="n">
         <v>16</v>
       </c>
-      <c r="L328" t="n">
-        <v>22</v>
-      </c>
       <c r="M328" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N328" t="n">
         <v>27</v>
       </c>
       <c r="O328" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P328" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Q328" t="n">
+        <v>9</v>
+      </c>
+      <c r="R328" t="n">
         <v>16</v>
       </c>
-      <c r="R328" t="n">
-        <v>20</v>
-      </c>
       <c r="S328" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T328" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>2487743</t>
+          <t>2487740</t>
         </is>
       </c>
       <c r="V328" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="W328" t="n">
-        <v>87.68000000000001</v>
+        <v>85.03999999999999</v>
       </c>
       <c r="X328" t="n">
-        <v>0.9238138686131386</v>
+        <v>0.8819379115710255</v>
       </c>
       <c r="Y328" t="n">
-        <v>79.68000000000001</v>
+        <v>81.03999999999999</v>
       </c>
       <c r="Z328" t="n">
-        <v>101.6566265060241</v>
+        <v>92.54689042448175</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.6339712918660287</v>
+        <v>0.8535582064993829</v>
       </c>
       <c r="AB328" t="n">
-        <v>66.58291457286433</v>
+        <v>96.24304267161409</v>
       </c>
       <c r="AC328" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.1</v>
       </c>
       <c r="AD328" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="AE328" t="n">
-        <v>0.5303030303030303</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="AF328" t="n">
-        <v>35.07371193315976</v>
+        <v>-3.696152247132346</v>
       </c>
       <c r="AG328" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AI328" t="b">
@@ -39529,25 +39529,25 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E329" t="n">
         <v>200</v>
       </c>
       <c r="F329" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G329" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H329" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I329" t="n">
         <v>9</v>
@@ -39556,85 +39556,2703 @@
         <v>30</v>
       </c>
       <c r="K329" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L329" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M329" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N329" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="O329" t="n">
         <v>10</v>
       </c>
       <c r="P329" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>16</v>
+      </c>
+      <c r="R329" t="n">
+        <v>21</v>
+      </c>
+      <c r="S329" t="n">
+        <v>24</v>
+      </c>
+      <c r="T329" t="n">
+        <v>2</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487739</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>51</v>
+      </c>
+      <c r="W329" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="X329" t="n">
+        <v>0.7261853908586074</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>91.10396570203645</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.5619215513442045</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>66.44085461177697</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>24.66311109025948</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>24</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>200</v>
+      </c>
+      <c r="F330" t="n">
+        <v>87</v>
+      </c>
+      <c r="G330" t="n">
+        <v>29</v>
+      </c>
+      <c r="H330" t="n">
+        <v>45</v>
+      </c>
+      <c r="I330" t="n">
         <v>8</v>
       </c>
-      <c r="Q329" t="n">
+      <c r="J330" t="n">
+        <v>25</v>
+      </c>
+      <c r="K330" t="n">
+        <v>5</v>
+      </c>
+      <c r="L330" t="n">
+        <v>12</v>
+      </c>
+      <c r="M330" t="n">
+        <v>9</v>
+      </c>
+      <c r="N330" t="n">
+        <v>22</v>
+      </c>
+      <c r="O330" t="n">
         <v>19</v>
       </c>
-      <c r="R329" t="n">
+      <c r="P330" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>19</v>
+      </c>
+      <c r="R330" t="n">
         <v>15</v>
       </c>
-      <c r="S329" t="n">
+      <c r="S330" t="n">
+        <v>15</v>
+      </c>
+      <c r="T330" t="n">
+        <v>1</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>70</v>
+      </c>
+      <c r="W330" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>0.4626865671641791</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>18.40484541969165</v>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI330" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>24</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" t="n">
+        <v>51</v>
+      </c>
+      <c r="G331" t="n">
+        <v>12</v>
+      </c>
+      <c r="H331" t="n">
+        <v>35</v>
+      </c>
+      <c r="I331" t="n">
+        <v>2</v>
+      </c>
+      <c r="J331" t="n">
+        <v>24</v>
+      </c>
+      <c r="K331" t="n">
+        <v>21</v>
+      </c>
+      <c r="L331" t="n">
+        <v>29</v>
+      </c>
+      <c r="M331" t="n">
+        <v>14</v>
+      </c>
+      <c r="N331" t="n">
+        <v>21</v>
+      </c>
+      <c r="O331" t="n">
+        <v>7</v>
+      </c>
+      <c r="P331" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>19</v>
+      </c>
+      <c r="R331" t="n">
+        <v>25</v>
+      </c>
+      <c r="S331" t="n">
+        <v>20</v>
+      </c>
+      <c r="T331" t="n">
+        <v>3</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2487739</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>68</v>
+      </c>
+      <c r="W331" t="n">
+        <v>90.75999999999999</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0.5619215513442045</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>76.75999999999999</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>66.44085461177697</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>0.7261853908586074</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>91.10396570203645</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>-24.66311109025948</v>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI331" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>24</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>200</v>
+      </c>
+      <c r="F332" t="n">
+        <v>95</v>
+      </c>
+      <c r="G332" t="n">
+        <v>27</v>
+      </c>
+      <c r="H332" t="n">
+        <v>51</v>
+      </c>
+      <c r="I332" t="n">
+        <v>8</v>
+      </c>
+      <c r="J332" t="n">
+        <v>20</v>
+      </c>
+      <c r="K332" t="n">
+        <v>17</v>
+      </c>
+      <c r="L332" t="n">
+        <v>24</v>
+      </c>
+      <c r="M332" t="n">
+        <v>9</v>
+      </c>
+      <c r="N332" t="n">
+        <v>33</v>
+      </c>
+      <c r="O332" t="n">
+        <v>23</v>
+      </c>
+      <c r="P332" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>11</v>
+      </c>
+      <c r="R332" t="n">
+        <v>18</v>
+      </c>
+      <c r="S332" t="n">
+        <v>20</v>
+      </c>
+      <c r="T332" t="n">
+        <v>2</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>70</v>
+      </c>
+      <c r="W332" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="X332" t="n">
+        <v>1.026361279170268</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>113.6907611297271</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>86.41975308641975</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>27.27100804330739</v>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>24</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>70</v>
+      </c>
+      <c r="G333" t="n">
+        <v>25</v>
+      </c>
+      <c r="H333" t="n">
+        <v>41</v>
+      </c>
+      <c r="I333" t="n">
+        <v>4</v>
+      </c>
+      <c r="J333" t="n">
+        <v>27</v>
+      </c>
+      <c r="K333" t="n">
+        <v>8</v>
+      </c>
+      <c r="L333" t="n">
+        <v>13</v>
+      </c>
+      <c r="M333" t="n">
+        <v>12</v>
+      </c>
+      <c r="N333" t="n">
+        <v>24</v>
+      </c>
+      <c r="O333" t="n">
+        <v>13</v>
+      </c>
+      <c r="P333" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>22</v>
+      </c>
+      <c r="R333" t="n">
+        <v>15</v>
+      </c>
+      <c r="S333" t="n">
+        <v>15</v>
+      </c>
+      <c r="T333" t="n">
+        <v>2</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>87</v>
+      </c>
+      <c r="W333" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>-18.40484541969165</v>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>24</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>200</v>
+      </c>
+      <c r="F334" t="n">
+        <v>53</v>
+      </c>
+      <c r="G334" t="n">
+        <v>12</v>
+      </c>
+      <c r="H334" t="n">
+        <v>29</v>
+      </c>
+      <c r="I334" t="n">
+        <v>6</v>
+      </c>
+      <c r="J334" t="n">
+        <v>21</v>
+      </c>
+      <c r="K334" t="n">
+        <v>11</v>
+      </c>
+      <c r="L334" t="n">
+        <v>15</v>
+      </c>
+      <c r="M334" t="n">
+        <v>4</v>
+      </c>
+      <c r="N334" t="n">
+        <v>27</v>
+      </c>
+      <c r="O334" t="n">
+        <v>13</v>
+      </c>
+      <c r="P334" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>27</v>
+      </c>
+      <c r="R334" t="n">
+        <v>21</v>
+      </c>
+      <c r="S334" t="n">
+        <v>20</v>
+      </c>
+      <c r="T334" t="n">
+        <v>1</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>81</v>
+      </c>
+      <c r="W334" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>0.4696969696969697</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>-35.07371193315976</v>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI334" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>24</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>200</v>
+      </c>
+      <c r="F335" t="n">
+        <v>77</v>
+      </c>
+      <c r="G335" t="n">
+        <v>24</v>
+      </c>
+      <c r="H335" t="n">
+        <v>43</v>
+      </c>
+      <c r="I335" t="n">
+        <v>6</v>
+      </c>
+      <c r="J335" t="n">
+        <v>19</v>
+      </c>
+      <c r="K335" t="n">
+        <v>11</v>
+      </c>
+      <c r="L335" t="n">
+        <v>20</v>
+      </c>
+      <c r="M335" t="n">
+        <v>14</v>
+      </c>
+      <c r="N335" t="n">
+        <v>26</v>
+      </c>
+      <c r="O335" t="n">
+        <v>13</v>
+      </c>
+      <c r="P335" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>15</v>
+      </c>
+      <c r="R335" t="n">
+        <v>20</v>
+      </c>
+      <c r="S335" t="n">
+        <v>20</v>
+      </c>
+      <c r="T335" t="n">
+        <v>3</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2487742</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>64</v>
+      </c>
+      <c r="W335" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>107.2423398328691</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>0.7133303611234953</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>85.65310492505354</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>21.58923490781554</v>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>24</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>200</v>
+      </c>
+      <c r="F336" t="n">
+        <v>81</v>
+      </c>
+      <c r="G336" t="n">
+        <v>19</v>
+      </c>
+      <c r="H336" t="n">
+        <v>39</v>
+      </c>
+      <c r="I336" t="n">
+        <v>9</v>
+      </c>
+      <c r="J336" t="n">
+        <v>23</v>
+      </c>
+      <c r="K336" t="n">
         <v>16</v>
       </c>
-      <c r="T329" t="n">
+      <c r="L336" t="n">
+        <v>22</v>
+      </c>
+      <c r="M336" t="n">
+        <v>8</v>
+      </c>
+      <c r="N336" t="n">
+        <v>27</v>
+      </c>
+      <c r="O336" t="n">
+        <v>24</v>
+      </c>
+      <c r="P336" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>16</v>
+      </c>
+      <c r="R336" t="n">
+        <v>20</v>
+      </c>
+      <c r="S336" t="n">
+        <v>21</v>
+      </c>
+      <c r="T336" t="n">
+        <v>0</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>53</v>
+      </c>
+      <c r="W336" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="X336" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>35.07371193315976</v>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI336" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>24</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>200</v>
+      </c>
+      <c r="F337" t="n">
+        <v>83</v>
+      </c>
+      <c r="G337" t="n">
+        <v>21</v>
+      </c>
+      <c r="H337" t="n">
+        <v>39</v>
+      </c>
+      <c r="I337" t="n">
+        <v>9</v>
+      </c>
+      <c r="J337" t="n">
+        <v>30</v>
+      </c>
+      <c r="K337" t="n">
+        <v>14</v>
+      </c>
+      <c r="L337" t="n">
+        <v>21</v>
+      </c>
+      <c r="M337" t="n">
+        <v>11</v>
+      </c>
+      <c r="N337" t="n">
+        <v>36</v>
+      </c>
+      <c r="O337" t="n">
+        <v>10</v>
+      </c>
+      <c r="P337" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>19</v>
+      </c>
+      <c r="R337" t="n">
+        <v>15</v>
+      </c>
+      <c r="S337" t="n">
+        <v>16</v>
+      </c>
+      <c r="T337" t="n">
         <v>3</v>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="U337" t="inlineStr">
         <is>
           <t>2487740</t>
         </is>
       </c>
-      <c r="V329" t="n">
+      <c r="V337" t="n">
         <v>75</v>
       </c>
-      <c r="W329" t="n">
+      <c r="W337" t="n">
         <v>97.24000000000001</v>
       </c>
-      <c r="X329" t="n">
+      <c r="X337" t="n">
         <v>0.8535582064993829</v>
       </c>
-      <c r="Y329" t="n">
+      <c r="Y337" t="n">
         <v>86.24000000000001</v>
       </c>
-      <c r="Z329" t="n">
+      <c r="Z337" t="n">
         <v>96.24304267161409</v>
       </c>
-      <c r="AA329" t="n">
+      <c r="AA337" t="n">
         <v>0.8819379115710255</v>
       </c>
-      <c r="AB329" t="n">
+      <c r="AB337" t="n">
         <v>92.54689042448175</v>
       </c>
-      <c r="AC329" t="n">
+      <c r="AC337" t="n">
         <v>0.2894736842105263</v>
       </c>
-      <c r="AD329" t="n">
+      <c r="AD337" t="n">
         <v>0.9</v>
       </c>
-      <c r="AE329" t="n">
+      <c r="AE337" t="n">
         <v>0.6025641025641025</v>
       </c>
-      <c r="AF329" t="n">
+      <c r="AF337" t="n">
         <v>3.696152247132346</v>
       </c>
-      <c r="AG329" t="inlineStr">
+      <c r="AG337" t="inlineStr">
         <is>
           <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
-      <c r="AH329" t="inlineStr">
+      <c r="AH337" t="inlineStr">
         <is>
           <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
-      <c r="AI329" t="b">
+      <c r="AI337" t="b">
         <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>25</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>200</v>
+      </c>
+      <c r="F338" t="n">
+        <v>80</v>
+      </c>
+      <c r="G338" t="n">
+        <v>20</v>
+      </c>
+      <c r="H338" t="n">
+        <v>35</v>
+      </c>
+      <c r="I338" t="n">
+        <v>8</v>
+      </c>
+      <c r="J338" t="n">
+        <v>34</v>
+      </c>
+      <c r="K338" t="n">
+        <v>16</v>
+      </c>
+      <c r="L338" t="n">
+        <v>24</v>
+      </c>
+      <c r="M338" t="n">
+        <v>8</v>
+      </c>
+      <c r="N338" t="n">
+        <v>22</v>
+      </c>
+      <c r="O338" t="n">
+        <v>21</v>
+      </c>
+      <c r="P338" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>8</v>
+      </c>
+      <c r="R338" t="n">
+        <v>26</v>
+      </c>
+      <c r="S338" t="n">
+        <v>25</v>
+      </c>
+      <c r="T338" t="n">
+        <v>2</v>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>70</v>
+      </c>
+      <c r="W338" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="X338" t="n">
+        <v>0.9136592051164916</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>100.5530417295123</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>13.05304172951232</v>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AI338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>25</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>200</v>
+      </c>
+      <c r="F339" t="n">
+        <v>61</v>
+      </c>
+      <c r="G339" t="n">
+        <v>13</v>
+      </c>
+      <c r="H339" t="n">
+        <v>39</v>
+      </c>
+      <c r="I339" t="n">
+        <v>7</v>
+      </c>
+      <c r="J339" t="n">
+        <v>25</v>
+      </c>
+      <c r="K339" t="n">
+        <v>14</v>
+      </c>
+      <c r="L339" t="n">
+        <v>23</v>
+      </c>
+      <c r="M339" t="n">
+        <v>13</v>
+      </c>
+      <c r="N339" t="n">
+        <v>20</v>
+      </c>
+      <c r="O339" t="n">
+        <v>10</v>
+      </c>
+      <c r="P339" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>23</v>
+      </c>
+      <c r="R339" t="n">
+        <v>18</v>
+      </c>
+      <c r="S339" t="n">
+        <v>18</v>
+      </c>
+      <c r="T339" t="n">
+        <v>2</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>2487747</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>91</v>
+      </c>
+      <c r="W339" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="X339" t="n">
+        <v>0.6280889621087314</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>72.51545411317166</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>1.028481012658228</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>111.6838487972509</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>-39.1683946840792</v>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AI339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>25</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>200</v>
+      </c>
+      <c r="F340" t="n">
+        <v>74</v>
+      </c>
+      <c r="G340" t="n">
+        <v>18</v>
+      </c>
+      <c r="H340" t="n">
+        <v>40</v>
+      </c>
+      <c r="I340" t="n">
+        <v>9</v>
+      </c>
+      <c r="J340" t="n">
+        <v>29</v>
+      </c>
+      <c r="K340" t="n">
+        <v>11</v>
+      </c>
+      <c r="L340" t="n">
+        <v>21</v>
+      </c>
+      <c r="M340" t="n">
+        <v>18</v>
+      </c>
+      <c r="N340" t="n">
+        <v>23</v>
+      </c>
+      <c r="O340" t="n">
+        <v>18</v>
+      </c>
+      <c r="P340" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>18</v>
+      </c>
+      <c r="R340" t="n">
+        <v>19</v>
+      </c>
+      <c r="S340" t="n">
+        <v>19</v>
+      </c>
+      <c r="T340" t="n">
+        <v>1</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>2487745</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>107</v>
+      </c>
+      <c r="W340" t="n">
+        <v>96.24000000000001</v>
+      </c>
+      <c r="X340" t="n">
+        <v>0.768911055694098</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>78.24000000000001</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>94.5807770961145</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>1.156006914433881</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>132.8202581926514</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>0.5189873417721519</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>-38.23948109653693</v>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI340" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>25</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>200</v>
+      </c>
+      <c r="F341" t="n">
+        <v>74</v>
+      </c>
+      <c r="G341" t="n">
+        <v>23</v>
+      </c>
+      <c r="H341" t="n">
+        <v>44</v>
+      </c>
+      <c r="I341" t="n">
+        <v>4</v>
+      </c>
+      <c r="J341" t="n">
+        <v>24</v>
+      </c>
+      <c r="K341" t="n">
+        <v>16</v>
+      </c>
+      <c r="L341" t="n">
+        <v>26</v>
+      </c>
+      <c r="M341" t="n">
+        <v>11</v>
+      </c>
+      <c r="N341" t="n">
+        <v>26</v>
+      </c>
+      <c r="O341" t="n">
+        <v>12</v>
+      </c>
+      <c r="P341" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>16</v>
+      </c>
+      <c r="R341" t="n">
+        <v>20</v>
+      </c>
+      <c r="S341" t="n">
+        <v>23</v>
+      </c>
+      <c r="T341" t="n">
+        <v>1</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>82</v>
+      </c>
+      <c r="W341" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="X341" t="n">
+        <v>0.7753562447611064</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>87.63619137849361</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>0.8570234113712374</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>99.17755200774067</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>0.4567901234567901</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>-11.54136062924707</v>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AI341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>25</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>200</v>
+      </c>
+      <c r="F342" t="n">
+        <v>70</v>
+      </c>
+      <c r="G342" t="n">
+        <v>20</v>
+      </c>
+      <c r="H342" t="n">
+        <v>32</v>
+      </c>
+      <c r="I342" t="n">
+        <v>5</v>
+      </c>
+      <c r="J342" t="n">
+        <v>21</v>
+      </c>
+      <c r="K342" t="n">
+        <v>15</v>
+      </c>
+      <c r="L342" t="n">
+        <v>25</v>
+      </c>
+      <c r="M342" t="n">
+        <v>6</v>
+      </c>
+      <c r="N342" t="n">
+        <v>33</v>
+      </c>
+      <c r="O342" t="n">
+        <v>13</v>
+      </c>
+      <c r="P342" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>22</v>
+      </c>
+      <c r="R342" t="n">
+        <v>27</v>
+      </c>
+      <c r="S342" t="n">
+        <v>24</v>
+      </c>
+      <c r="T342" t="n">
+        <v>2</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>80</v>
+      </c>
+      <c r="W342" t="n">
+        <v>86</v>
+      </c>
+      <c r="X342" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>0.9136592051164916</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>100.5530417295123</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>0.8048780487804879</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>-13.05304172951232</v>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AI342" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>25</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>225</v>
+      </c>
+      <c r="F343" t="n">
+        <v>69</v>
+      </c>
+      <c r="G343" t="n">
+        <v>16</v>
+      </c>
+      <c r="H343" t="n">
+        <v>43</v>
+      </c>
+      <c r="I343" t="n">
+        <v>10</v>
+      </c>
+      <c r="J343" t="n">
+        <v>34</v>
+      </c>
+      <c r="K343" t="n">
+        <v>7</v>
+      </c>
+      <c r="L343" t="n">
+        <v>14</v>
+      </c>
+      <c r="M343" t="n">
+        <v>16</v>
+      </c>
+      <c r="N343" t="n">
+        <v>37</v>
+      </c>
+      <c r="O343" t="n">
+        <v>15</v>
+      </c>
+      <c r="P343" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>18</v>
+      </c>
+      <c r="R343" t="n">
+        <v>25</v>
+      </c>
+      <c r="S343" t="n">
+        <v>20</v>
+      </c>
+      <c r="T343" t="n">
+        <v>7</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>71</v>
+      </c>
+      <c r="W343" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="X343" t="n">
+        <v>0.6820877817319099</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>81.0239549084077</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>0.6501831501831502</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>77.85087719298245</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>0.5047619047619047</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>3.173077715425251</v>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AI343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>25</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>200</v>
+      </c>
+      <c r="F344" t="n">
+        <v>107</v>
+      </c>
+      <c r="G344" t="n">
+        <v>26</v>
+      </c>
+      <c r="H344" t="n">
+        <v>38</v>
+      </c>
+      <c r="I344" t="n">
+        <v>14</v>
+      </c>
+      <c r="J344" t="n">
+        <v>36</v>
+      </c>
+      <c r="K344" t="n">
+        <v>13</v>
+      </c>
+      <c r="L344" t="n">
+        <v>24</v>
+      </c>
+      <c r="M344" t="n">
+        <v>12</v>
+      </c>
+      <c r="N344" t="n">
+        <v>26</v>
+      </c>
+      <c r="O344" t="n">
+        <v>28</v>
+      </c>
+      <c r="P344" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>8</v>
+      </c>
+      <c r="R344" t="n">
+        <v>21</v>
+      </c>
+      <c r="S344" t="n">
+        <v>19</v>
+      </c>
+      <c r="T344" t="n">
+        <v>5</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>2487745</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>74</v>
+      </c>
+      <c r="W344" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="X344" t="n">
+        <v>1.156006914433881</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>132.8202581926514</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>0.768911055694098</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>94.5807770961145</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>0.4810126582278481</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>38.23948109653693</v>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>25</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>200</v>
+      </c>
+      <c r="F345" t="n">
+        <v>82</v>
+      </c>
+      <c r="G345" t="n">
+        <v>19</v>
+      </c>
+      <c r="H345" t="n">
+        <v>44</v>
+      </c>
+      <c r="I345" t="n">
+        <v>10</v>
+      </c>
+      <c r="J345" t="n">
+        <v>28</v>
+      </c>
+      <c r="K345" t="n">
+        <v>14</v>
+      </c>
+      <c r="L345" t="n">
+        <v>22</v>
+      </c>
+      <c r="M345" t="n">
+        <v>13</v>
+      </c>
+      <c r="N345" t="n">
+        <v>31</v>
+      </c>
+      <c r="O345" t="n">
+        <v>14</v>
+      </c>
+      <c r="P345" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>14</v>
+      </c>
+      <c r="R345" t="n">
+        <v>24</v>
+      </c>
+      <c r="S345" t="n">
+        <v>20</v>
+      </c>
+      <c r="T345" t="n">
+        <v>4</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>74</v>
+      </c>
+      <c r="W345" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="X345" t="n">
+        <v>0.8570234113712374</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>99.17755200774067</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>0.7753562447611064</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>87.63619137849361</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD345" t="n">
+        <v>0.7380952380952381</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>0.5432098765432098</v>
+      </c>
+      <c r="AF345" t="n">
+        <v>11.54136062924707</v>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AI345" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>25</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>200</v>
+      </c>
+      <c r="F346" t="n">
+        <v>51</v>
+      </c>
+      <c r="G346" t="n">
+        <v>13</v>
+      </c>
+      <c r="H346" t="n">
+        <v>41</v>
+      </c>
+      <c r="I346" t="n">
+        <v>4</v>
+      </c>
+      <c r="J346" t="n">
+        <v>26</v>
+      </c>
+      <c r="K346" t="n">
+        <v>13</v>
+      </c>
+      <c r="L346" t="n">
+        <v>30</v>
+      </c>
+      <c r="M346" t="n">
+        <v>13</v>
+      </c>
+      <c r="N346" t="n">
+        <v>21</v>
+      </c>
+      <c r="O346" t="n">
+        <v>9</v>
+      </c>
+      <c r="P346" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>10</v>
+      </c>
+      <c r="R346" t="n">
+        <v>24</v>
+      </c>
+      <c r="S346" t="n">
+        <v>25</v>
+      </c>
+      <c r="T346" t="n">
+        <v>1</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>62</v>
+      </c>
+      <c r="W346" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="X346" t="n">
+        <v>0.565410199556541</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>66.06217616580311</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>0.6837229819144243</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>81.92389006342493</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>0.2549019607843137</v>
+      </c>
+      <c r="AD346" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>0.3908045977011494</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>-15.86171389762183</v>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AI346" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>25</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>200</v>
+      </c>
+      <c r="F347" t="n">
+        <v>63</v>
+      </c>
+      <c r="G347" t="n">
+        <v>14</v>
+      </c>
+      <c r="H347" t="n">
+        <v>36</v>
+      </c>
+      <c r="I347" t="n">
+        <v>8</v>
+      </c>
+      <c r="J347" t="n">
+        <v>26</v>
+      </c>
+      <c r="K347" t="n">
+        <v>11</v>
+      </c>
+      <c r="L347" t="n">
+        <v>14</v>
+      </c>
+      <c r="M347" t="n">
+        <v>7</v>
+      </c>
+      <c r="N347" t="n">
+        <v>26</v>
+      </c>
+      <c r="O347" t="n">
+        <v>10</v>
+      </c>
+      <c r="P347" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>19</v>
+      </c>
+      <c r="R347" t="n">
+        <v>23</v>
+      </c>
+      <c r="S347" t="n">
+        <v>19</v>
+      </c>
+      <c r="T347" t="n">
+        <v>2</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>70</v>
+      </c>
+      <c r="W347" t="n">
+        <v>87.16</v>
+      </c>
+      <c r="X347" t="n">
+        <v>0.7228086278109225</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>78.59281437125749</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>0.8549096238397655</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>91.05098855359002</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>-12.45817418233253</v>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AI347" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>25</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>200</v>
+      </c>
+      <c r="F348" t="n">
+        <v>91</v>
+      </c>
+      <c r="G348" t="n">
+        <v>27</v>
+      </c>
+      <c r="H348" t="n">
+        <v>43</v>
+      </c>
+      <c r="I348" t="n">
+        <v>9</v>
+      </c>
+      <c r="J348" t="n">
+        <v>23</v>
+      </c>
+      <c r="K348" t="n">
+        <v>10</v>
+      </c>
+      <c r="L348" t="n">
+        <v>17</v>
+      </c>
+      <c r="M348" t="n">
+        <v>7</v>
+      </c>
+      <c r="N348" t="n">
+        <v>29</v>
+      </c>
+      <c r="O348" t="n">
+        <v>29</v>
+      </c>
+      <c r="P348" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>15</v>
+      </c>
+      <c r="R348" t="n">
+        <v>18</v>
+      </c>
+      <c r="S348" t="n">
+        <v>18</v>
+      </c>
+      <c r="T348" t="n">
+        <v>4</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>2487747</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>61</v>
+      </c>
+      <c r="W348" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="X348" t="n">
+        <v>1.028481012658228</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>111.6838487972509</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>0.6280889621087314</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>72.51545411317166</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>0.6904761904761905</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>39.1683946840792</v>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AI348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>25</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>200</v>
+      </c>
+      <c r="F349" t="n">
+        <v>62</v>
+      </c>
+      <c r="G349" t="n">
+        <v>20</v>
+      </c>
+      <c r="H349" t="n">
+        <v>37</v>
+      </c>
+      <c r="I349" t="n">
+        <v>3</v>
+      </c>
+      <c r="J349" t="n">
+        <v>27</v>
+      </c>
+      <c r="K349" t="n">
+        <v>13</v>
+      </c>
+      <c r="L349" t="n">
+        <v>22</v>
+      </c>
+      <c r="M349" t="n">
+        <v>15</v>
+      </c>
+      <c r="N349" t="n">
+        <v>38</v>
+      </c>
+      <c r="O349" t="n">
+        <v>11</v>
+      </c>
+      <c r="P349" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>17</v>
+      </c>
+      <c r="R349" t="n">
+        <v>25</v>
+      </c>
+      <c r="S349" t="n">
+        <v>23</v>
+      </c>
+      <c r="T349" t="n">
+        <v>2</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>51</v>
+      </c>
+      <c r="W349" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="X349" t="n">
+        <v>0.6837229819144243</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>81.92389006342493</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>0.565410199556541</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>66.06217616580311</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>0.7450980392156863</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>0.6091954022988506</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>15.86171389762183</v>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AI349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>25</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>200</v>
+      </c>
+      <c r="F350" t="n">
+        <v>70</v>
+      </c>
+      <c r="G350" t="n">
+        <v>15</v>
+      </c>
+      <c r="H350" t="n">
+        <v>35</v>
+      </c>
+      <c r="I350" t="n">
+        <v>6</v>
+      </c>
+      <c r="J350" t="n">
+        <v>22</v>
+      </c>
+      <c r="K350" t="n">
+        <v>22</v>
+      </c>
+      <c r="L350" t="n">
+        <v>27</v>
+      </c>
+      <c r="M350" t="n">
+        <v>5</v>
+      </c>
+      <c r="N350" t="n">
+        <v>21</v>
+      </c>
+      <c r="O350" t="n">
+        <v>8</v>
+      </c>
+      <c r="P350" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>13</v>
+      </c>
+      <c r="R350" t="n">
+        <v>19</v>
+      </c>
+      <c r="S350" t="n">
+        <v>23</v>
+      </c>
+      <c r="T350" t="n">
+        <v>2</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>63</v>
+      </c>
+      <c r="W350" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="X350" t="n">
+        <v>0.8549096238397655</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>91.05098855359002</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>0.7228086278109225</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>78.59281437125749</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>0.4406779661016949</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>12.45817418233253</v>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AI350" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>25</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>225</v>
+      </c>
+      <c r="F351" t="n">
+        <v>71</v>
+      </c>
+      <c r="G351" t="n">
+        <v>15</v>
+      </c>
+      <c r="H351" t="n">
+        <v>48</v>
+      </c>
+      <c r="I351" t="n">
+        <v>6</v>
+      </c>
+      <c r="J351" t="n">
+        <v>31</v>
+      </c>
+      <c r="K351" t="n">
+        <v>23</v>
+      </c>
+      <c r="L351" t="n">
+        <v>30</v>
+      </c>
+      <c r="M351" t="n">
+        <v>18</v>
+      </c>
+      <c r="N351" t="n">
+        <v>34</v>
+      </c>
+      <c r="O351" t="n">
+        <v>13</v>
+      </c>
+      <c r="P351" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>17</v>
+      </c>
+      <c r="R351" t="n">
+        <v>20</v>
+      </c>
+      <c r="S351" t="n">
+        <v>25</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>69</v>
+      </c>
+      <c r="W351" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="X351" t="n">
+        <v>0.6501831501831502</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>77.85087719298245</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>0.6820877817319099</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>81.0239549084077</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>0.3272727272727273</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>0.4952380952380953</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>-3.173077715425251</v>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AI351" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI351"/>
+  <dimension ref="A1:AI365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42253,6 +42253,1672 @@
       </c>
       <c r="AI351" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>26</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>200</v>
+      </c>
+      <c r="F352" t="n">
+        <v>79</v>
+      </c>
+      <c r="G352" t="n">
+        <v>19</v>
+      </c>
+      <c r="H352" t="n">
+        <v>36</v>
+      </c>
+      <c r="I352" t="n">
+        <v>7</v>
+      </c>
+      <c r="J352" t="n">
+        <v>20</v>
+      </c>
+      <c r="K352" t="n">
+        <v>20</v>
+      </c>
+      <c r="L352" t="n">
+        <v>33</v>
+      </c>
+      <c r="M352" t="n">
+        <v>4</v>
+      </c>
+      <c r="N352" t="n">
+        <v>29</v>
+      </c>
+      <c r="O352" t="n">
+        <v>14</v>
+      </c>
+      <c r="P352" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>21</v>
+      </c>
+      <c r="R352" t="n">
+        <v>23</v>
+      </c>
+      <c r="S352" t="n">
+        <v>23</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>82</v>
+      </c>
+      <c r="W352" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="X352" t="n">
+        <v>0.8631993006993007</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>90.26508226691043</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>0.8979413053000439</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>98.41574651944312</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>-8.150664252532692</v>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI352" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>26</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>200</v>
+      </c>
+      <c r="F353" t="n">
+        <v>71</v>
+      </c>
+      <c r="G353" t="n">
+        <v>19</v>
+      </c>
+      <c r="H353" t="n">
+        <v>42</v>
+      </c>
+      <c r="I353" t="n">
+        <v>7</v>
+      </c>
+      <c r="J353" t="n">
+        <v>31</v>
+      </c>
+      <c r="K353" t="n">
+        <v>12</v>
+      </c>
+      <c r="L353" t="n">
+        <v>16</v>
+      </c>
+      <c r="M353" t="n">
+        <v>8</v>
+      </c>
+      <c r="N353" t="n">
+        <v>26</v>
+      </c>
+      <c r="O353" t="n">
+        <v>16</v>
+      </c>
+      <c r="P353" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>6</v>
+      </c>
+      <c r="R353" t="n">
+        <v>17</v>
+      </c>
+      <c r="S353" t="n">
+        <v>20</v>
+      </c>
+      <c r="T353" t="n">
+        <v>0</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>2487757</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>81</v>
+      </c>
+      <c r="W353" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X353" t="n">
+        <v>0.8251975825197583</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>78.03999999999999</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>90.97898513582778</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>101.9124308002013</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>-10.93344566437352</v>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>26</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>200</v>
+      </c>
+      <c r="F354" t="n">
+        <v>86</v>
+      </c>
+      <c r="G354" t="n">
+        <v>22</v>
+      </c>
+      <c r="H354" t="n">
+        <v>40</v>
+      </c>
+      <c r="I354" t="n">
+        <v>7</v>
+      </c>
+      <c r="J354" t="n">
+        <v>28</v>
+      </c>
+      <c r="K354" t="n">
+        <v>21</v>
+      </c>
+      <c r="L354" t="n">
+        <v>36</v>
+      </c>
+      <c r="M354" t="n">
+        <v>14</v>
+      </c>
+      <c r="N354" t="n">
+        <v>24</v>
+      </c>
+      <c r="O354" t="n">
+        <v>12</v>
+      </c>
+      <c r="P354" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>17</v>
+      </c>
+      <c r="R354" t="n">
+        <v>21</v>
+      </c>
+      <c r="S354" t="n">
+        <v>26</v>
+      </c>
+      <c r="T354" t="n">
+        <v>0</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>94</v>
+      </c>
+      <c r="W354" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="X354" t="n">
+        <v>0.852836176120587</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>99.03270382312299</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>1.026649191786806</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>119.6537678207739</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>0.6486486486486487</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>-20.62106399765094</v>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AI354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>26</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>200</v>
+      </c>
+      <c r="F355" t="n">
+        <v>82</v>
+      </c>
+      <c r="G355" t="n">
+        <v>18</v>
+      </c>
+      <c r="H355" t="n">
+        <v>35</v>
+      </c>
+      <c r="I355" t="n">
+        <v>7</v>
+      </c>
+      <c r="J355" t="n">
+        <v>23</v>
+      </c>
+      <c r="K355" t="n">
+        <v>25</v>
+      </c>
+      <c r="L355" t="n">
+        <v>28</v>
+      </c>
+      <c r="M355" t="n">
+        <v>5</v>
+      </c>
+      <c r="N355" t="n">
+        <v>22</v>
+      </c>
+      <c r="O355" t="n">
+        <v>12</v>
+      </c>
+      <c r="P355" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>24</v>
+      </c>
+      <c r="R355" t="n">
+        <v>28</v>
+      </c>
+      <c r="S355" t="n">
+        <v>26</v>
+      </c>
+      <c r="T355" t="n">
+        <v>2</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>2487753</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>102</v>
+      </c>
+      <c r="W355" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="X355" t="n">
+        <v>0.8693808312128923</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>91.80474697716078</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>1.043371522094926</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>121.7765042979943</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>0.3970588235294117</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>-29.9717573208335</v>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AI355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>26</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>200</v>
+      </c>
+      <c r="F356" t="n">
+        <v>65</v>
+      </c>
+      <c r="G356" t="n">
+        <v>14</v>
+      </c>
+      <c r="H356" t="n">
+        <v>28</v>
+      </c>
+      <c r="I356" t="n">
+        <v>11</v>
+      </c>
+      <c r="J356" t="n">
+        <v>34</v>
+      </c>
+      <c r="K356" t="n">
+        <v>4</v>
+      </c>
+      <c r="L356" t="n">
+        <v>13</v>
+      </c>
+      <c r="M356" t="n">
+        <v>10</v>
+      </c>
+      <c r="N356" t="n">
+        <v>27</v>
+      </c>
+      <c r="O356" t="n">
+        <v>12</v>
+      </c>
+      <c r="P356" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>12</v>
+      </c>
+      <c r="R356" t="n">
+        <v>18</v>
+      </c>
+      <c r="S356" t="n">
+        <v>15</v>
+      </c>
+      <c r="T356" t="n">
+        <v>5</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>2487755</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>47</v>
+      </c>
+      <c r="W356" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="X356" t="n">
+        <v>0.8153537380832915</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>93.23006310958118</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>0.5831265508684864</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>67.52873563218391</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>0.7105263157894737</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>0.4805194805194805</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>25.70132747739727</v>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AI356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>26</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>200</v>
+      </c>
+      <c r="F357" t="n">
+        <v>82</v>
+      </c>
+      <c r="G357" t="n">
+        <v>19</v>
+      </c>
+      <c r="H357" t="n">
+        <v>43</v>
+      </c>
+      <c r="I357" t="n">
+        <v>9</v>
+      </c>
+      <c r="J357" t="n">
+        <v>25</v>
+      </c>
+      <c r="K357" t="n">
+        <v>17</v>
+      </c>
+      <c r="L357" t="n">
+        <v>28</v>
+      </c>
+      <c r="M357" t="n">
+        <v>8</v>
+      </c>
+      <c r="N357" t="n">
+        <v>25</v>
+      </c>
+      <c r="O357" t="n">
+        <v>16</v>
+      </c>
+      <c r="P357" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>11</v>
+      </c>
+      <c r="R357" t="n">
+        <v>23</v>
+      </c>
+      <c r="S357" t="n">
+        <v>22</v>
+      </c>
+      <c r="T357" t="n">
+        <v>5</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>79</v>
+      </c>
+      <c r="W357" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="X357" t="n">
+        <v>0.8979413053000439</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>98.41574651944312</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>0.8631993006993007</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>90.26508226691043</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>8.150664252532692</v>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>26</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>200</v>
+      </c>
+      <c r="F358" t="n">
+        <v>77</v>
+      </c>
+      <c r="G358" t="n">
+        <v>17</v>
+      </c>
+      <c r="H358" t="n">
+        <v>38</v>
+      </c>
+      <c r="I358" t="n">
+        <v>6</v>
+      </c>
+      <c r="J358" t="n">
+        <v>27</v>
+      </c>
+      <c r="K358" t="n">
+        <v>25</v>
+      </c>
+      <c r="L358" t="n">
+        <v>36</v>
+      </c>
+      <c r="M358" t="n">
+        <v>18</v>
+      </c>
+      <c r="N358" t="n">
+        <v>34</v>
+      </c>
+      <c r="O358" t="n">
+        <v>10</v>
+      </c>
+      <c r="P358" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>15</v>
+      </c>
+      <c r="R358" t="n">
+        <v>16</v>
+      </c>
+      <c r="S358" t="n">
+        <v>25</v>
+      </c>
+      <c r="T358" t="n">
+        <v>1</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>74</v>
+      </c>
+      <c r="W358" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="X358" t="n">
+        <v>0.8034223706176962</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>98.92086330935251</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>0.780261493040911</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>96.30400832899531</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>2.616854980357203</v>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI358" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>26</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>200</v>
+      </c>
+      <c r="F359" t="n">
+        <v>94</v>
+      </c>
+      <c r="G359" t="n">
+        <v>19</v>
+      </c>
+      <c r="H359" t="n">
+        <v>37</v>
+      </c>
+      <c r="I359" t="n">
+        <v>12</v>
+      </c>
+      <c r="J359" t="n">
+        <v>32</v>
+      </c>
+      <c r="K359" t="n">
+        <v>20</v>
+      </c>
+      <c r="L359" t="n">
+        <v>24</v>
+      </c>
+      <c r="M359" t="n">
+        <v>13</v>
+      </c>
+      <c r="N359" t="n">
+        <v>22</v>
+      </c>
+      <c r="O359" t="n">
+        <v>13</v>
+      </c>
+      <c r="P359" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>12</v>
+      </c>
+      <c r="R359" t="n">
+        <v>32</v>
+      </c>
+      <c r="S359" t="n">
+        <v>19</v>
+      </c>
+      <c r="T359" t="n">
+        <v>0</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>86</v>
+      </c>
+      <c r="W359" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="X359" t="n">
+        <v>1.026649191786806</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>119.6537678207739</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>0.852836176120587</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>99.03270382312299</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>0.4794520547945205</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>20.62106399765094</v>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AI359" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>26</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>200</v>
+      </c>
+      <c r="F360" t="n">
+        <v>75</v>
+      </c>
+      <c r="G360" t="n">
+        <v>18</v>
+      </c>
+      <c r="H360" t="n">
+        <v>40</v>
+      </c>
+      <c r="I360" t="n">
+        <v>7</v>
+      </c>
+      <c r="J360" t="n">
+        <v>21</v>
+      </c>
+      <c r="K360" t="n">
+        <v>18</v>
+      </c>
+      <c r="L360" t="n">
+        <v>24</v>
+      </c>
+      <c r="M360" t="n">
+        <v>7</v>
+      </c>
+      <c r="N360" t="n">
+        <v>23</v>
+      </c>
+      <c r="O360" t="n">
+        <v>17</v>
+      </c>
+      <c r="P360" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>17</v>
+      </c>
+      <c r="R360" t="n">
+        <v>23</v>
+      </c>
+      <c r="S360" t="n">
+        <v>20</v>
+      </c>
+      <c r="T360" t="n">
+        <v>3</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>76</v>
+      </c>
+      <c r="W360" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="X360" t="n">
+        <v>0.8468834688346883</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>91.95684158901422</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>0.7923269391159299</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>91.65460684997588</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>0.3022347390383402</v>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI360" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>26</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>200</v>
+      </c>
+      <c r="F361" t="n">
+        <v>81</v>
+      </c>
+      <c r="G361" t="n">
+        <v>24</v>
+      </c>
+      <c r="H361" t="n">
+        <v>46</v>
+      </c>
+      <c r="I361" t="n">
+        <v>8</v>
+      </c>
+      <c r="J361" t="n">
+        <v>21</v>
+      </c>
+      <c r="K361" t="n">
+        <v>9</v>
+      </c>
+      <c r="L361" t="n">
+        <v>17</v>
+      </c>
+      <c r="M361" t="n">
+        <v>8</v>
+      </c>
+      <c r="N361" t="n">
+        <v>34</v>
+      </c>
+      <c r="O361" t="n">
+        <v>15</v>
+      </c>
+      <c r="P361" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>13</v>
+      </c>
+      <c r="R361" t="n">
+        <v>20</v>
+      </c>
+      <c r="S361" t="n">
+        <v>17</v>
+      </c>
+      <c r="T361" t="n">
+        <v>3</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>2487757</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>71</v>
+      </c>
+      <c r="W361" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="X361" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>101.9124308002013</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>0.8251975825197583</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>90.97898513582778</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>0.5526315789473685</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>10.93344566437352</v>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI361" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>26</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>200</v>
+      </c>
+      <c r="F362" t="n">
+        <v>76</v>
+      </c>
+      <c r="G362" t="n">
+        <v>19</v>
+      </c>
+      <c r="H362" t="n">
+        <v>37</v>
+      </c>
+      <c r="I362" t="n">
+        <v>9</v>
+      </c>
+      <c r="J362" t="n">
+        <v>33</v>
+      </c>
+      <c r="K362" t="n">
+        <v>11</v>
+      </c>
+      <c r="L362" t="n">
+        <v>18</v>
+      </c>
+      <c r="M362" t="n">
+        <v>13</v>
+      </c>
+      <c r="N362" t="n">
+        <v>31</v>
+      </c>
+      <c r="O362" t="n">
+        <v>17</v>
+      </c>
+      <c r="P362" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>18</v>
+      </c>
+      <c r="R362" t="n">
+        <v>21</v>
+      </c>
+      <c r="S362" t="n">
+        <v>22</v>
+      </c>
+      <c r="T362" t="n">
+        <v>2</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>75</v>
+      </c>
+      <c r="W362" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="X362" t="n">
+        <v>0.7923269391159299</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>91.65460684997588</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>0.8468834688346883</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>91.95684158901422</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>-0.3022347390383402</v>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI362" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>26</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>200</v>
+      </c>
+      <c r="F363" t="n">
+        <v>47</v>
+      </c>
+      <c r="G363" t="n">
+        <v>15</v>
+      </c>
+      <c r="H363" t="n">
+        <v>36</v>
+      </c>
+      <c r="I363" t="n">
+        <v>3</v>
+      </c>
+      <c r="J363" t="n">
+        <v>21</v>
+      </c>
+      <c r="K363" t="n">
+        <v>8</v>
+      </c>
+      <c r="L363" t="n">
+        <v>15</v>
+      </c>
+      <c r="M363" t="n">
+        <v>11</v>
+      </c>
+      <c r="N363" t="n">
+        <v>29</v>
+      </c>
+      <c r="O363" t="n">
+        <v>7</v>
+      </c>
+      <c r="P363" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>17</v>
+      </c>
+      <c r="R363" t="n">
+        <v>15</v>
+      </c>
+      <c r="S363" t="n">
+        <v>18</v>
+      </c>
+      <c r="T363" t="n">
+        <v>0</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2487755</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>65</v>
+      </c>
+      <c r="W363" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="X363" t="n">
+        <v>0.5831265508684864</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>67.52873563218391</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>0.8153537380832915</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>93.23006310958118</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>-25.70132747739727</v>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AI363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>26</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>200</v>
+      </c>
+      <c r="F364" t="n">
+        <v>74</v>
+      </c>
+      <c r="G364" t="n">
+        <v>20</v>
+      </c>
+      <c r="H364" t="n">
+        <v>45</v>
+      </c>
+      <c r="I364" t="n">
+        <v>9</v>
+      </c>
+      <c r="J364" t="n">
+        <v>42</v>
+      </c>
+      <c r="K364" t="n">
+        <v>7</v>
+      </c>
+      <c r="L364" t="n">
+        <v>11</v>
+      </c>
+      <c r="M364" t="n">
+        <v>18</v>
+      </c>
+      <c r="N364" t="n">
+        <v>24</v>
+      </c>
+      <c r="O364" t="n">
+        <v>17</v>
+      </c>
+      <c r="P364" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>3</v>
+      </c>
+      <c r="R364" t="n">
+        <v>25</v>
+      </c>
+      <c r="S364" t="n">
+        <v>16</v>
+      </c>
+      <c r="T364" t="n">
+        <v>2</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>77</v>
+      </c>
+      <c r="W364" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="X364" t="n">
+        <v>0.780261493040911</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>96.30400832899531</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>0.8034223706176962</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>98.92086330935251</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>-2.616854980357203</v>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI364" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>26</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>200</v>
+      </c>
+      <c r="F365" t="n">
+        <v>102</v>
+      </c>
+      <c r="G365" t="n">
+        <v>23</v>
+      </c>
+      <c r="H365" t="n">
+        <v>38</v>
+      </c>
+      <c r="I365" t="n">
+        <v>11</v>
+      </c>
+      <c r="J365" t="n">
+        <v>30</v>
+      </c>
+      <c r="K365" t="n">
+        <v>23</v>
+      </c>
+      <c r="L365" t="n">
+        <v>29</v>
+      </c>
+      <c r="M365" t="n">
+        <v>14</v>
+      </c>
+      <c r="N365" t="n">
+        <v>27</v>
+      </c>
+      <c r="O365" t="n">
+        <v>18</v>
+      </c>
+      <c r="P365" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>17</v>
+      </c>
+      <c r="R365" t="n">
+        <v>26</v>
+      </c>
+      <c r="S365" t="n">
+        <v>28</v>
+      </c>
+      <c r="T365" t="n">
+        <v>0</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>2487753</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>82</v>
+      </c>
+      <c r="W365" t="n">
+        <v>97.75999999999999</v>
+      </c>
+      <c r="X365" t="n">
+        <v>1.043371522094926</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>83.75999999999999</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>121.7765042979943</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>0.8693808312128923</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>91.80474697716078</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>0.6029411764705882</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>29.9717573208335</v>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AI365" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI365"/>
+  <dimension ref="A1:AI329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37625,112 +37625,112 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E313" t="n">
         <v>200</v>
       </c>
       <c r="F313" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="G313" t="n">
+        <v>25</v>
+      </c>
+      <c r="H313" t="n">
+        <v>48</v>
+      </c>
+      <c r="I313" t="n">
+        <v>6</v>
+      </c>
+      <c r="J313" t="n">
+        <v>22</v>
+      </c>
+      <c r="K313" t="n">
+        <v>19</v>
+      </c>
+      <c r="L313" t="n">
+        <v>23</v>
+      </c>
+      <c r="M313" t="n">
+        <v>8</v>
+      </c>
+      <c r="N313" t="n">
+        <v>21</v>
+      </c>
+      <c r="O313" t="n">
         <v>18</v>
       </c>
-      <c r="H313" t="n">
-        <v>40</v>
-      </c>
-      <c r="I313" t="n">
-        <v>9</v>
-      </c>
-      <c r="J313" t="n">
-        <v>28</v>
-      </c>
-      <c r="K313" t="n">
-        <v>16</v>
-      </c>
-      <c r="L313" t="n">
-        <v>19</v>
-      </c>
-      <c r="M313" t="n">
-        <v>10</v>
-      </c>
-      <c r="N313" t="n">
-        <v>26</v>
-      </c>
-      <c r="O313" t="n">
-        <v>14</v>
-      </c>
       <c r="P313" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q313" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="R313" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="S313" t="n">
         <v>18</v>
       </c>
       <c r="T313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>2487737</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V313" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="W313" t="n">
-        <v>89.36</v>
+        <v>100.12</v>
       </c>
       <c r="X313" t="n">
-        <v>0.8840644583706356</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="Y313" t="n">
-        <v>79.36</v>
+        <v>92.12</v>
       </c>
       <c r="Z313" t="n">
-        <v>99.54637096774194</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AA313" t="n">
-        <v>1.047381546134663</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="AB313" t="n">
-        <v>114.7540983606557</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AC313" t="n">
-        <v>0.2702702702702703</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="AD313" t="n">
-        <v>0.7878787878787878</v>
+        <v>0.525</v>
       </c>
       <c r="AE313" t="n">
-        <v>0.5142857142857142</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="AF313" t="n">
-        <v>-15.2077273929138</v>
+        <v>2.698912865946681</v>
       </c>
       <c r="AG313" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI313" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
@@ -37744,108 +37744,108 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E314" t="n">
         <v>200</v>
       </c>
       <c r="F314" t="n">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="G314" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H314" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="I314" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="J314" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="K314" t="n">
         <v>29</v>
       </c>
       <c r="L314" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M314" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N314" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O314" t="n">
         <v>11</v>
       </c>
       <c r="P314" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Q314" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R314" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="S314" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="T314" t="n">
         <v>4</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>2487736</t>
+          <t>2487731</t>
         </is>
       </c>
       <c r="V314" t="n">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="W314" t="n">
-        <v>93.28</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="X314" t="n">
-        <v>0.9862778730703259</v>
+        <v>0.8465011286681716</v>
       </c>
       <c r="Y314" t="n">
-        <v>82.28</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Z314" t="n">
-        <v>111.8133203694701</v>
+        <v>93.05210918114145</v>
       </c>
       <c r="AA314" t="n">
-        <v>1.01843910806175</v>
+        <v>0.7302731411229135</v>
       </c>
       <c r="AB314" t="n">
-        <v>119.8284561049445</v>
+        <v>96.92849949647533</v>
       </c>
       <c r="AC314" t="n">
-        <v>0.275</v>
+        <v>0.25</v>
       </c>
       <c r="AD314" t="n">
-        <v>0.65</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="AE314" t="n">
-        <v>0.4625</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AF314" t="n">
-        <v>-8.015135735474388</v>
+        <v>-3.876390315333879</v>
       </c>
       <c r="AG314" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AI314" t="b">
@@ -37863,112 +37863,112 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="E315" t="n">
         <v>200</v>
       </c>
       <c r="F315" t="n">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="G315" t="n">
+        <v>10</v>
+      </c>
+      <c r="H315" t="n">
+        <v>26</v>
+      </c>
+      <c r="I315" t="n">
+        <v>6</v>
+      </c>
+      <c r="J315" t="n">
+        <v>26</v>
+      </c>
+      <c r="K315" t="n">
+        <v>13</v>
+      </c>
+      <c r="L315" t="n">
         <v>20</v>
       </c>
-      <c r="H315" t="n">
-        <v>37</v>
-      </c>
-      <c r="I315" t="n">
-        <v>8</v>
-      </c>
-      <c r="J315" t="n">
-        <v>22</v>
-      </c>
-      <c r="K315" t="n">
-        <v>20</v>
-      </c>
-      <c r="L315" t="n">
+      <c r="M315" t="n">
+        <v>6</v>
+      </c>
+      <c r="N315" t="n">
         <v>30</v>
       </c>
-      <c r="M315" t="n">
-        <v>7</v>
-      </c>
-      <c r="N315" t="n">
-        <v>27</v>
-      </c>
       <c r="O315" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="P315" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="Q315" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R315" t="n">
+        <v>24</v>
+      </c>
+      <c r="S315" t="n">
         <v>19</v>
       </c>
-      <c r="S315" t="n">
-        <v>25</v>
-      </c>
       <c r="T315" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>2487737</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V315" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="W315" t="n">
-        <v>80.2</v>
+        <v>71.8</v>
       </c>
       <c r="X315" t="n">
-        <v>1.047381546134663</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="Y315" t="n">
-        <v>73.2</v>
+        <v>65.8</v>
       </c>
       <c r="Z315" t="n">
-        <v>114.7540983606557</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.8840644583706356</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="AB315" t="n">
-        <v>99.54637096774194</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AC315" t="n">
-        <v>0.2121212121212121</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AD315" t="n">
-        <v>0.7297297297297297</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AE315" t="n">
-        <v>0.4857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="AF315" t="n">
-        <v>15.2077273929138</v>
+        <v>-28.02577257918253</v>
       </c>
       <c r="AG315" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI315" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -37982,108 +37982,108 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>200</v>
       </c>
       <c r="F316" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="G316" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="H316" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="I316" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J316" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K316" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L316" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="M316" t="n">
+        <v>9</v>
+      </c>
+      <c r="N316" t="n">
+        <v>27</v>
+      </c>
+      <c r="O316" t="n">
         <v>13</v>
       </c>
-      <c r="N316" t="n">
-        <v>22</v>
-      </c>
-      <c r="O316" t="n">
-        <v>16</v>
-      </c>
       <c r="P316" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q316" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R316" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="S316" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="T316" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>2487732</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V316" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="W316" t="n">
-        <v>92.96000000000001</v>
+        <v>79.12</v>
       </c>
       <c r="X316" t="n">
-        <v>0.9143717728055076</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="Y316" t="n">
-        <v>79.96000000000001</v>
+        <v>70.12</v>
       </c>
       <c r="Z316" t="n">
-        <v>106.3031515757879</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AA316" t="n">
-        <v>1.049868766404199</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="AB316" t="n">
-        <v>116.448326055313</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AC316" t="n">
-        <v>0.3611111111111111</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AD316" t="n">
-        <v>0.7096774193548387</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="AE316" t="n">
-        <v>0.5223880597014925</v>
+        <v>0.5</v>
       </c>
       <c r="AF316" t="n">
-        <v>-10.14517447952508</v>
+        <v>28.02577257918253</v>
       </c>
       <c r="AG316" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI316" t="b">
@@ -38101,108 +38101,108 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="E317" t="n">
         <v>200</v>
       </c>
       <c r="F317" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="G317" t="n">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="H317" t="n">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="I317" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="J317" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="K317" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="L317" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="M317" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="N317" t="n">
         <v>29</v>
       </c>
       <c r="O317" t="n">
+        <v>18</v>
+      </c>
+      <c r="P317" t="n">
         <v>13</v>
       </c>
-      <c r="P317" t="n">
-        <v>9</v>
-      </c>
       <c r="Q317" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="R317" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="S317" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="T317" t="n">
         <v>4</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>2487736</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V317" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="W317" t="n">
-        <v>93.28</v>
+        <v>114.92</v>
       </c>
       <c r="X317" t="n">
-        <v>1.01843910806175</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="Y317" t="n">
-        <v>79.28</v>
+        <v>95.92</v>
       </c>
       <c r="Z317" t="n">
-        <v>119.8284561049445</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.9862778730703259</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="AB317" t="n">
-        <v>111.8133203694701</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AC317" t="n">
-        <v>0.35</v>
+        <v>0.475</v>
       </c>
       <c r="AD317" t="n">
-        <v>0.725</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="AE317" t="n">
-        <v>0.5375</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="AF317" t="n">
-        <v>8.015135735474388</v>
+        <v>-2.698912865946681</v>
       </c>
       <c r="AG317" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI317" t="b">
@@ -38216,112 +38216,112 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
           <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="D318" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E318" t="n">
         <v>200</v>
       </c>
       <c r="F318" t="n">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="G318" t="n">
+        <v>23</v>
+      </c>
+      <c r="H318" t="n">
+        <v>53</v>
+      </c>
+      <c r="I318" t="n">
+        <v>3</v>
+      </c>
+      <c r="J318" t="n">
+        <v>16</v>
+      </c>
+      <c r="K318" t="n">
+        <v>15</v>
+      </c>
+      <c r="L318" t="n">
         <v>25</v>
       </c>
-      <c r="H318" t="n">
-        <v>48</v>
-      </c>
-      <c r="I318" t="n">
+      <c r="M318" t="n">
+        <v>11</v>
+      </c>
+      <c r="N318" t="n">
+        <v>25</v>
+      </c>
+      <c r="O318" t="n">
+        <v>15</v>
+      </c>
+      <c r="P318" t="n">
         <v>6</v>
       </c>
-      <c r="J318" t="n">
-        <v>22</v>
-      </c>
-      <c r="K318" t="n">
-        <v>19</v>
-      </c>
-      <c r="L318" t="n">
-        <v>23</v>
-      </c>
-      <c r="M318" t="n">
-        <v>8</v>
-      </c>
-      <c r="N318" t="n">
-        <v>21</v>
-      </c>
-      <c r="O318" t="n">
-        <v>18</v>
-      </c>
-      <c r="P318" t="n">
-        <v>21</v>
-      </c>
       <c r="Q318" t="n">
+        <v>12</v>
+      </c>
+      <c r="R318" t="n">
         <v>20</v>
-      </c>
-      <c r="R318" t="n">
-        <v>18</v>
       </c>
       <c r="S318" t="n">
         <v>18</v>
       </c>
       <c r="T318" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487741</t>
         </is>
       </c>
       <c r="V318" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="W318" t="n">
-        <v>100.12</v>
+        <v>92</v>
       </c>
       <c r="X318" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="Y318" t="n">
-        <v>92.12</v>
+        <v>81</v>
       </c>
       <c r="Z318" t="n">
-        <v>94.44203213200173</v>
+        <v>86.41975308641975</v>
       </c>
       <c r="AA318" t="n">
-        <v>0.7657500870170554</v>
+        <v>1.026361279170268</v>
       </c>
       <c r="AB318" t="n">
-        <v>91.74311926605505</v>
+        <v>113.6907611297271</v>
       </c>
       <c r="AC318" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.25</v>
       </c>
       <c r="AD318" t="n">
-        <v>0.525</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="AE318" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AF318" t="n">
-        <v>2.698912865946681</v>
+        <v>-27.27100804330739</v>
       </c>
       <c r="AG318" t="inlineStr">
         <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH318" t="inlineStr">
+        <is>
           <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="AH318" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI318" t="b">
@@ -38335,116 +38335,116 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E319" t="n">
         <v>200</v>
       </c>
       <c r="F319" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G319" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H319" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I319" t="n">
         <v>4</v>
       </c>
       <c r="J319" t="n">
+        <v>29</v>
+      </c>
+      <c r="K319" t="n">
+        <v>10</v>
+      </c>
+      <c r="L319" t="n">
+        <v>13</v>
+      </c>
+      <c r="M319" t="n">
+        <v>15</v>
+      </c>
+      <c r="N319" t="n">
+        <v>18</v>
+      </c>
+      <c r="O319" t="n">
+        <v>14</v>
+      </c>
+      <c r="P319" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>14</v>
+      </c>
+      <c r="R319" t="n">
+        <v>20</v>
+      </c>
+      <c r="S319" t="n">
         <v>19</v>
       </c>
-      <c r="K319" t="n">
-        <v>29</v>
-      </c>
-      <c r="L319" t="n">
-        <v>40</v>
-      </c>
-      <c r="M319" t="n">
-        <v>8</v>
-      </c>
-      <c r="N319" t="n">
-        <v>27</v>
-      </c>
-      <c r="O319" t="n">
-        <v>11</v>
-      </c>
-      <c r="P319" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q319" t="n">
-        <v>16</v>
-      </c>
-      <c r="R319" t="n">
-        <v>27</v>
-      </c>
-      <c r="S319" t="n">
-        <v>25</v>
-      </c>
       <c r="T319" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>2487731</t>
+          <t>2487742</t>
         </is>
       </c>
       <c r="V319" t="n">
         <v>77</v>
       </c>
       <c r="W319" t="n">
-        <v>88.59999999999999</v>
+        <v>89.72</v>
       </c>
       <c r="X319" t="n">
-        <v>0.8465011286681716</v>
+        <v>0.7133303611234953</v>
       </c>
       <c r="Y319" t="n">
-        <v>80.59999999999999</v>
+        <v>74.72</v>
       </c>
       <c r="Z319" t="n">
-        <v>93.05210918114145</v>
+        <v>85.65310492505354</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.7302731411229135</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="AB319" t="n">
-        <v>96.92849949647533</v>
+        <v>107.2423398328691</v>
       </c>
       <c r="AC319" t="n">
-        <v>0.25</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="AD319" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.5625</v>
       </c>
       <c r="AE319" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="AF319" t="n">
-        <v>-3.876390315333879</v>
+        <v>-21.58923490781554</v>
       </c>
       <c r="AG319" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="AI319" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -38454,112 +38454,112 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E320" t="n">
         <v>200</v>
       </c>
       <c r="F320" t="n">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="G320" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H320" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I320" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J320" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K320" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="L320" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="M320" t="n">
+        <v>4</v>
+      </c>
+      <c r="N320" t="n">
+        <v>27</v>
+      </c>
+      <c r="O320" t="n">
+        <v>20</v>
+      </c>
+      <c r="P320" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q320" t="n">
         <v>9</v>
       </c>
-      <c r="N320" t="n">
-        <v>23</v>
-      </c>
-      <c r="O320" t="n">
-        <v>18</v>
-      </c>
-      <c r="P320" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q320" t="n">
-        <v>8</v>
-      </c>
       <c r="R320" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="S320" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>2487732</t>
+          <t>2487740</t>
         </is>
       </c>
       <c r="V320" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="W320" t="n">
-        <v>91.44</v>
+        <v>85.03999999999999</v>
       </c>
       <c r="X320" t="n">
-        <v>1.049868766404199</v>
+        <v>0.8819379115710255</v>
       </c>
       <c r="Y320" t="n">
-        <v>82.44</v>
+        <v>81.03999999999999</v>
       </c>
       <c r="Z320" t="n">
-        <v>116.448326055313</v>
+        <v>92.54689042448175</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.9143717728055076</v>
+        <v>0.8535582064993829</v>
       </c>
       <c r="AB320" t="n">
-        <v>106.3031515757879</v>
+        <v>96.24304267161409</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.2903225806451613</v>
+        <v>0.1</v>
       </c>
       <c r="AD320" t="n">
-        <v>0.6388888888888888</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="AE320" t="n">
-        <v>0.4776119402985075</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="AF320" t="n">
-        <v>10.14517447952508</v>
+        <v>-3.696152247132346</v>
       </c>
       <c r="AG320" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AI320" t="b">
@@ -38573,112 +38573,112 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E321" t="n">
         <v>200</v>
       </c>
       <c r="F321" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="G321" t="n">
+        <v>13</v>
+      </c>
+      <c r="H321" t="n">
+        <v>34</v>
+      </c>
+      <c r="I321" t="n">
+        <v>9</v>
+      </c>
+      <c r="J321" t="n">
+        <v>30</v>
+      </c>
+      <c r="K321" t="n">
+        <v>15</v>
+      </c>
+      <c r="L321" t="n">
+        <v>31</v>
+      </c>
+      <c r="M321" t="n">
+        <v>19</v>
+      </c>
+      <c r="N321" t="n">
+        <v>23</v>
+      </c>
+      <c r="O321" t="n">
         <v>10</v>
       </c>
-      <c r="H321" t="n">
-        <v>26</v>
-      </c>
-      <c r="I321" t="n">
-        <v>6</v>
-      </c>
-      <c r="J321" t="n">
-        <v>26</v>
-      </c>
-      <c r="K321" t="n">
-        <v>13</v>
-      </c>
-      <c r="L321" t="n">
-        <v>20</v>
-      </c>
-      <c r="M321" t="n">
-        <v>6</v>
-      </c>
-      <c r="N321" t="n">
-        <v>30</v>
-      </c>
-      <c r="O321" t="n">
-        <v>6</v>
-      </c>
       <c r="P321" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="Q321" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R321" t="n">
+        <v>21</v>
+      </c>
+      <c r="S321" t="n">
         <v>24</v>
-      </c>
-      <c r="S321" t="n">
-        <v>19</v>
       </c>
       <c r="T321" t="n">
         <v>2</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487739</t>
         </is>
       </c>
       <c r="V321" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="W321" t="n">
-        <v>71.8</v>
+        <v>93.64</v>
       </c>
       <c r="X321" t="n">
-        <v>0.7103064066852368</v>
+        <v>0.7261853908586074</v>
       </c>
       <c r="Y321" t="n">
-        <v>65.8</v>
+        <v>74.64</v>
       </c>
       <c r="Z321" t="n">
-        <v>77.50759878419453</v>
+        <v>91.10396570203645</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.935288169868554</v>
+        <v>0.5619215513442045</v>
       </c>
       <c r="AB321" t="n">
-        <v>105.5333713633771</v>
+        <v>66.44085461177697</v>
       </c>
       <c r="AC321" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.475</v>
       </c>
       <c r="AD321" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="AE321" t="n">
-        <v>0.5</v>
+        <v>0.5454545454545454</v>
       </c>
       <c r="AF321" t="n">
-        <v>-28.02577257918253</v>
+        <v>24.66311109025948</v>
       </c>
       <c r="AG321" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AI321" t="b">
@@ -38692,116 +38692,116 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="E322" t="n">
         <v>200</v>
       </c>
       <c r="F322" t="n">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="G322" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="H322" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="I322" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J322" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K322" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="L322" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="M322" t="n">
         <v>9</v>
       </c>
       <c r="N322" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O322" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="P322" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="Q322" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="R322" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="S322" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="T322" t="n">
         <v>1</v>
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487744</t>
         </is>
       </c>
       <c r="V322" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="W322" t="n">
-        <v>79.12</v>
+        <v>94.28</v>
       </c>
       <c r="X322" t="n">
-        <v>0.935288169868554</v>
+        <v>0.9227831989817564</v>
       </c>
       <c r="Y322" t="n">
-        <v>70.12</v>
+        <v>85.28</v>
       </c>
       <c r="Z322" t="n">
-        <v>105.5333713633771</v>
+        <v>102.0168855534709</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.7103064066852368</v>
+        <v>0.7312996239030506</v>
       </c>
       <c r="AB322" t="n">
-        <v>77.50759878419453</v>
+        <v>83.61204013377926</v>
       </c>
       <c r="AC322" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="AD322" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.6470588235294118</v>
       </c>
       <c r="AE322" t="n">
-        <v>0.5</v>
+        <v>0.4626865671641791</v>
       </c>
       <c r="AF322" t="n">
-        <v>28.02577257918253</v>
+        <v>18.40484541969165</v>
       </c>
       <c r="AG322" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AI322" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -38811,116 +38811,116 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="E323" t="n">
         <v>200</v>
       </c>
       <c r="F323" t="n">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="G323" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="H323" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="I323" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="J323" t="n">
         <v>24</v>
       </c>
       <c r="K323" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="L323" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="M323" t="n">
+        <v>14</v>
+      </c>
+      <c r="N323" t="n">
+        <v>21</v>
+      </c>
+      <c r="O323" t="n">
+        <v>7</v>
+      </c>
+      <c r="P323" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q323" t="n">
         <v>19</v>
       </c>
-      <c r="N323" t="n">
-        <v>29</v>
-      </c>
-      <c r="O323" t="n">
-        <v>18</v>
-      </c>
-      <c r="P323" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q323" t="n">
-        <v>31</v>
-      </c>
       <c r="R323" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="S323" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="T323" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487739</t>
         </is>
       </c>
       <c r="V323" t="n">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="W323" t="n">
-        <v>114.92</v>
+        <v>90.75999999999999</v>
       </c>
       <c r="X323" t="n">
-        <v>0.7657500870170554</v>
+        <v>0.5619215513442045</v>
       </c>
       <c r="Y323" t="n">
-        <v>95.92</v>
+        <v>76.75999999999999</v>
       </c>
       <c r="Z323" t="n">
-        <v>91.74311926605505</v>
+        <v>66.44085461177697</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.7261853908586074</v>
       </c>
       <c r="AB323" t="n">
-        <v>94.44203213200173</v>
+        <v>91.10396570203645</v>
       </c>
       <c r="AC323" t="n">
-        <v>0.475</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="AD323" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.525</v>
       </c>
       <c r="AE323" t="n">
-        <v>0.6233766233766234</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="AF323" t="n">
-        <v>-2.698912865946681</v>
+        <v>-24.66311109025948</v>
       </c>
       <c r="AG323" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AI323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -38934,99 +38934,99 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
           <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="E324" t="n">
         <v>200</v>
       </c>
       <c r="F324" t="n">
+        <v>95</v>
+      </c>
+      <c r="G324" t="n">
+        <v>27</v>
+      </c>
+      <c r="H324" t="n">
+        <v>51</v>
+      </c>
+      <c r="I324" t="n">
+        <v>8</v>
+      </c>
+      <c r="J324" t="n">
+        <v>20</v>
+      </c>
+      <c r="K324" t="n">
+        <v>17</v>
+      </c>
+      <c r="L324" t="n">
+        <v>24</v>
+      </c>
+      <c r="M324" t="n">
+        <v>9</v>
+      </c>
+      <c r="N324" t="n">
+        <v>33</v>
+      </c>
+      <c r="O324" t="n">
+        <v>23</v>
+      </c>
+      <c r="P324" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>11</v>
+      </c>
+      <c r="R324" t="n">
+        <v>18</v>
+      </c>
+      <c r="S324" t="n">
+        <v>20</v>
+      </c>
+      <c r="T324" t="n">
+        <v>2</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
         <v>70</v>
       </c>
-      <c r="G324" t="n">
-        <v>23</v>
-      </c>
-      <c r="H324" t="n">
-        <v>53</v>
-      </c>
-      <c r="I324" t="n">
-        <v>3</v>
-      </c>
-      <c r="J324" t="n">
-        <v>16</v>
-      </c>
-      <c r="K324" t="n">
-        <v>15</v>
-      </c>
-      <c r="L324" t="n">
-        <v>25</v>
-      </c>
-      <c r="M324" t="n">
-        <v>11</v>
-      </c>
-      <c r="N324" t="n">
-        <v>25</v>
-      </c>
-      <c r="O324" t="n">
-        <v>15</v>
-      </c>
-      <c r="P324" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q324" t="n">
-        <v>12</v>
-      </c>
-      <c r="R324" t="n">
-        <v>20</v>
-      </c>
-      <c r="S324" t="n">
-        <v>18</v>
-      </c>
-      <c r="T324" t="n">
-        <v>3</v>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>2487741</t>
-        </is>
-      </c>
-      <c r="V324" t="n">
-        <v>95</v>
-      </c>
       <c r="W324" t="n">
-        <v>92</v>
+        <v>92.56</v>
       </c>
       <c r="X324" t="n">
+        <v>1.026361279170268</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>113.6907611297271</v>
+      </c>
+      <c r="AA324" t="n">
         <v>0.7608695652173914</v>
       </c>
-      <c r="Y324" t="n">
-        <v>81</v>
-      </c>
-      <c r="Z324" t="n">
+      <c r="AB324" t="n">
         <v>86.41975308641975</v>
       </c>
-      <c r="AA324" t="n">
-        <v>1.026361279170268</v>
-      </c>
-      <c r="AB324" t="n">
-        <v>113.6907611297271</v>
-      </c>
       <c r="AC324" t="n">
-        <v>0.25</v>
+        <v>0.2647058823529412</v>
       </c>
       <c r="AD324" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.75</v>
       </c>
       <c r="AE324" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="AF324" t="n">
-        <v>-27.27100804330739</v>
+        <v>27.27100804330739</v>
       </c>
       <c r="AG324" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         </is>
       </c>
       <c r="AI324" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -39053,22 +39053,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="E325" t="n">
         <v>200</v>
       </c>
       <c r="F325" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G325" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H325" t="n">
         <v>41</v>
@@ -39077,88 +39077,88 @@
         <v>4</v>
       </c>
       <c r="J325" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K325" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L325" t="n">
         <v>13</v>
       </c>
       <c r="M325" t="n">
+        <v>12</v>
+      </c>
+      <c r="N325" t="n">
+        <v>24</v>
+      </c>
+      <c r="O325" t="n">
+        <v>13</v>
+      </c>
+      <c r="P325" t="n">
         <v>15</v>
       </c>
-      <c r="N325" t="n">
-        <v>18</v>
-      </c>
-      <c r="O325" t="n">
-        <v>14</v>
-      </c>
-      <c r="P325" t="n">
-        <v>8</v>
-      </c>
       <c r="Q325" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="R325" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="S325" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="T325" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487744</t>
         </is>
       </c>
       <c r="V325" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="W325" t="n">
-        <v>89.72</v>
+        <v>95.72</v>
       </c>
       <c r="X325" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.7312996239030506</v>
       </c>
       <c r="Y325" t="n">
-        <v>74.72</v>
+        <v>83.72</v>
       </c>
       <c r="Z325" t="n">
-        <v>85.65310492505354</v>
+        <v>83.61204013377926</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.9227831989817564</v>
       </c>
       <c r="AB325" t="n">
-        <v>107.2423398328691</v>
+        <v>102.0168855534709</v>
       </c>
       <c r="AC325" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.3529411764705883</v>
       </c>
       <c r="AD325" t="n">
-        <v>0.5625</v>
+        <v>0.7272727272727273</v>
       </c>
       <c r="AE325" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.5373134328358209</v>
       </c>
       <c r="AF325" t="n">
-        <v>-21.58923490781554</v>
+        <v>-18.40484541969165</v>
       </c>
       <c r="AG325" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AI325" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
@@ -39172,108 +39172,108 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="E326" t="n">
         <v>200</v>
       </c>
       <c r="F326" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="G326" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="H326" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I326" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J326" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="K326" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L326" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M326" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="N326" t="n">
         <v>27</v>
       </c>
       <c r="O326" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P326" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="Q326" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="R326" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="S326" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="T326" t="n">
         <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>2487738</t>
+          <t>2487743</t>
         </is>
       </c>
       <c r="V326" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="W326" t="n">
-        <v>92.92</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="X326" t="n">
-        <v>0.8179078777442962</v>
+        <v>0.6339712918660287</v>
       </c>
       <c r="Y326" t="n">
-        <v>79.92</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="Z326" t="n">
-        <v>95.09509509509509</v>
+        <v>66.58291457286433</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.8848566308243727</v>
+        <v>0.9238138686131386</v>
       </c>
       <c r="AB326" t="n">
-        <v>98.40558046836074</v>
+        <v>101.6566265060241</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.3170731707317073</v>
+        <v>0.1290322580645161</v>
       </c>
       <c r="AD326" t="n">
-        <v>0.75</v>
+        <v>0.7714285714285715</v>
       </c>
       <c r="AE326" t="n">
-        <v>0.5194805194805194</v>
+        <v>0.4696969696969697</v>
       </c>
       <c r="AF326" t="n">
-        <v>-3.310485373265649</v>
+        <v>-35.07371193315976</v>
       </c>
       <c r="AG326" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AI326" t="b">
@@ -39291,112 +39291,112 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="E327" t="n">
         <v>200</v>
       </c>
       <c r="F327" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G327" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H327" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="I327" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J327" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K327" t="n">
+        <v>11</v>
+      </c>
+      <c r="L327" t="n">
         <v>20</v>
       </c>
-      <c r="L327" t="n">
-        <v>37</v>
-      </c>
       <c r="M327" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N327" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="O327" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="P327" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Q327" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="R327" t="n">
         <v>20</v>
       </c>
       <c r="S327" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="T327" t="n">
         <v>3</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>2487738</t>
+          <t>2487742</t>
         </is>
       </c>
       <c r="V327" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="W327" t="n">
-        <v>89.28</v>
+        <v>85.8</v>
       </c>
       <c r="X327" t="n">
-        <v>0.8848566308243727</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="Y327" t="n">
-        <v>80.28</v>
+        <v>71.8</v>
       </c>
       <c r="Z327" t="n">
-        <v>98.40558046836074</v>
+        <v>107.2423398328691</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.8179078777442962</v>
+        <v>0.7133303611234953</v>
       </c>
       <c r="AB327" t="n">
-        <v>95.09509509509509</v>
+        <v>85.65310492505354</v>
       </c>
       <c r="AC327" t="n">
-        <v>0.25</v>
+        <v>0.4375</v>
       </c>
       <c r="AD327" t="n">
-        <v>0.6829268292682927</v>
+        <v>0.6341463414634146</v>
       </c>
       <c r="AE327" t="n">
-        <v>0.4805194805194805</v>
+        <v>0.547945205479452</v>
       </c>
       <c r="AF327" t="n">
-        <v>3.310485373265649</v>
+        <v>21.58923490781554</v>
       </c>
       <c r="AG327" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>BALONCESTO TELDE</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="AI327" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
@@ -39410,108 +39410,108 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="E328" t="n">
         <v>200</v>
       </c>
       <c r="F328" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="G328" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H328" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="I328" t="n">
         <v>9</v>
       </c>
       <c r="J328" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="K328" t="n">
+        <v>16</v>
+      </c>
+      <c r="L328" t="n">
+        <v>22</v>
+      </c>
+      <c r="M328" t="n">
         <v>8</v>
-      </c>
-      <c r="L328" t="n">
-        <v>16</v>
-      </c>
-      <c r="M328" t="n">
-        <v>4</v>
       </c>
       <c r="N328" t="n">
         <v>27</v>
       </c>
       <c r="O328" t="n">
+        <v>24</v>
+      </c>
+      <c r="P328" t="n">
         <v>20</v>
       </c>
-      <c r="P328" t="n">
-        <v>11</v>
-      </c>
       <c r="Q328" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R328" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="S328" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T328" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>2487740</t>
+          <t>2487743</t>
         </is>
       </c>
       <c r="V328" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="W328" t="n">
-        <v>85.03999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="X328" t="n">
-        <v>0.8819379115710255</v>
+        <v>0.9238138686131386</v>
       </c>
       <c r="Y328" t="n">
-        <v>81.03999999999999</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="Z328" t="n">
-        <v>92.54689042448175</v>
+        <v>101.6566265060241</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.8535582064993829</v>
+        <v>0.6339712918660287</v>
       </c>
       <c r="AB328" t="n">
-        <v>96.24304267161409</v>
+        <v>66.58291457286433</v>
       </c>
       <c r="AC328" t="n">
-        <v>0.1</v>
+        <v>0.2285714285714286</v>
       </c>
       <c r="AD328" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.8709677419354839</v>
       </c>
       <c r="AE328" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.5303030303030303</v>
       </c>
       <c r="AF328" t="n">
-        <v>-3.696152247132346</v>
+        <v>35.07371193315976</v>
       </c>
       <c r="AG328" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AI328" t="b">
@@ -39529,25 +39529,25 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="E329" t="n">
         <v>200</v>
       </c>
       <c r="F329" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G329" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H329" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I329" t="n">
         <v>9</v>
@@ -39556,4368 +39556,84 @@
         <v>30</v>
       </c>
       <c r="K329" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L329" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="M329" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="N329" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="O329" t="n">
         <v>10</v>
       </c>
       <c r="P329" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="Q329" t="n">
+        <v>19</v>
+      </c>
+      <c r="R329" t="n">
+        <v>15</v>
+      </c>
+      <c r="S329" t="n">
         <v>16</v>
       </c>
-      <c r="R329" t="n">
-        <v>21</v>
-      </c>
-      <c r="S329" t="n">
-        <v>24</v>
-      </c>
       <c r="T329" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487740</t>
         </is>
       </c>
       <c r="V329" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="W329" t="n">
-        <v>93.64</v>
+        <v>97.24000000000001</v>
       </c>
       <c r="X329" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.8535582064993829</v>
       </c>
       <c r="Y329" t="n">
-        <v>74.64</v>
+        <v>86.24000000000001</v>
       </c>
       <c r="Z329" t="n">
-        <v>91.10396570203645</v>
+        <v>96.24304267161409</v>
       </c>
       <c r="AA329" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.8819379115710255</v>
       </c>
       <c r="AB329" t="n">
-        <v>66.44085461177697</v>
+        <v>92.54689042448175</v>
       </c>
       <c r="AC329" t="n">
-        <v>0.475</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="AD329" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.9</v>
       </c>
       <c r="AE329" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.6025641025641025</v>
       </c>
       <c r="AF329" t="n">
-        <v>24.66311109025948</v>
+        <v>3.696152247132346</v>
       </c>
       <c r="AG329" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AH329" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AI329" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B330" t="n">
-        <v>24</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="E330" t="n">
-        <v>200</v>
-      </c>
-      <c r="F330" t="n">
-        <v>87</v>
-      </c>
-      <c r="G330" t="n">
-        <v>29</v>
-      </c>
-      <c r="H330" t="n">
-        <v>45</v>
-      </c>
-      <c r="I330" t="n">
-        <v>8</v>
-      </c>
-      <c r="J330" t="n">
-        <v>25</v>
-      </c>
-      <c r="K330" t="n">
-        <v>5</v>
-      </c>
-      <c r="L330" t="n">
-        <v>12</v>
-      </c>
-      <c r="M330" t="n">
-        <v>9</v>
-      </c>
-      <c r="N330" t="n">
-        <v>22</v>
-      </c>
-      <c r="O330" t="n">
-        <v>19</v>
-      </c>
-      <c r="P330" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q330" t="n">
-        <v>19</v>
-      </c>
-      <c r="R330" t="n">
-        <v>15</v>
-      </c>
-      <c r="S330" t="n">
-        <v>15</v>
-      </c>
-      <c r="T330" t="n">
-        <v>1</v>
-      </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>2487744</t>
-        </is>
-      </c>
-      <c r="V330" t="n">
-        <v>70</v>
-      </c>
-      <c r="W330" t="n">
-        <v>94.28</v>
-      </c>
-      <c r="X330" t="n">
-        <v>0.9227831989817564</v>
-      </c>
-      <c r="Y330" t="n">
-        <v>85.28</v>
-      </c>
-      <c r="Z330" t="n">
-        <v>102.0168855534709</v>
-      </c>
-      <c r="AA330" t="n">
-        <v>0.7312996239030506</v>
-      </c>
-      <c r="AB330" t="n">
-        <v>83.61204013377926</v>
-      </c>
-      <c r="AC330" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="AD330" t="n">
-        <v>0.6470588235294118</v>
-      </c>
-      <c r="AE330" t="n">
-        <v>0.4626865671641791</v>
-      </c>
-      <c r="AF330" t="n">
-        <v>18.40484541969165</v>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="AI330" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>24</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="E331" t="n">
-        <v>200</v>
-      </c>
-      <c r="F331" t="n">
-        <v>51</v>
-      </c>
-      <c r="G331" t="n">
-        <v>12</v>
-      </c>
-      <c r="H331" t="n">
-        <v>35</v>
-      </c>
-      <c r="I331" t="n">
-        <v>2</v>
-      </c>
-      <c r="J331" t="n">
-        <v>24</v>
-      </c>
-      <c r="K331" t="n">
-        <v>21</v>
-      </c>
-      <c r="L331" t="n">
-        <v>29</v>
-      </c>
-      <c r="M331" t="n">
-        <v>14</v>
-      </c>
-      <c r="N331" t="n">
-        <v>21</v>
-      </c>
-      <c r="O331" t="n">
-        <v>7</v>
-      </c>
-      <c r="P331" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q331" t="n">
-        <v>19</v>
-      </c>
-      <c r="R331" t="n">
-        <v>25</v>
-      </c>
-      <c r="S331" t="n">
-        <v>20</v>
-      </c>
-      <c r="T331" t="n">
-        <v>3</v>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>2487739</t>
-        </is>
-      </c>
-      <c r="V331" t="n">
-        <v>68</v>
-      </c>
-      <c r="W331" t="n">
-        <v>90.75999999999999</v>
-      </c>
-      <c r="X331" t="n">
-        <v>0.5619215513442045</v>
-      </c>
-      <c r="Y331" t="n">
-        <v>76.75999999999999</v>
-      </c>
-      <c r="Z331" t="n">
-        <v>66.44085461177697</v>
-      </c>
-      <c r="AA331" t="n">
-        <v>0.7261853908586074</v>
-      </c>
-      <c r="AB331" t="n">
-        <v>91.10396570203645</v>
-      </c>
-      <c r="AC331" t="n">
-        <v>0.3783783783783784</v>
-      </c>
-      <c r="AD331" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="AE331" t="n">
-        <v>0.4545454545454545</v>
-      </c>
-      <c r="AF331" t="n">
-        <v>-24.66311109025948</v>
-      </c>
-      <c r="AG331" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="AI331" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>24</v>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="E332" t="n">
-        <v>200</v>
-      </c>
-      <c r="F332" t="n">
-        <v>95</v>
-      </c>
-      <c r="G332" t="n">
-        <v>27</v>
-      </c>
-      <c r="H332" t="n">
-        <v>51</v>
-      </c>
-      <c r="I332" t="n">
-        <v>8</v>
-      </c>
-      <c r="J332" t="n">
-        <v>20</v>
-      </c>
-      <c r="K332" t="n">
-        <v>17</v>
-      </c>
-      <c r="L332" t="n">
-        <v>24</v>
-      </c>
-      <c r="M332" t="n">
-        <v>9</v>
-      </c>
-      <c r="N332" t="n">
-        <v>33</v>
-      </c>
-      <c r="O332" t="n">
-        <v>23</v>
-      </c>
-      <c r="P332" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q332" t="n">
-        <v>11</v>
-      </c>
-      <c r="R332" t="n">
-        <v>18</v>
-      </c>
-      <c r="S332" t="n">
-        <v>20</v>
-      </c>
-      <c r="T332" t="n">
-        <v>2</v>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>2487741</t>
-        </is>
-      </c>
-      <c r="V332" t="n">
-        <v>70</v>
-      </c>
-      <c r="W332" t="n">
-        <v>92.56</v>
-      </c>
-      <c r="X332" t="n">
-        <v>1.026361279170268</v>
-      </c>
-      <c r="Y332" t="n">
-        <v>83.56</v>
-      </c>
-      <c r="Z332" t="n">
-        <v>113.6907611297271</v>
-      </c>
-      <c r="AA332" t="n">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="AB332" t="n">
-        <v>86.41975308641975</v>
-      </c>
-      <c r="AC332" t="n">
-        <v>0.2647058823529412</v>
-      </c>
-      <c r="AD332" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE332" t="n">
-        <v>0.5384615384615384</v>
-      </c>
-      <c r="AF332" t="n">
-        <v>27.27100804330739</v>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="AI332" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B333" t="n">
-        <v>24</v>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>200</v>
-      </c>
-      <c r="F333" t="n">
-        <v>70</v>
-      </c>
-      <c r="G333" t="n">
-        <v>25</v>
-      </c>
-      <c r="H333" t="n">
-        <v>41</v>
-      </c>
-      <c r="I333" t="n">
-        <v>4</v>
-      </c>
-      <c r="J333" t="n">
-        <v>27</v>
-      </c>
-      <c r="K333" t="n">
-        <v>8</v>
-      </c>
-      <c r="L333" t="n">
-        <v>13</v>
-      </c>
-      <c r="M333" t="n">
-        <v>12</v>
-      </c>
-      <c r="N333" t="n">
-        <v>24</v>
-      </c>
-      <c r="O333" t="n">
-        <v>13</v>
-      </c>
-      <c r="P333" t="n">
-        <v>15</v>
-      </c>
-      <c r="Q333" t="n">
-        <v>22</v>
-      </c>
-      <c r="R333" t="n">
-        <v>15</v>
-      </c>
-      <c r="S333" t="n">
-        <v>15</v>
-      </c>
-      <c r="T333" t="n">
-        <v>2</v>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>2487744</t>
-        </is>
-      </c>
-      <c r="V333" t="n">
-        <v>87</v>
-      </c>
-      <c r="W333" t="n">
-        <v>95.72</v>
-      </c>
-      <c r="X333" t="n">
-        <v>0.7312996239030506</v>
-      </c>
-      <c r="Y333" t="n">
-        <v>83.72</v>
-      </c>
-      <c r="Z333" t="n">
-        <v>83.61204013377926</v>
-      </c>
-      <c r="AA333" t="n">
-        <v>0.9227831989817564</v>
-      </c>
-      <c r="AB333" t="n">
-        <v>102.0168855534709</v>
-      </c>
-      <c r="AC333" t="n">
-        <v>0.3529411764705883</v>
-      </c>
-      <c r="AD333" t="n">
-        <v>0.7272727272727273</v>
-      </c>
-      <c r="AE333" t="n">
-        <v>0.5373134328358209</v>
-      </c>
-      <c r="AF333" t="n">
-        <v>-18.40484541969165</v>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="AI333" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>24</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>200</v>
-      </c>
-      <c r="F334" t="n">
-        <v>53</v>
-      </c>
-      <c r="G334" t="n">
-        <v>12</v>
-      </c>
-      <c r="H334" t="n">
-        <v>29</v>
-      </c>
-      <c r="I334" t="n">
-        <v>6</v>
-      </c>
-      <c r="J334" t="n">
-        <v>21</v>
-      </c>
-      <c r="K334" t="n">
-        <v>11</v>
-      </c>
-      <c r="L334" t="n">
-        <v>15</v>
-      </c>
-      <c r="M334" t="n">
-        <v>4</v>
-      </c>
-      <c r="N334" t="n">
-        <v>27</v>
-      </c>
-      <c r="O334" t="n">
-        <v>13</v>
-      </c>
-      <c r="P334" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q334" t="n">
-        <v>27</v>
-      </c>
-      <c r="R334" t="n">
-        <v>21</v>
-      </c>
-      <c r="S334" t="n">
-        <v>20</v>
-      </c>
-      <c r="T334" t="n">
-        <v>1</v>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>2487743</t>
-        </is>
-      </c>
-      <c r="V334" t="n">
-        <v>81</v>
-      </c>
-      <c r="W334" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="X334" t="n">
-        <v>0.6339712918660287</v>
-      </c>
-      <c r="Y334" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="Z334" t="n">
-        <v>66.58291457286433</v>
-      </c>
-      <c r="AA334" t="n">
-        <v>0.9238138686131386</v>
-      </c>
-      <c r="AB334" t="n">
-        <v>101.6566265060241</v>
-      </c>
-      <c r="AC334" t="n">
-        <v>0.1290322580645161</v>
-      </c>
-      <c r="AD334" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-      <c r="AE334" t="n">
-        <v>0.4696969696969697</v>
-      </c>
-      <c r="AF334" t="n">
-        <v>-35.07371193315976</v>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="AI334" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>24</v>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>200</v>
-      </c>
-      <c r="F335" t="n">
-        <v>77</v>
-      </c>
-      <c r="G335" t="n">
-        <v>24</v>
-      </c>
-      <c r="H335" t="n">
-        <v>43</v>
-      </c>
-      <c r="I335" t="n">
-        <v>6</v>
-      </c>
-      <c r="J335" t="n">
-        <v>19</v>
-      </c>
-      <c r="K335" t="n">
-        <v>11</v>
-      </c>
-      <c r="L335" t="n">
-        <v>20</v>
-      </c>
-      <c r="M335" t="n">
-        <v>14</v>
-      </c>
-      <c r="N335" t="n">
-        <v>26</v>
-      </c>
-      <c r="O335" t="n">
-        <v>13</v>
-      </c>
-      <c r="P335" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q335" t="n">
-        <v>15</v>
-      </c>
-      <c r="R335" t="n">
-        <v>20</v>
-      </c>
-      <c r="S335" t="n">
-        <v>20</v>
-      </c>
-      <c r="T335" t="n">
-        <v>3</v>
-      </c>
-      <c r="U335" t="inlineStr">
-        <is>
-          <t>2487742</t>
-        </is>
-      </c>
-      <c r="V335" t="n">
-        <v>64</v>
-      </c>
-      <c r="W335" t="n">
-        <v>85.8</v>
-      </c>
-      <c r="X335" t="n">
-        <v>0.8974358974358975</v>
-      </c>
-      <c r="Y335" t="n">
-        <v>71.8</v>
-      </c>
-      <c r="Z335" t="n">
-        <v>107.2423398328691</v>
-      </c>
-      <c r="AA335" t="n">
-        <v>0.7133303611234953</v>
-      </c>
-      <c r="AB335" t="n">
-        <v>85.65310492505354</v>
-      </c>
-      <c r="AC335" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="AD335" t="n">
-        <v>0.6341463414634146</v>
-      </c>
-      <c r="AE335" t="n">
-        <v>0.547945205479452</v>
-      </c>
-      <c r="AF335" t="n">
-        <v>21.58923490781554</v>
-      </c>
-      <c r="AG335" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="AH335" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="AI335" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B336" t="n">
-        <v>24</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>200</v>
-      </c>
-      <c r="F336" t="n">
-        <v>81</v>
-      </c>
-      <c r="G336" t="n">
-        <v>19</v>
-      </c>
-      <c r="H336" t="n">
-        <v>39</v>
-      </c>
-      <c r="I336" t="n">
-        <v>9</v>
-      </c>
-      <c r="J336" t="n">
-        <v>23</v>
-      </c>
-      <c r="K336" t="n">
-        <v>16</v>
-      </c>
-      <c r="L336" t="n">
-        <v>22</v>
-      </c>
-      <c r="M336" t="n">
-        <v>8</v>
-      </c>
-      <c r="N336" t="n">
-        <v>27</v>
-      </c>
-      <c r="O336" t="n">
-        <v>24</v>
-      </c>
-      <c r="P336" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q336" t="n">
-        <v>16</v>
-      </c>
-      <c r="R336" t="n">
-        <v>20</v>
-      </c>
-      <c r="S336" t="n">
-        <v>21</v>
-      </c>
-      <c r="T336" t="n">
-        <v>0</v>
-      </c>
-      <c r="U336" t="inlineStr">
-        <is>
-          <t>2487743</t>
-        </is>
-      </c>
-      <c r="V336" t="n">
-        <v>53</v>
-      </c>
-      <c r="W336" t="n">
-        <v>87.68000000000001</v>
-      </c>
-      <c r="X336" t="n">
-        <v>0.9238138686131386</v>
-      </c>
-      <c r="Y336" t="n">
-        <v>79.68000000000001</v>
-      </c>
-      <c r="Z336" t="n">
-        <v>101.6566265060241</v>
-      </c>
-      <c r="AA336" t="n">
-        <v>0.6339712918660287</v>
-      </c>
-      <c r="AB336" t="n">
-        <v>66.58291457286433</v>
-      </c>
-      <c r="AC336" t="n">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AD336" t="n">
-        <v>0.8709677419354839</v>
-      </c>
-      <c r="AE336" t="n">
-        <v>0.5303030303030303</v>
-      </c>
-      <c r="AF336" t="n">
-        <v>35.07371193315976</v>
-      </c>
-      <c r="AG336" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="AI336" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>24</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>200</v>
-      </c>
-      <c r="F337" t="n">
-        <v>83</v>
-      </c>
-      <c r="G337" t="n">
-        <v>21</v>
-      </c>
-      <c r="H337" t="n">
-        <v>39</v>
-      </c>
-      <c r="I337" t="n">
-        <v>9</v>
-      </c>
-      <c r="J337" t="n">
-        <v>30</v>
-      </c>
-      <c r="K337" t="n">
-        <v>14</v>
-      </c>
-      <c r="L337" t="n">
-        <v>21</v>
-      </c>
-      <c r="M337" t="n">
-        <v>11</v>
-      </c>
-      <c r="N337" t="n">
-        <v>36</v>
-      </c>
-      <c r="O337" t="n">
-        <v>10</v>
-      </c>
-      <c r="P337" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q337" t="n">
-        <v>19</v>
-      </c>
-      <c r="R337" t="n">
-        <v>15</v>
-      </c>
-      <c r="S337" t="n">
-        <v>16</v>
-      </c>
-      <c r="T337" t="n">
-        <v>3</v>
-      </c>
-      <c r="U337" t="inlineStr">
-        <is>
-          <t>2487740</t>
-        </is>
-      </c>
-      <c r="V337" t="n">
-        <v>75</v>
-      </c>
-      <c r="W337" t="n">
-        <v>97.24000000000001</v>
-      </c>
-      <c r="X337" t="n">
-        <v>0.8535582064993829</v>
-      </c>
-      <c r="Y337" t="n">
-        <v>86.24000000000001</v>
-      </c>
-      <c r="Z337" t="n">
-        <v>96.24304267161409</v>
-      </c>
-      <c r="AA337" t="n">
-        <v>0.8819379115710255</v>
-      </c>
-      <c r="AB337" t="n">
-        <v>92.54689042448175</v>
-      </c>
-      <c r="AC337" t="n">
-        <v>0.2894736842105263</v>
-      </c>
-      <c r="AD337" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AE337" t="n">
-        <v>0.6025641025641025</v>
-      </c>
-      <c r="AF337" t="n">
-        <v>3.696152247132346</v>
-      </c>
-      <c r="AG337" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="AI337" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B338" t="n">
-        <v>25</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>200</v>
-      </c>
-      <c r="F338" t="n">
-        <v>80</v>
-      </c>
-      <c r="G338" t="n">
-        <v>20</v>
-      </c>
-      <c r="H338" t="n">
-        <v>35</v>
-      </c>
-      <c r="I338" t="n">
-        <v>8</v>
-      </c>
-      <c r="J338" t="n">
-        <v>34</v>
-      </c>
-      <c r="K338" t="n">
-        <v>16</v>
-      </c>
-      <c r="L338" t="n">
-        <v>24</v>
-      </c>
-      <c r="M338" t="n">
-        <v>8</v>
-      </c>
-      <c r="N338" t="n">
-        <v>22</v>
-      </c>
-      <c r="O338" t="n">
-        <v>21</v>
-      </c>
-      <c r="P338" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q338" t="n">
-        <v>8</v>
-      </c>
-      <c r="R338" t="n">
-        <v>26</v>
-      </c>
-      <c r="S338" t="n">
-        <v>25</v>
-      </c>
-      <c r="T338" t="n">
-        <v>2</v>
-      </c>
-      <c r="U338" t="inlineStr">
-        <is>
-          <t>2487749</t>
-        </is>
-      </c>
-      <c r="V338" t="n">
-        <v>70</v>
-      </c>
-      <c r="W338" t="n">
-        <v>87.56</v>
-      </c>
-      <c r="X338" t="n">
-        <v>0.9136592051164916</v>
-      </c>
-      <c r="Y338" t="n">
-        <v>79.56</v>
-      </c>
-      <c r="Z338" t="n">
-        <v>100.5530417295123</v>
-      </c>
-      <c r="AA338" t="n">
-        <v>0.813953488372093</v>
-      </c>
-      <c r="AB338" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="AC338" t="n">
-        <v>0.1951219512195122</v>
-      </c>
-      <c r="AD338" t="n">
-        <v>0.7857142857142857</v>
-      </c>
-      <c r="AE338" t="n">
-        <v>0.4347826086956522</v>
-      </c>
-      <c r="AF338" t="n">
-        <v>13.05304172951232</v>
-      </c>
-      <c r="AG338" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="AI338" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>25</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>200</v>
-      </c>
-      <c r="F339" t="n">
-        <v>61</v>
-      </c>
-      <c r="G339" t="n">
-        <v>13</v>
-      </c>
-      <c r="H339" t="n">
-        <v>39</v>
-      </c>
-      <c r="I339" t="n">
-        <v>7</v>
-      </c>
-      <c r="J339" t="n">
-        <v>25</v>
-      </c>
-      <c r="K339" t="n">
-        <v>14</v>
-      </c>
-      <c r="L339" t="n">
-        <v>23</v>
-      </c>
-      <c r="M339" t="n">
-        <v>13</v>
-      </c>
-      <c r="N339" t="n">
-        <v>20</v>
-      </c>
-      <c r="O339" t="n">
-        <v>10</v>
-      </c>
-      <c r="P339" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q339" t="n">
-        <v>23</v>
-      </c>
-      <c r="R339" t="n">
-        <v>18</v>
-      </c>
-      <c r="S339" t="n">
-        <v>18</v>
-      </c>
-      <c r="T339" t="n">
-        <v>2</v>
-      </c>
-      <c r="U339" t="inlineStr">
-        <is>
-          <t>2487747</t>
-        </is>
-      </c>
-      <c r="V339" t="n">
-        <v>91</v>
-      </c>
-      <c r="W339" t="n">
-        <v>97.12</v>
-      </c>
-      <c r="X339" t="n">
-        <v>0.6280889621087314</v>
-      </c>
-      <c r="Y339" t="n">
-        <v>84.12</v>
-      </c>
-      <c r="Z339" t="n">
-        <v>72.51545411317166</v>
-      </c>
-      <c r="AA339" t="n">
-        <v>1.028481012658228</v>
-      </c>
-      <c r="AB339" t="n">
-        <v>111.6838487972509</v>
-      </c>
-      <c r="AC339" t="n">
-        <v>0.3095238095238095</v>
-      </c>
-      <c r="AD339" t="n">
-        <v>0.7407407407407407</v>
-      </c>
-      <c r="AE339" t="n">
-        <v>0.4782608695652174</v>
-      </c>
-      <c r="AF339" t="n">
-        <v>-39.1683946840792</v>
-      </c>
-      <c r="AG339" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="AI339" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>25</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="E340" t="n">
-        <v>200</v>
-      </c>
-      <c r="F340" t="n">
-        <v>74</v>
-      </c>
-      <c r="G340" t="n">
-        <v>18</v>
-      </c>
-      <c r="H340" t="n">
-        <v>40</v>
-      </c>
-      <c r="I340" t="n">
-        <v>9</v>
-      </c>
-      <c r="J340" t="n">
-        <v>29</v>
-      </c>
-      <c r="K340" t="n">
-        <v>11</v>
-      </c>
-      <c r="L340" t="n">
-        <v>21</v>
-      </c>
-      <c r="M340" t="n">
-        <v>18</v>
-      </c>
-      <c r="N340" t="n">
-        <v>23</v>
-      </c>
-      <c r="O340" t="n">
-        <v>18</v>
-      </c>
-      <c r="P340" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>18</v>
-      </c>
-      <c r="R340" t="n">
-        <v>19</v>
-      </c>
-      <c r="S340" t="n">
-        <v>19</v>
-      </c>
-      <c r="T340" t="n">
-        <v>1</v>
-      </c>
-      <c r="U340" t="inlineStr">
-        <is>
-          <t>2487745</t>
-        </is>
-      </c>
-      <c r="V340" t="n">
-        <v>107</v>
-      </c>
-      <c r="W340" t="n">
-        <v>96.24000000000001</v>
-      </c>
-      <c r="X340" t="n">
-        <v>0.768911055694098</v>
-      </c>
-      <c r="Y340" t="n">
-        <v>78.24000000000001</v>
-      </c>
-      <c r="Z340" t="n">
-        <v>94.5807770961145</v>
-      </c>
-      <c r="AA340" t="n">
-        <v>1.156006914433881</v>
-      </c>
-      <c r="AB340" t="n">
-        <v>132.8202581926514</v>
-      </c>
-      <c r="AC340" t="n">
-        <v>0.4090909090909091</v>
-      </c>
-      <c r="AD340" t="n">
-        <v>0.6571428571428571</v>
-      </c>
-      <c r="AE340" t="n">
-        <v>0.5189873417721519</v>
-      </c>
-      <c r="AF340" t="n">
-        <v>-38.23948109653693</v>
-      </c>
-      <c r="AG340" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="AI340" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>25</v>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="E341" t="n">
-        <v>200</v>
-      </c>
-      <c r="F341" t="n">
-        <v>74</v>
-      </c>
-      <c r="G341" t="n">
-        <v>23</v>
-      </c>
-      <c r="H341" t="n">
-        <v>44</v>
-      </c>
-      <c r="I341" t="n">
-        <v>4</v>
-      </c>
-      <c r="J341" t="n">
-        <v>24</v>
-      </c>
-      <c r="K341" t="n">
-        <v>16</v>
-      </c>
-      <c r="L341" t="n">
-        <v>26</v>
-      </c>
-      <c r="M341" t="n">
-        <v>11</v>
-      </c>
-      <c r="N341" t="n">
-        <v>26</v>
-      </c>
-      <c r="O341" t="n">
-        <v>12</v>
-      </c>
-      <c r="P341" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q341" t="n">
-        <v>16</v>
-      </c>
-      <c r="R341" t="n">
-        <v>20</v>
-      </c>
-      <c r="S341" t="n">
-        <v>23</v>
-      </c>
-      <c r="T341" t="n">
-        <v>1</v>
-      </c>
-      <c r="U341" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="V341" t="n">
-        <v>82</v>
-      </c>
-      <c r="W341" t="n">
-        <v>95.44</v>
-      </c>
-      <c r="X341" t="n">
-        <v>0.7753562447611064</v>
-      </c>
-      <c r="Y341" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="Z341" t="n">
-        <v>87.63619137849361</v>
-      </c>
-      <c r="AA341" t="n">
-        <v>0.8570234113712374</v>
-      </c>
-      <c r="AB341" t="n">
-        <v>99.17755200774067</v>
-      </c>
-      <c r="AC341" t="n">
-        <v>0.2619047619047619</v>
-      </c>
-      <c r="AD341" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE341" t="n">
-        <v>0.4567901234567901</v>
-      </c>
-      <c r="AF341" t="n">
-        <v>-11.54136062924707</v>
-      </c>
-      <c r="AG341" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="AI341" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B342" t="n">
-        <v>25</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="E342" t="n">
-        <v>200</v>
-      </c>
-      <c r="F342" t="n">
-        <v>70</v>
-      </c>
-      <c r="G342" t="n">
-        <v>20</v>
-      </c>
-      <c r="H342" t="n">
-        <v>32</v>
-      </c>
-      <c r="I342" t="n">
-        <v>5</v>
-      </c>
-      <c r="J342" t="n">
-        <v>21</v>
-      </c>
-      <c r="K342" t="n">
-        <v>15</v>
-      </c>
-      <c r="L342" t="n">
-        <v>25</v>
-      </c>
-      <c r="M342" t="n">
-        <v>6</v>
-      </c>
-      <c r="N342" t="n">
-        <v>33</v>
-      </c>
-      <c r="O342" t="n">
-        <v>13</v>
-      </c>
-      <c r="P342" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q342" t="n">
-        <v>22</v>
-      </c>
-      <c r="R342" t="n">
-        <v>27</v>
-      </c>
-      <c r="S342" t="n">
-        <v>24</v>
-      </c>
-      <c r="T342" t="n">
-        <v>2</v>
-      </c>
-      <c r="U342" t="inlineStr">
-        <is>
-          <t>2487749</t>
-        </is>
-      </c>
-      <c r="V342" t="n">
-        <v>80</v>
-      </c>
-      <c r="W342" t="n">
-        <v>86</v>
-      </c>
-      <c r="X342" t="n">
-        <v>0.813953488372093</v>
-      </c>
-      <c r="Y342" t="n">
-        <v>80</v>
-      </c>
-      <c r="Z342" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="AA342" t="n">
-        <v>0.9136592051164916</v>
-      </c>
-      <c r="AB342" t="n">
-        <v>100.5530417295123</v>
-      </c>
-      <c r="AC342" t="n">
-        <v>0.2142857142857143</v>
-      </c>
-      <c r="AD342" t="n">
-        <v>0.8048780487804879</v>
-      </c>
-      <c r="AE342" t="n">
-        <v>0.5652173913043478</v>
-      </c>
-      <c r="AF342" t="n">
-        <v>-13.05304172951232</v>
-      </c>
-      <c r="AG342" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="AI342" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B343" t="n">
-        <v>25</v>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="E343" t="n">
-        <v>225</v>
-      </c>
-      <c r="F343" t="n">
-        <v>69</v>
-      </c>
-      <c r="G343" t="n">
-        <v>16</v>
-      </c>
-      <c r="H343" t="n">
-        <v>43</v>
-      </c>
-      <c r="I343" t="n">
-        <v>10</v>
-      </c>
-      <c r="J343" t="n">
-        <v>34</v>
-      </c>
-      <c r="K343" t="n">
-        <v>7</v>
-      </c>
-      <c r="L343" t="n">
-        <v>14</v>
-      </c>
-      <c r="M343" t="n">
-        <v>16</v>
-      </c>
-      <c r="N343" t="n">
-        <v>37</v>
-      </c>
-      <c r="O343" t="n">
-        <v>15</v>
-      </c>
-      <c r="P343" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q343" t="n">
-        <v>18</v>
-      </c>
-      <c r="R343" t="n">
-        <v>25</v>
-      </c>
-      <c r="S343" t="n">
-        <v>20</v>
-      </c>
-      <c r="T343" t="n">
-        <v>7</v>
-      </c>
-      <c r="U343" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="V343" t="n">
-        <v>71</v>
-      </c>
-      <c r="W343" t="n">
-        <v>101.16</v>
-      </c>
-      <c r="X343" t="n">
-        <v>0.6820877817319099</v>
-      </c>
-      <c r="Y343" t="n">
-        <v>85.16</v>
-      </c>
-      <c r="Z343" t="n">
-        <v>81.0239549084077</v>
-      </c>
-      <c r="AA343" t="n">
-        <v>0.6501831501831502</v>
-      </c>
-      <c r="AB343" t="n">
-        <v>77.85087719298245</v>
-      </c>
-      <c r="AC343" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="AD343" t="n">
-        <v>0.6727272727272727</v>
-      </c>
-      <c r="AE343" t="n">
-        <v>0.5047619047619047</v>
-      </c>
-      <c r="AF343" t="n">
-        <v>3.173077715425251</v>
-      </c>
-      <c r="AG343" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="AI343" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>25</v>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="E344" t="n">
-        <v>200</v>
-      </c>
-      <c r="F344" t="n">
-        <v>107</v>
-      </c>
-      <c r="G344" t="n">
-        <v>26</v>
-      </c>
-      <c r="H344" t="n">
-        <v>38</v>
-      </c>
-      <c r="I344" t="n">
-        <v>14</v>
-      </c>
-      <c r="J344" t="n">
-        <v>36</v>
-      </c>
-      <c r="K344" t="n">
-        <v>13</v>
-      </c>
-      <c r="L344" t="n">
-        <v>24</v>
-      </c>
-      <c r="M344" t="n">
-        <v>12</v>
-      </c>
-      <c r="N344" t="n">
-        <v>26</v>
-      </c>
-      <c r="O344" t="n">
-        <v>28</v>
-      </c>
-      <c r="P344" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q344" t="n">
-        <v>8</v>
-      </c>
-      <c r="R344" t="n">
-        <v>21</v>
-      </c>
-      <c r="S344" t="n">
-        <v>19</v>
-      </c>
-      <c r="T344" t="n">
-        <v>5</v>
-      </c>
-      <c r="U344" t="inlineStr">
-        <is>
-          <t>2487745</t>
-        </is>
-      </c>
-      <c r="V344" t="n">
-        <v>74</v>
-      </c>
-      <c r="W344" t="n">
-        <v>92.56</v>
-      </c>
-      <c r="X344" t="n">
-        <v>1.156006914433881</v>
-      </c>
-      <c r="Y344" t="n">
-        <v>80.56</v>
-      </c>
-      <c r="Z344" t="n">
-        <v>132.8202581926514</v>
-      </c>
-      <c r="AA344" t="n">
-        <v>0.768911055694098</v>
-      </c>
-      <c r="AB344" t="n">
-        <v>94.5807770961145</v>
-      </c>
-      <c r="AC344" t="n">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AD344" t="n">
-        <v>0.5909090909090909</v>
-      </c>
-      <c r="AE344" t="n">
-        <v>0.4810126582278481</v>
-      </c>
-      <c r="AF344" t="n">
-        <v>38.23948109653693</v>
-      </c>
-      <c r="AG344" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="AH344" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="AI344" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B345" t="n">
-        <v>25</v>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="E345" t="n">
-        <v>200</v>
-      </c>
-      <c r="F345" t="n">
-        <v>82</v>
-      </c>
-      <c r="G345" t="n">
-        <v>19</v>
-      </c>
-      <c r="H345" t="n">
-        <v>44</v>
-      </c>
-      <c r="I345" t="n">
-        <v>10</v>
-      </c>
-      <c r="J345" t="n">
-        <v>28</v>
-      </c>
-      <c r="K345" t="n">
-        <v>14</v>
-      </c>
-      <c r="L345" t="n">
-        <v>22</v>
-      </c>
-      <c r="M345" t="n">
-        <v>13</v>
-      </c>
-      <c r="N345" t="n">
-        <v>31</v>
-      </c>
-      <c r="O345" t="n">
-        <v>14</v>
-      </c>
-      <c r="P345" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q345" t="n">
-        <v>14</v>
-      </c>
-      <c r="R345" t="n">
-        <v>24</v>
-      </c>
-      <c r="S345" t="n">
-        <v>20</v>
-      </c>
-      <c r="T345" t="n">
-        <v>4</v>
-      </c>
-      <c r="U345" t="inlineStr">
-        <is>
-          <t>2487751</t>
-        </is>
-      </c>
-      <c r="V345" t="n">
-        <v>74</v>
-      </c>
-      <c r="W345" t="n">
-        <v>95.68000000000001</v>
-      </c>
-      <c r="X345" t="n">
-        <v>0.8570234113712374</v>
-      </c>
-      <c r="Y345" t="n">
-        <v>82.68000000000001</v>
-      </c>
-      <c r="Z345" t="n">
-        <v>99.17755200774067</v>
-      </c>
-      <c r="AA345" t="n">
-        <v>0.7753562447611064</v>
-      </c>
-      <c r="AB345" t="n">
-        <v>87.63619137849361</v>
-      </c>
-      <c r="AC345" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD345" t="n">
-        <v>0.7380952380952381</v>
-      </c>
-      <c r="AE345" t="n">
-        <v>0.5432098765432098</v>
-      </c>
-      <c r="AF345" t="n">
-        <v>11.54136062924707</v>
-      </c>
-      <c r="AG345" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="AH345" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="AI345" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B346" t="n">
-        <v>25</v>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="E346" t="n">
-        <v>200</v>
-      </c>
-      <c r="F346" t="n">
-        <v>51</v>
-      </c>
-      <c r="G346" t="n">
-        <v>13</v>
-      </c>
-      <c r="H346" t="n">
-        <v>41</v>
-      </c>
-      <c r="I346" t="n">
-        <v>4</v>
-      </c>
-      <c r="J346" t="n">
-        <v>26</v>
-      </c>
-      <c r="K346" t="n">
-        <v>13</v>
-      </c>
-      <c r="L346" t="n">
-        <v>30</v>
-      </c>
-      <c r="M346" t="n">
-        <v>13</v>
-      </c>
-      <c r="N346" t="n">
-        <v>21</v>
-      </c>
-      <c r="O346" t="n">
-        <v>9</v>
-      </c>
-      <c r="P346" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q346" t="n">
-        <v>10</v>
-      </c>
-      <c r="R346" t="n">
-        <v>24</v>
-      </c>
-      <c r="S346" t="n">
-        <v>25</v>
-      </c>
-      <c r="T346" t="n">
-        <v>1</v>
-      </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>2487748</t>
-        </is>
-      </c>
-      <c r="V346" t="n">
-        <v>62</v>
-      </c>
-      <c r="W346" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="X346" t="n">
-        <v>0.565410199556541</v>
-      </c>
-      <c r="Y346" t="n">
-        <v>77.2</v>
-      </c>
-      <c r="Z346" t="n">
-        <v>66.06217616580311</v>
-      </c>
-      <c r="AA346" t="n">
-        <v>0.6837229819144243</v>
-      </c>
-      <c r="AB346" t="n">
-        <v>81.92389006342493</v>
-      </c>
-      <c r="AC346" t="n">
-        <v>0.2549019607843137</v>
-      </c>
-      <c r="AD346" t="n">
-        <v>0.5833333333333334</v>
-      </c>
-      <c r="AE346" t="n">
-        <v>0.3908045977011494</v>
-      </c>
-      <c r="AF346" t="n">
-        <v>-15.86171389762183</v>
-      </c>
-      <c r="AG346" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="AH346" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="AI346" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>25</v>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="E347" t="n">
-        <v>200</v>
-      </c>
-      <c r="F347" t="n">
-        <v>63</v>
-      </c>
-      <c r="G347" t="n">
-        <v>14</v>
-      </c>
-      <c r="H347" t="n">
-        <v>36</v>
-      </c>
-      <c r="I347" t="n">
-        <v>8</v>
-      </c>
-      <c r="J347" t="n">
-        <v>26</v>
-      </c>
-      <c r="K347" t="n">
-        <v>11</v>
-      </c>
-      <c r="L347" t="n">
-        <v>14</v>
-      </c>
-      <c r="M347" t="n">
-        <v>7</v>
-      </c>
-      <c r="N347" t="n">
-        <v>26</v>
-      </c>
-      <c r="O347" t="n">
-        <v>10</v>
-      </c>
-      <c r="P347" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q347" t="n">
-        <v>19</v>
-      </c>
-      <c r="R347" t="n">
-        <v>23</v>
-      </c>
-      <c r="S347" t="n">
-        <v>19</v>
-      </c>
-      <c r="T347" t="n">
-        <v>2</v>
-      </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="V347" t="n">
-        <v>70</v>
-      </c>
-      <c r="W347" t="n">
-        <v>87.16</v>
-      </c>
-      <c r="X347" t="n">
-        <v>0.7228086278109225</v>
-      </c>
-      <c r="Y347" t="n">
-        <v>80.16</v>
-      </c>
-      <c r="Z347" t="n">
-        <v>78.59281437125749</v>
-      </c>
-      <c r="AA347" t="n">
-        <v>0.8549096238397655</v>
-      </c>
-      <c r="AB347" t="n">
-        <v>91.05098855359002</v>
-      </c>
-      <c r="AC347" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AD347" t="n">
-        <v>0.8387096774193549</v>
-      </c>
-      <c r="AE347" t="n">
-        <v>0.559322033898305</v>
-      </c>
-      <c r="AF347" t="n">
-        <v>-12.45817418233253</v>
-      </c>
-      <c r="AG347" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="AI347" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B348" t="n">
-        <v>25</v>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="E348" t="n">
-        <v>200</v>
-      </c>
-      <c r="F348" t="n">
-        <v>91</v>
-      </c>
-      <c r="G348" t="n">
-        <v>27</v>
-      </c>
-      <c r="H348" t="n">
-        <v>43</v>
-      </c>
-      <c r="I348" t="n">
-        <v>9</v>
-      </c>
-      <c r="J348" t="n">
-        <v>23</v>
-      </c>
-      <c r="K348" t="n">
-        <v>10</v>
-      </c>
-      <c r="L348" t="n">
-        <v>17</v>
-      </c>
-      <c r="M348" t="n">
-        <v>7</v>
-      </c>
-      <c r="N348" t="n">
-        <v>29</v>
-      </c>
-      <c r="O348" t="n">
-        <v>29</v>
-      </c>
-      <c r="P348" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q348" t="n">
-        <v>15</v>
-      </c>
-      <c r="R348" t="n">
-        <v>18</v>
-      </c>
-      <c r="S348" t="n">
-        <v>18</v>
-      </c>
-      <c r="T348" t="n">
-        <v>4</v>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>2487747</t>
-        </is>
-      </c>
-      <c r="V348" t="n">
-        <v>61</v>
-      </c>
-      <c r="W348" t="n">
-        <v>88.48</v>
-      </c>
-      <c r="X348" t="n">
-        <v>1.028481012658228</v>
-      </c>
-      <c r="Y348" t="n">
-        <v>81.48</v>
-      </c>
-      <c r="Z348" t="n">
-        <v>111.6838487972509</v>
-      </c>
-      <c r="AA348" t="n">
-        <v>0.6280889621087314</v>
-      </c>
-      <c r="AB348" t="n">
-        <v>72.51545411317166</v>
-      </c>
-      <c r="AC348" t="n">
-        <v>0.2592592592592592</v>
-      </c>
-      <c r="AD348" t="n">
-        <v>0.6904761904761905</v>
-      </c>
-      <c r="AE348" t="n">
-        <v>0.5217391304347826</v>
-      </c>
-      <c r="AF348" t="n">
-        <v>39.1683946840792</v>
-      </c>
-      <c r="AG348" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="AH348" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="AI348" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>25</v>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="E349" t="n">
-        <v>200</v>
-      </c>
-      <c r="F349" t="n">
-        <v>62</v>
-      </c>
-      <c r="G349" t="n">
-        <v>20</v>
-      </c>
-      <c r="H349" t="n">
-        <v>37</v>
-      </c>
-      <c r="I349" t="n">
-        <v>3</v>
-      </c>
-      <c r="J349" t="n">
-        <v>27</v>
-      </c>
-      <c r="K349" t="n">
-        <v>13</v>
-      </c>
-      <c r="L349" t="n">
-        <v>22</v>
-      </c>
-      <c r="M349" t="n">
-        <v>15</v>
-      </c>
-      <c r="N349" t="n">
-        <v>38</v>
-      </c>
-      <c r="O349" t="n">
-        <v>11</v>
-      </c>
-      <c r="P349" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q349" t="n">
-        <v>17</v>
-      </c>
-      <c r="R349" t="n">
-        <v>25</v>
-      </c>
-      <c r="S349" t="n">
-        <v>23</v>
-      </c>
-      <c r="T349" t="n">
-        <v>2</v>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>2487748</t>
-        </is>
-      </c>
-      <c r="V349" t="n">
-        <v>51</v>
-      </c>
-      <c r="W349" t="n">
-        <v>90.68000000000001</v>
-      </c>
-      <c r="X349" t="n">
-        <v>0.6837229819144243</v>
-      </c>
-      <c r="Y349" t="n">
-        <v>75.68000000000001</v>
-      </c>
-      <c r="Z349" t="n">
-        <v>81.92389006342493</v>
-      </c>
-      <c r="AA349" t="n">
-        <v>0.565410199556541</v>
-      </c>
-      <c r="AB349" t="n">
-        <v>66.06217616580311</v>
-      </c>
-      <c r="AC349" t="n">
-        <v>0.4166666666666667</v>
-      </c>
-      <c r="AD349" t="n">
-        <v>0.7450980392156863</v>
-      </c>
-      <c r="AE349" t="n">
-        <v>0.6091954022988506</v>
-      </c>
-      <c r="AF349" t="n">
-        <v>15.86171389762183</v>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="AI349" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B350" t="n">
-        <v>25</v>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="E350" t="n">
-        <v>200</v>
-      </c>
-      <c r="F350" t="n">
-        <v>70</v>
-      </c>
-      <c r="G350" t="n">
-        <v>15</v>
-      </c>
-      <c r="H350" t="n">
-        <v>35</v>
-      </c>
-      <c r="I350" t="n">
-        <v>6</v>
-      </c>
-      <c r="J350" t="n">
-        <v>22</v>
-      </c>
-      <c r="K350" t="n">
-        <v>22</v>
-      </c>
-      <c r="L350" t="n">
-        <v>27</v>
-      </c>
-      <c r="M350" t="n">
-        <v>5</v>
-      </c>
-      <c r="N350" t="n">
-        <v>21</v>
-      </c>
-      <c r="O350" t="n">
-        <v>8</v>
-      </c>
-      <c r="P350" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q350" t="n">
-        <v>13</v>
-      </c>
-      <c r="R350" t="n">
-        <v>19</v>
-      </c>
-      <c r="S350" t="n">
-        <v>23</v>
-      </c>
-      <c r="T350" t="n">
-        <v>2</v>
-      </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>2487746</t>
-        </is>
-      </c>
-      <c r="V350" t="n">
-        <v>63</v>
-      </c>
-      <c r="W350" t="n">
-        <v>81.88</v>
-      </c>
-      <c r="X350" t="n">
-        <v>0.8549096238397655</v>
-      </c>
-      <c r="Y350" t="n">
-        <v>76.88</v>
-      </c>
-      <c r="Z350" t="n">
-        <v>91.05098855359002</v>
-      </c>
-      <c r="AA350" t="n">
-        <v>0.7228086278109225</v>
-      </c>
-      <c r="AB350" t="n">
-        <v>78.59281437125749</v>
-      </c>
-      <c r="AC350" t="n">
-        <v>0.1612903225806452</v>
-      </c>
-      <c r="AD350" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AE350" t="n">
-        <v>0.4406779661016949</v>
-      </c>
-      <c r="AF350" t="n">
-        <v>12.45817418233253</v>
-      </c>
-      <c r="AG350" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="AH350" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="AI350" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B351" t="n">
-        <v>25</v>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="E351" t="n">
-        <v>225</v>
-      </c>
-      <c r="F351" t="n">
-        <v>71</v>
-      </c>
-      <c r="G351" t="n">
-        <v>15</v>
-      </c>
-      <c r="H351" t="n">
-        <v>48</v>
-      </c>
-      <c r="I351" t="n">
-        <v>6</v>
-      </c>
-      <c r="J351" t="n">
-        <v>31</v>
-      </c>
-      <c r="K351" t="n">
-        <v>23</v>
-      </c>
-      <c r="L351" t="n">
-        <v>30</v>
-      </c>
-      <c r="M351" t="n">
-        <v>18</v>
-      </c>
-      <c r="N351" t="n">
-        <v>34</v>
-      </c>
-      <c r="O351" t="n">
-        <v>13</v>
-      </c>
-      <c r="P351" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q351" t="n">
-        <v>17</v>
-      </c>
-      <c r="R351" t="n">
-        <v>20</v>
-      </c>
-      <c r="S351" t="n">
-        <v>25</v>
-      </c>
-      <c r="T351" t="n">
-        <v>0</v>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>2487750</t>
-        </is>
-      </c>
-      <c r="V351" t="n">
-        <v>69</v>
-      </c>
-      <c r="W351" t="n">
-        <v>109.2</v>
-      </c>
-      <c r="X351" t="n">
-        <v>0.6501831501831502</v>
-      </c>
-      <c r="Y351" t="n">
-        <v>91.2</v>
-      </c>
-      <c r="Z351" t="n">
-        <v>77.85087719298245</v>
-      </c>
-      <c r="AA351" t="n">
-        <v>0.6820877817319099</v>
-      </c>
-      <c r="AB351" t="n">
-        <v>81.0239549084077</v>
-      </c>
-      <c r="AC351" t="n">
-        <v>0.3272727272727273</v>
-      </c>
-      <c r="AD351" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="AE351" t="n">
-        <v>0.4952380952380953</v>
-      </c>
-      <c r="AF351" t="n">
-        <v>-3.173077715425251</v>
-      </c>
-      <c r="AG351" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="AH351" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="AI351" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B352" t="n">
-        <v>26</v>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="E352" t="n">
-        <v>200</v>
-      </c>
-      <c r="F352" t="n">
-        <v>79</v>
-      </c>
-      <c r="G352" t="n">
-        <v>19</v>
-      </c>
-      <c r="H352" t="n">
-        <v>36</v>
-      </c>
-      <c r="I352" t="n">
-        <v>7</v>
-      </c>
-      <c r="J352" t="n">
-        <v>20</v>
-      </c>
-      <c r="K352" t="n">
-        <v>20</v>
-      </c>
-      <c r="L352" t="n">
-        <v>33</v>
-      </c>
-      <c r="M352" t="n">
-        <v>4</v>
-      </c>
-      <c r="N352" t="n">
-        <v>29</v>
-      </c>
-      <c r="O352" t="n">
-        <v>14</v>
-      </c>
-      <c r="P352" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q352" t="n">
-        <v>21</v>
-      </c>
-      <c r="R352" t="n">
-        <v>23</v>
-      </c>
-      <c r="S352" t="n">
-        <v>23</v>
-      </c>
-      <c r="T352" t="n">
-        <v>1</v>
-      </c>
-      <c r="U352" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="V352" t="n">
-        <v>82</v>
-      </c>
-      <c r="W352" t="n">
-        <v>91.52</v>
-      </c>
-      <c r="X352" t="n">
-        <v>0.8631993006993007</v>
-      </c>
-      <c r="Y352" t="n">
-        <v>87.52</v>
-      </c>
-      <c r="Z352" t="n">
-        <v>90.26508226691043</v>
-      </c>
-      <c r="AA352" t="n">
-        <v>0.8979413053000439</v>
-      </c>
-      <c r="AB352" t="n">
-        <v>98.41574651944312</v>
-      </c>
-      <c r="AC352" t="n">
-        <v>0.1379310344827586</v>
-      </c>
-      <c r="AD352" t="n">
-        <v>0.7837837837837838</v>
-      </c>
-      <c r="AE352" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF352" t="n">
-        <v>-8.150664252532692</v>
-      </c>
-      <c r="AG352" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="AH352" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="AI352" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B353" t="n">
-        <v>26</v>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="E353" t="n">
-        <v>200</v>
-      </c>
-      <c r="F353" t="n">
-        <v>71</v>
-      </c>
-      <c r="G353" t="n">
-        <v>19</v>
-      </c>
-      <c r="H353" t="n">
-        <v>42</v>
-      </c>
-      <c r="I353" t="n">
-        <v>7</v>
-      </c>
-      <c r="J353" t="n">
-        <v>31</v>
-      </c>
-      <c r="K353" t="n">
-        <v>12</v>
-      </c>
-      <c r="L353" t="n">
-        <v>16</v>
-      </c>
-      <c r="M353" t="n">
-        <v>8</v>
-      </c>
-      <c r="N353" t="n">
-        <v>26</v>
-      </c>
-      <c r="O353" t="n">
-        <v>16</v>
-      </c>
-      <c r="P353" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q353" t="n">
-        <v>6</v>
-      </c>
-      <c r="R353" t="n">
-        <v>17</v>
-      </c>
-      <c r="S353" t="n">
-        <v>20</v>
-      </c>
-      <c r="T353" t="n">
-        <v>0</v>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>2487757</t>
-        </is>
-      </c>
-      <c r="V353" t="n">
-        <v>81</v>
-      </c>
-      <c r="W353" t="n">
-        <v>86.03999999999999</v>
-      </c>
-      <c r="X353" t="n">
-        <v>0.8251975825197583</v>
-      </c>
-      <c r="Y353" t="n">
-        <v>78.03999999999999</v>
-      </c>
-      <c r="Z353" t="n">
-        <v>90.97898513582778</v>
-      </c>
-      <c r="AA353" t="n">
-        <v>0.9259259259259259</v>
-      </c>
-      <c r="AB353" t="n">
-        <v>101.9124308002013</v>
-      </c>
-      <c r="AC353" t="n">
-        <v>0.1904761904761905</v>
-      </c>
-      <c r="AD353" t="n">
-        <v>0.7647058823529411</v>
-      </c>
-      <c r="AE353" t="n">
-        <v>0.4473684210526316</v>
-      </c>
-      <c r="AF353" t="n">
-        <v>-10.93344566437352</v>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="AI353" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>26</v>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="E354" t="n">
-        <v>200</v>
-      </c>
-      <c r="F354" t="n">
-        <v>86</v>
-      </c>
-      <c r="G354" t="n">
-        <v>22</v>
-      </c>
-      <c r="H354" t="n">
-        <v>40</v>
-      </c>
-      <c r="I354" t="n">
-        <v>7</v>
-      </c>
-      <c r="J354" t="n">
-        <v>28</v>
-      </c>
-      <c r="K354" t="n">
-        <v>21</v>
-      </c>
-      <c r="L354" t="n">
-        <v>36</v>
-      </c>
-      <c r="M354" t="n">
-        <v>14</v>
-      </c>
-      <c r="N354" t="n">
-        <v>24</v>
-      </c>
-      <c r="O354" t="n">
-        <v>12</v>
-      </c>
-      <c r="P354" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q354" t="n">
-        <v>17</v>
-      </c>
-      <c r="R354" t="n">
-        <v>21</v>
-      </c>
-      <c r="S354" t="n">
-        <v>26</v>
-      </c>
-      <c r="T354" t="n">
-        <v>0</v>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="V354" t="n">
-        <v>94</v>
-      </c>
-      <c r="W354" t="n">
-        <v>100.84</v>
-      </c>
-      <c r="X354" t="n">
-        <v>0.852836176120587</v>
-      </c>
-      <c r="Y354" t="n">
-        <v>86.84</v>
-      </c>
-      <c r="Z354" t="n">
-        <v>99.03270382312299</v>
-      </c>
-      <c r="AA354" t="n">
-        <v>1.026649191786806</v>
-      </c>
-      <c r="AB354" t="n">
-        <v>119.6537678207739</v>
-      </c>
-      <c r="AC354" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="AD354" t="n">
-        <v>0.6486486486486487</v>
-      </c>
-      <c r="AE354" t="n">
-        <v>0.5205479452054794</v>
-      </c>
-      <c r="AF354" t="n">
-        <v>-20.62106399765094</v>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="AI354" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>26</v>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="E355" t="n">
-        <v>200</v>
-      </c>
-      <c r="F355" t="n">
-        <v>82</v>
-      </c>
-      <c r="G355" t="n">
-        <v>18</v>
-      </c>
-      <c r="H355" t="n">
-        <v>35</v>
-      </c>
-      <c r="I355" t="n">
-        <v>7</v>
-      </c>
-      <c r="J355" t="n">
-        <v>23</v>
-      </c>
-      <c r="K355" t="n">
-        <v>25</v>
-      </c>
-      <c r="L355" t="n">
-        <v>28</v>
-      </c>
-      <c r="M355" t="n">
-        <v>5</v>
-      </c>
-      <c r="N355" t="n">
-        <v>22</v>
-      </c>
-      <c r="O355" t="n">
-        <v>12</v>
-      </c>
-      <c r="P355" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q355" t="n">
-        <v>24</v>
-      </c>
-      <c r="R355" t="n">
-        <v>28</v>
-      </c>
-      <c r="S355" t="n">
-        <v>26</v>
-      </c>
-      <c r="T355" t="n">
-        <v>2</v>
-      </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>2487753</t>
-        </is>
-      </c>
-      <c r="V355" t="n">
-        <v>102</v>
-      </c>
-      <c r="W355" t="n">
-        <v>94.31999999999999</v>
-      </c>
-      <c r="X355" t="n">
-        <v>0.8693808312128923</v>
-      </c>
-      <c r="Y355" t="n">
-        <v>89.31999999999999</v>
-      </c>
-      <c r="Z355" t="n">
-        <v>91.80474697716078</v>
-      </c>
-      <c r="AA355" t="n">
-        <v>1.043371522094926</v>
-      </c>
-      <c r="AB355" t="n">
-        <v>121.7765042979943</v>
-      </c>
-      <c r="AC355" t="n">
-        <v>0.15625</v>
-      </c>
-      <c r="AD355" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="AE355" t="n">
-        <v>0.3970588235294117</v>
-      </c>
-      <c r="AF355" t="n">
-        <v>-29.9717573208335</v>
-      </c>
-      <c r="AG355" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="AI355" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>26</v>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="E356" t="n">
-        <v>200</v>
-      </c>
-      <c r="F356" t="n">
-        <v>65</v>
-      </c>
-      <c r="G356" t="n">
-        <v>14</v>
-      </c>
-      <c r="H356" t="n">
-        <v>28</v>
-      </c>
-      <c r="I356" t="n">
-        <v>11</v>
-      </c>
-      <c r="J356" t="n">
-        <v>34</v>
-      </c>
-      <c r="K356" t="n">
-        <v>4</v>
-      </c>
-      <c r="L356" t="n">
-        <v>13</v>
-      </c>
-      <c r="M356" t="n">
-        <v>10</v>
-      </c>
-      <c r="N356" t="n">
-        <v>27</v>
-      </c>
-      <c r="O356" t="n">
-        <v>12</v>
-      </c>
-      <c r="P356" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q356" t="n">
-        <v>12</v>
-      </c>
-      <c r="R356" t="n">
-        <v>18</v>
-      </c>
-      <c r="S356" t="n">
-        <v>15</v>
-      </c>
-      <c r="T356" t="n">
-        <v>5</v>
-      </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>2487755</t>
-        </is>
-      </c>
-      <c r="V356" t="n">
-        <v>47</v>
-      </c>
-      <c r="W356" t="n">
-        <v>79.72</v>
-      </c>
-      <c r="X356" t="n">
-        <v>0.8153537380832915</v>
-      </c>
-      <c r="Y356" t="n">
-        <v>69.72</v>
-      </c>
-      <c r="Z356" t="n">
-        <v>93.23006310958118</v>
-      </c>
-      <c r="AA356" t="n">
-        <v>0.5831265508684864</v>
-      </c>
-      <c r="AB356" t="n">
-        <v>67.52873563218391</v>
-      </c>
-      <c r="AC356" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="AD356" t="n">
-        <v>0.7105263157894737</v>
-      </c>
-      <c r="AE356" t="n">
-        <v>0.4805194805194805</v>
-      </c>
-      <c r="AF356" t="n">
-        <v>25.70132747739727</v>
-      </c>
-      <c r="AG356" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="AI356" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>26</v>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="E357" t="n">
-        <v>200</v>
-      </c>
-      <c r="F357" t="n">
-        <v>82</v>
-      </c>
-      <c r="G357" t="n">
-        <v>19</v>
-      </c>
-      <c r="H357" t="n">
-        <v>43</v>
-      </c>
-      <c r="I357" t="n">
-        <v>9</v>
-      </c>
-      <c r="J357" t="n">
-        <v>25</v>
-      </c>
-      <c r="K357" t="n">
-        <v>17</v>
-      </c>
-      <c r="L357" t="n">
-        <v>28</v>
-      </c>
-      <c r="M357" t="n">
-        <v>8</v>
-      </c>
-      <c r="N357" t="n">
-        <v>25</v>
-      </c>
-      <c r="O357" t="n">
-        <v>16</v>
-      </c>
-      <c r="P357" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q357" t="n">
-        <v>11</v>
-      </c>
-      <c r="R357" t="n">
-        <v>23</v>
-      </c>
-      <c r="S357" t="n">
-        <v>22</v>
-      </c>
-      <c r="T357" t="n">
-        <v>5</v>
-      </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>2487754</t>
-        </is>
-      </c>
-      <c r="V357" t="n">
-        <v>79</v>
-      </c>
-      <c r="W357" t="n">
-        <v>91.31999999999999</v>
-      </c>
-      <c r="X357" t="n">
-        <v>0.8979413053000439</v>
-      </c>
-      <c r="Y357" t="n">
-        <v>83.31999999999999</v>
-      </c>
-      <c r="Z357" t="n">
-        <v>98.41574651944312</v>
-      </c>
-      <c r="AA357" t="n">
-        <v>0.8631993006993007</v>
-      </c>
-      <c r="AB357" t="n">
-        <v>90.26508226691043</v>
-      </c>
-      <c r="AC357" t="n">
-        <v>0.2162162162162162</v>
-      </c>
-      <c r="AD357" t="n">
-        <v>0.8620689655172413</v>
-      </c>
-      <c r="AE357" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AF357" t="n">
-        <v>8.150664252532692</v>
-      </c>
-      <c r="AG357" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
-        </is>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>C.B. TRES CANTOS</t>
-        </is>
-      </c>
-      <c r="AI357" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>26</v>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="E358" t="n">
-        <v>200</v>
-      </c>
-      <c r="F358" t="n">
-        <v>77</v>
-      </c>
-      <c r="G358" t="n">
-        <v>17</v>
-      </c>
-      <c r="H358" t="n">
-        <v>38</v>
-      </c>
-      <c r="I358" t="n">
-        <v>6</v>
-      </c>
-      <c r="J358" t="n">
-        <v>27</v>
-      </c>
-      <c r="K358" t="n">
-        <v>25</v>
-      </c>
-      <c r="L358" t="n">
-        <v>36</v>
-      </c>
-      <c r="M358" t="n">
-        <v>18</v>
-      </c>
-      <c r="N358" t="n">
-        <v>34</v>
-      </c>
-      <c r="O358" t="n">
-        <v>10</v>
-      </c>
-      <c r="P358" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q358" t="n">
-        <v>15</v>
-      </c>
-      <c r="R358" t="n">
-        <v>16</v>
-      </c>
-      <c r="S358" t="n">
-        <v>25</v>
-      </c>
-      <c r="T358" t="n">
-        <v>1</v>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="V358" t="n">
-        <v>74</v>
-      </c>
-      <c r="W358" t="n">
-        <v>95.84</v>
-      </c>
-      <c r="X358" t="n">
-        <v>0.8034223706176962</v>
-      </c>
-      <c r="Y358" t="n">
-        <v>77.84</v>
-      </c>
-      <c r="Z358" t="n">
-        <v>98.92086330935251</v>
-      </c>
-      <c r="AA358" t="n">
-        <v>0.780261493040911</v>
-      </c>
-      <c r="AB358" t="n">
-        <v>96.30400832899531</v>
-      </c>
-      <c r="AC358" t="n">
-        <v>0.4285714285714285</v>
-      </c>
-      <c r="AD358" t="n">
-        <v>0.6538461538461539</v>
-      </c>
-      <c r="AE358" t="n">
-        <v>0.5531914893617021</v>
-      </c>
-      <c r="AF358" t="n">
-        <v>2.616854980357203</v>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="AI358" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>26</v>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="E359" t="n">
-        <v>200</v>
-      </c>
-      <c r="F359" t="n">
-        <v>94</v>
-      </c>
-      <c r="G359" t="n">
-        <v>19</v>
-      </c>
-      <c r="H359" t="n">
-        <v>37</v>
-      </c>
-      <c r="I359" t="n">
-        <v>12</v>
-      </c>
-      <c r="J359" t="n">
-        <v>32</v>
-      </c>
-      <c r="K359" t="n">
-        <v>20</v>
-      </c>
-      <c r="L359" t="n">
-        <v>24</v>
-      </c>
-      <c r="M359" t="n">
-        <v>13</v>
-      </c>
-      <c r="N359" t="n">
-        <v>22</v>
-      </c>
-      <c r="O359" t="n">
-        <v>13</v>
-      </c>
-      <c r="P359" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q359" t="n">
-        <v>12</v>
-      </c>
-      <c r="R359" t="n">
-        <v>32</v>
-      </c>
-      <c r="S359" t="n">
-        <v>19</v>
-      </c>
-      <c r="T359" t="n">
-        <v>0</v>
-      </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>2487752</t>
-        </is>
-      </c>
-      <c r="V359" t="n">
-        <v>86</v>
-      </c>
-      <c r="W359" t="n">
-        <v>91.56</v>
-      </c>
-      <c r="X359" t="n">
-        <v>1.026649191786806</v>
-      </c>
-      <c r="Y359" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="Z359" t="n">
-        <v>119.6537678207739</v>
-      </c>
-      <c r="AA359" t="n">
-        <v>0.852836176120587</v>
-      </c>
-      <c r="AB359" t="n">
-        <v>99.03270382312299</v>
-      </c>
-      <c r="AC359" t="n">
-        <v>0.3513513513513514</v>
-      </c>
-      <c r="AD359" t="n">
-        <v>0.6111111111111112</v>
-      </c>
-      <c r="AE359" t="n">
-        <v>0.4794520547945205</v>
-      </c>
-      <c r="AF359" t="n">
-        <v>20.62106399765094</v>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>EB FELIPE ANTÓN</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>BALONCESTO TALAVERA</t>
-        </is>
-      </c>
-      <c r="AI359" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>26</v>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="E360" t="n">
-        <v>200</v>
-      </c>
-      <c r="F360" t="n">
-        <v>75</v>
-      </c>
-      <c r="G360" t="n">
-        <v>18</v>
-      </c>
-      <c r="H360" t="n">
-        <v>40</v>
-      </c>
-      <c r="I360" t="n">
-        <v>7</v>
-      </c>
-      <c r="J360" t="n">
-        <v>21</v>
-      </c>
-      <c r="K360" t="n">
-        <v>18</v>
-      </c>
-      <c r="L360" t="n">
-        <v>24</v>
-      </c>
-      <c r="M360" t="n">
-        <v>7</v>
-      </c>
-      <c r="N360" t="n">
-        <v>23</v>
-      </c>
-      <c r="O360" t="n">
-        <v>17</v>
-      </c>
-      <c r="P360" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q360" t="n">
-        <v>17</v>
-      </c>
-      <c r="R360" t="n">
-        <v>23</v>
-      </c>
-      <c r="S360" t="n">
-        <v>20</v>
-      </c>
-      <c r="T360" t="n">
-        <v>3</v>
-      </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="V360" t="n">
-        <v>76</v>
-      </c>
-      <c r="W360" t="n">
-        <v>88.56</v>
-      </c>
-      <c r="X360" t="n">
-        <v>0.8468834688346883</v>
-      </c>
-      <c r="Y360" t="n">
-        <v>81.56</v>
-      </c>
-      <c r="Z360" t="n">
-        <v>91.95684158901422</v>
-      </c>
-      <c r="AA360" t="n">
-        <v>0.7923269391159299</v>
-      </c>
-      <c r="AB360" t="n">
-        <v>91.65460684997588</v>
-      </c>
-      <c r="AC360" t="n">
-        <v>0.1842105263157895</v>
-      </c>
-      <c r="AD360" t="n">
-        <v>0.6388888888888888</v>
-      </c>
-      <c r="AE360" t="n">
-        <v>0.4054054054054054</v>
-      </c>
-      <c r="AF360" t="n">
-        <v>0.3022347390383402</v>
-      </c>
-      <c r="AG360" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="AI360" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B361" t="n">
-        <v>26</v>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="E361" t="n">
-        <v>200</v>
-      </c>
-      <c r="F361" t="n">
-        <v>81</v>
-      </c>
-      <c r="G361" t="n">
-        <v>24</v>
-      </c>
-      <c r="H361" t="n">
-        <v>46</v>
-      </c>
-      <c r="I361" t="n">
-        <v>8</v>
-      </c>
-      <c r="J361" t="n">
-        <v>21</v>
-      </c>
-      <c r="K361" t="n">
-        <v>9</v>
-      </c>
-      <c r="L361" t="n">
-        <v>17</v>
-      </c>
-      <c r="M361" t="n">
-        <v>8</v>
-      </c>
-      <c r="N361" t="n">
-        <v>34</v>
-      </c>
-      <c r="O361" t="n">
-        <v>15</v>
-      </c>
-      <c r="P361" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q361" t="n">
-        <v>13</v>
-      </c>
-      <c r="R361" t="n">
-        <v>20</v>
-      </c>
-      <c r="S361" t="n">
-        <v>17</v>
-      </c>
-      <c r="T361" t="n">
-        <v>3</v>
-      </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>2487757</t>
-        </is>
-      </c>
-      <c r="V361" t="n">
-        <v>71</v>
-      </c>
-      <c r="W361" t="n">
-        <v>87.48</v>
-      </c>
-      <c r="X361" t="n">
-        <v>0.9259259259259259</v>
-      </c>
-      <c r="Y361" t="n">
-        <v>79.48</v>
-      </c>
-      <c r="Z361" t="n">
-        <v>101.9124308002013</v>
-      </c>
-      <c r="AA361" t="n">
-        <v>0.8251975825197583</v>
-      </c>
-      <c r="AB361" t="n">
-        <v>90.97898513582778</v>
-      </c>
-      <c r="AC361" t="n">
-        <v>0.2352941176470588</v>
-      </c>
-      <c r="AD361" t="n">
-        <v>0.8095238095238095</v>
-      </c>
-      <c r="AE361" t="n">
-        <v>0.5526315789473685</v>
-      </c>
-      <c r="AF361" t="n">
-        <v>10.93344566437352</v>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
-        </is>
-      </c>
-      <c r="AI361" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B362" t="n">
-        <v>26</v>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="E362" t="n">
-        <v>200</v>
-      </c>
-      <c r="F362" t="n">
-        <v>76</v>
-      </c>
-      <c r="G362" t="n">
-        <v>19</v>
-      </c>
-      <c r="H362" t="n">
-        <v>37</v>
-      </c>
-      <c r="I362" t="n">
-        <v>9</v>
-      </c>
-      <c r="J362" t="n">
-        <v>33</v>
-      </c>
-      <c r="K362" t="n">
-        <v>11</v>
-      </c>
-      <c r="L362" t="n">
-        <v>18</v>
-      </c>
-      <c r="M362" t="n">
-        <v>13</v>
-      </c>
-      <c r="N362" t="n">
-        <v>31</v>
-      </c>
-      <c r="O362" t="n">
-        <v>17</v>
-      </c>
-      <c r="P362" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q362" t="n">
-        <v>18</v>
-      </c>
-      <c r="R362" t="n">
-        <v>21</v>
-      </c>
-      <c r="S362" t="n">
-        <v>22</v>
-      </c>
-      <c r="T362" t="n">
-        <v>2</v>
-      </c>
-      <c r="U362" t="inlineStr">
-        <is>
-          <t>2487756</t>
-        </is>
-      </c>
-      <c r="V362" t="n">
-        <v>75</v>
-      </c>
-      <c r="W362" t="n">
-        <v>95.92</v>
-      </c>
-      <c r="X362" t="n">
-        <v>0.7923269391159299</v>
-      </c>
-      <c r="Y362" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="Z362" t="n">
-        <v>91.65460684997588</v>
-      </c>
-      <c r="AA362" t="n">
-        <v>0.8468834688346883</v>
-      </c>
-      <c r="AB362" t="n">
-        <v>91.95684158901422</v>
-      </c>
-      <c r="AC362" t="n">
-        <v>0.3611111111111111</v>
-      </c>
-      <c r="AD362" t="n">
-        <v>0.8157894736842105</v>
-      </c>
-      <c r="AE362" t="n">
-        <v>0.5945945945945946</v>
-      </c>
-      <c r="AF362" t="n">
-        <v>-0.3022347390383402</v>
-      </c>
-      <c r="AG362" t="inlineStr">
-        <is>
-          <t>REAL CANOE N.C.</t>
-        </is>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="AI362" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B363" t="n">
-        <v>26</v>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="E363" t="n">
-        <v>200</v>
-      </c>
-      <c r="F363" t="n">
-        <v>47</v>
-      </c>
-      <c r="G363" t="n">
-        <v>15</v>
-      </c>
-      <c r="H363" t="n">
-        <v>36</v>
-      </c>
-      <c r="I363" t="n">
-        <v>3</v>
-      </c>
-      <c r="J363" t="n">
-        <v>21</v>
-      </c>
-      <c r="K363" t="n">
-        <v>8</v>
-      </c>
-      <c r="L363" t="n">
-        <v>15</v>
-      </c>
-      <c r="M363" t="n">
-        <v>11</v>
-      </c>
-      <c r="N363" t="n">
-        <v>29</v>
-      </c>
-      <c r="O363" t="n">
-        <v>7</v>
-      </c>
-      <c r="P363" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q363" t="n">
-        <v>17</v>
-      </c>
-      <c r="R363" t="n">
-        <v>15</v>
-      </c>
-      <c r="S363" t="n">
-        <v>18</v>
-      </c>
-      <c r="T363" t="n">
-        <v>0</v>
-      </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>2487755</t>
-        </is>
-      </c>
-      <c r="V363" t="n">
-        <v>65</v>
-      </c>
-      <c r="W363" t="n">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="X363" t="n">
-        <v>0.5831265508684864</v>
-      </c>
-      <c r="Y363" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="Z363" t="n">
-        <v>67.52873563218391</v>
-      </c>
-      <c r="AA363" t="n">
-        <v>0.8153537380832915</v>
-      </c>
-      <c r="AB363" t="n">
-        <v>93.23006310958118</v>
-      </c>
-      <c r="AC363" t="n">
-        <v>0.2894736842105263</v>
-      </c>
-      <c r="AD363" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="AE363" t="n">
-        <v>0.5194805194805194</v>
-      </c>
-      <c r="AF363" t="n">
-        <v>-25.70132747739727</v>
-      </c>
-      <c r="AG363" t="inlineStr">
-        <is>
-          <t>RECUCYM BAZU</t>
-        </is>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
-        </is>
-      </c>
-      <c r="AI363" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B364" t="n">
-        <v>26</v>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="E364" t="n">
-        <v>200</v>
-      </c>
-      <c r="F364" t="n">
-        <v>74</v>
-      </c>
-      <c r="G364" t="n">
-        <v>20</v>
-      </c>
-      <c r="H364" t="n">
-        <v>45</v>
-      </c>
-      <c r="I364" t="n">
-        <v>9</v>
-      </c>
-      <c r="J364" t="n">
-        <v>42</v>
-      </c>
-      <c r="K364" t="n">
-        <v>7</v>
-      </c>
-      <c r="L364" t="n">
-        <v>11</v>
-      </c>
-      <c r="M364" t="n">
-        <v>18</v>
-      </c>
-      <c r="N364" t="n">
-        <v>24</v>
-      </c>
-      <c r="O364" t="n">
-        <v>17</v>
-      </c>
-      <c r="P364" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q364" t="n">
-        <v>3</v>
-      </c>
-      <c r="R364" t="n">
-        <v>25</v>
-      </c>
-      <c r="S364" t="n">
-        <v>16</v>
-      </c>
-      <c r="T364" t="n">
-        <v>2</v>
-      </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>2487758</t>
-        </is>
-      </c>
-      <c r="V364" t="n">
-        <v>77</v>
-      </c>
-      <c r="W364" t="n">
-        <v>94.84</v>
-      </c>
-      <c r="X364" t="n">
-        <v>0.780261493040911</v>
-      </c>
-      <c r="Y364" t="n">
-        <v>76.84</v>
-      </c>
-      <c r="Z364" t="n">
-        <v>96.30400832899531</v>
-      </c>
-      <c r="AA364" t="n">
-        <v>0.8034223706176962</v>
-      </c>
-      <c r="AB364" t="n">
-        <v>98.92086330935251</v>
-      </c>
-      <c r="AC364" t="n">
-        <v>0.3461538461538461</v>
-      </c>
-      <c r="AD364" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="AE364" t="n">
-        <v>0.4468085106382979</v>
-      </c>
-      <c r="AF364" t="n">
-        <v>-2.616854980357203</v>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>CB ARIDANE</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>UROS DE RIVAS</t>
-        </is>
-      </c>
-      <c r="AI364" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Liga Regular "B-B"</t>
-        </is>
-      </c>
-      <c r="B365" t="n">
-        <v>26</v>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="E365" t="n">
-        <v>200</v>
-      </c>
-      <c r="F365" t="n">
-        <v>102</v>
-      </c>
-      <c r="G365" t="n">
-        <v>23</v>
-      </c>
-      <c r="H365" t="n">
-        <v>38</v>
-      </c>
-      <c r="I365" t="n">
-        <v>11</v>
-      </c>
-      <c r="J365" t="n">
-        <v>30</v>
-      </c>
-      <c r="K365" t="n">
-        <v>23</v>
-      </c>
-      <c r="L365" t="n">
-        <v>29</v>
-      </c>
-      <c r="M365" t="n">
-        <v>14</v>
-      </c>
-      <c r="N365" t="n">
-        <v>27</v>
-      </c>
-      <c r="O365" t="n">
-        <v>18</v>
-      </c>
-      <c r="P365" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q365" t="n">
-        <v>17</v>
-      </c>
-      <c r="R365" t="n">
-        <v>26</v>
-      </c>
-      <c r="S365" t="n">
-        <v>28</v>
-      </c>
-      <c r="T365" t="n">
-        <v>0</v>
-      </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>2487753</t>
-        </is>
-      </c>
-      <c r="V365" t="n">
-        <v>82</v>
-      </c>
-      <c r="W365" t="n">
-        <v>97.75999999999999</v>
-      </c>
-      <c r="X365" t="n">
-        <v>1.043371522094926</v>
-      </c>
-      <c r="Y365" t="n">
-        <v>83.75999999999999</v>
-      </c>
-      <c r="Z365" t="n">
-        <v>121.7765042979943</v>
-      </c>
-      <c r="AA365" t="n">
-        <v>0.8693808312128923</v>
-      </c>
-      <c r="AB365" t="n">
-        <v>91.80474697716078</v>
-      </c>
-      <c r="AC365" t="n">
-        <v>0.3888888888888889</v>
-      </c>
-      <c r="AD365" t="n">
-        <v>0.84375</v>
-      </c>
-      <c r="AE365" t="n">
-        <v>0.6029411764705882</v>
-      </c>
-      <c r="AF365" t="n">
-        <v>29.9717573208335</v>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>ZENTRO BASKET MADRID</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>BALONCESTO TELDE</t>
-        </is>
-      </c>
-      <c r="AI365" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
+++ b/data/3FEB_25_26/players_25_26_3FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI329"/>
+  <dimension ref="A1:AI365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37625,112 +37625,112 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="E313" t="n">
         <v>200</v>
       </c>
       <c r="F313" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="G313" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H313" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I313" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J313" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="K313" t="n">
+        <v>16</v>
+      </c>
+      <c r="L313" t="n">
         <v>19</v>
       </c>
-      <c r="L313" t="n">
-        <v>23</v>
-      </c>
       <c r="M313" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N313" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="O313" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="P313" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="Q313" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="R313" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="S313" t="n">
         <v>18</v>
       </c>
       <c r="T313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487737</t>
         </is>
       </c>
       <c r="V313" t="n">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="W313" t="n">
-        <v>100.12</v>
+        <v>89.36</v>
       </c>
       <c r="X313" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.8840644583706356</v>
       </c>
       <c r="Y313" t="n">
-        <v>92.12</v>
+        <v>79.36</v>
       </c>
       <c r="Z313" t="n">
-        <v>94.44203213200173</v>
+        <v>99.54637096774194</v>
       </c>
       <c r="AA313" t="n">
-        <v>0.7657500870170554</v>
+        <v>1.047381546134663</v>
       </c>
       <c r="AB313" t="n">
-        <v>91.74311926605505</v>
+        <v>114.7540983606557</v>
       </c>
       <c r="AC313" t="n">
-        <v>0.2162162162162162</v>
+        <v>0.2702702702702703</v>
       </c>
       <c r="AD313" t="n">
-        <v>0.525</v>
+        <v>0.7878787878787878</v>
       </c>
       <c r="AE313" t="n">
-        <v>0.3766233766233766</v>
+        <v>0.5142857142857142</v>
       </c>
       <c r="AF313" t="n">
-        <v>2.698912865946681</v>
+        <v>-15.2077273929138</v>
       </c>
       <c r="AG313" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AH313" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI313" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
@@ -37744,108 +37744,108 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E314" t="n">
         <v>200</v>
       </c>
       <c r="F314" t="n">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="G314" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H314" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="I314" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="J314" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="K314" t="n">
         <v>29</v>
       </c>
       <c r="L314" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M314" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="N314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O314" t="n">
         <v>11</v>
       </c>
       <c r="P314" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Q314" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R314" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="S314" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="T314" t="n">
         <v>4</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>2487731</t>
+          <t>2487736</t>
         </is>
       </c>
       <c r="V314" t="n">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="W314" t="n">
-        <v>88.59999999999999</v>
+        <v>93.28</v>
       </c>
       <c r="X314" t="n">
-        <v>0.8465011286681716</v>
+        <v>0.9862778730703259</v>
       </c>
       <c r="Y314" t="n">
-        <v>80.59999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="Z314" t="n">
-        <v>93.05210918114145</v>
+        <v>111.8133203694701</v>
       </c>
       <c r="AA314" t="n">
-        <v>0.7302731411229135</v>
+        <v>1.01843910806175</v>
       </c>
       <c r="AB314" t="n">
-        <v>96.92849949647533</v>
+        <v>119.8284561049445</v>
       </c>
       <c r="AC314" t="n">
-        <v>0.25</v>
+        <v>0.275</v>
       </c>
       <c r="AD314" t="n">
-        <v>0.5094339622641509</v>
+        <v>0.65</v>
       </c>
       <c r="AE314" t="n">
-        <v>0.4117647058823529</v>
+        <v>0.4625</v>
       </c>
       <c r="AF314" t="n">
-        <v>-3.876390315333879</v>
+        <v>-8.015135735474388</v>
       </c>
       <c r="AG314" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AH314" t="inlineStr">
         <is>
-          <t>BALONCESTO TALAVERA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AI314" t="b">
@@ -37863,112 +37863,112 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="E315" t="n">
         <v>200</v>
       </c>
       <c r="F315" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="G315" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H315" t="n">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="I315" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J315" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K315" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L315" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M315" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N315" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="O315" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P315" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Q315" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="R315" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="S315" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T315" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487737</t>
         </is>
       </c>
       <c r="V315" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="W315" t="n">
-        <v>71.8</v>
+        <v>80.2</v>
       </c>
       <c r="X315" t="n">
-        <v>0.7103064066852368</v>
+        <v>1.047381546134663</v>
       </c>
       <c r="Y315" t="n">
-        <v>65.8</v>
+        <v>73.2</v>
       </c>
       <c r="Z315" t="n">
-        <v>77.50759878419453</v>
+        <v>114.7540983606557</v>
       </c>
       <c r="AA315" t="n">
-        <v>0.935288169868554</v>
+        <v>0.8840644583706356</v>
       </c>
       <c r="AB315" t="n">
-        <v>105.5333713633771</v>
+        <v>99.54637096774194</v>
       </c>
       <c r="AC315" t="n">
-        <v>0.1818181818181818</v>
+        <v>0.2121212121212121</v>
       </c>
       <c r="AD315" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.7297297297297297</v>
       </c>
       <c r="AE315" t="n">
-        <v>0.5</v>
+        <v>0.4857142857142857</v>
       </c>
       <c r="AF315" t="n">
-        <v>-28.02577257918253</v>
+        <v>15.2077273929138</v>
       </c>
       <c r="AG315" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="AH315" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI315" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
@@ -37982,108 +37982,108 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="E316" t="n">
         <v>200</v>
       </c>
       <c r="F316" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="G316" t="n">
+        <v>22</v>
+      </c>
+      <c r="H316" t="n">
+        <v>38</v>
+      </c>
+      <c r="I316" t="n">
+        <v>8</v>
+      </c>
+      <c r="J316" t="n">
+        <v>26</v>
+      </c>
+      <c r="K316" t="n">
+        <v>17</v>
+      </c>
+      <c r="L316" t="n">
+        <v>34</v>
+      </c>
+      <c r="M316" t="n">
         <v>13</v>
       </c>
-      <c r="H316" t="n">
-        <v>29</v>
-      </c>
-      <c r="I316" t="n">
-        <v>11</v>
-      </c>
-      <c r="J316" t="n">
-        <v>30</v>
-      </c>
-      <c r="K316" t="n">
-        <v>15</v>
-      </c>
-      <c r="L316" t="n">
-        <v>23</v>
-      </c>
-      <c r="M316" t="n">
-        <v>9</v>
-      </c>
       <c r="N316" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="O316" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="P316" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q316" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R316" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="S316" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T316" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
-          <t>2487733</t>
+          <t>2487732</t>
         </is>
       </c>
       <c r="V316" t="n">
-        <v>51</v>
+        <v>96</v>
       </c>
       <c r="W316" t="n">
-        <v>79.12</v>
+        <v>92.96000000000001</v>
       </c>
       <c r="X316" t="n">
-        <v>0.935288169868554</v>
+        <v>0.9143717728055076</v>
       </c>
       <c r="Y316" t="n">
-        <v>70.12</v>
+        <v>79.96000000000001</v>
       </c>
       <c r="Z316" t="n">
-        <v>105.5333713633771</v>
+        <v>106.3031515757879</v>
       </c>
       <c r="AA316" t="n">
-        <v>0.7103064066852368</v>
+        <v>1.049868766404199</v>
       </c>
       <c r="AB316" t="n">
-        <v>77.50759878419453</v>
+        <v>116.448326055313</v>
       </c>
       <c r="AC316" t="n">
-        <v>0.2307692307692308</v>
+        <v>0.3611111111111111</v>
       </c>
       <c r="AD316" t="n">
-        <v>0.8181818181818182</v>
+        <v>0.7096774193548387</v>
       </c>
       <c r="AE316" t="n">
-        <v>0.5</v>
+        <v>0.5223880597014925</v>
       </c>
       <c r="AF316" t="n">
-        <v>28.02577257918253</v>
+        <v>-10.14517447952508</v>
       </c>
       <c r="AG316" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AH316" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="AI316" t="b">
@@ -38101,108 +38101,108 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="E317" t="n">
         <v>200</v>
       </c>
       <c r="F317" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G317" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H317" t="n">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="I317" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J317" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K317" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L317" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="M317" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="N317" t="n">
         <v>29</v>
       </c>
       <c r="O317" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="P317" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Q317" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="R317" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="S317" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="T317" t="n">
         <v>4</v>
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>2487735</t>
+          <t>2487736</t>
         </is>
       </c>
       <c r="V317" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="W317" t="n">
-        <v>114.92</v>
+        <v>93.28</v>
       </c>
       <c r="X317" t="n">
-        <v>0.7657500870170554</v>
+        <v>1.01843910806175</v>
       </c>
       <c r="Y317" t="n">
-        <v>95.92</v>
+        <v>79.28</v>
       </c>
       <c r="Z317" t="n">
-        <v>91.74311926605505</v>
+        <v>119.8284561049445</v>
       </c>
       <c r="AA317" t="n">
-        <v>0.8689572512984418</v>
+        <v>0.9862778730703259</v>
       </c>
       <c r="AB317" t="n">
-        <v>94.44203213200173</v>
+        <v>111.8133203694701</v>
       </c>
       <c r="AC317" t="n">
-        <v>0.475</v>
+        <v>0.35</v>
       </c>
       <c r="AD317" t="n">
-        <v>0.7837837837837838</v>
+        <v>0.725</v>
       </c>
       <c r="AE317" t="n">
-        <v>0.6233766233766234</v>
+        <v>0.5375</v>
       </c>
       <c r="AF317" t="n">
-        <v>-2.698912865946681</v>
+        <v>8.015135735474388</v>
       </c>
       <c r="AG317" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AH317" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="AI317" t="b">
@@ -38216,112 +38216,112 @@
         </is>
       </c>
       <c r="B318" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E318" t="n">
         <v>200</v>
       </c>
       <c r="F318" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="G318" t="n">
+        <v>25</v>
+      </c>
+      <c r="H318" t="n">
+        <v>48</v>
+      </c>
+      <c r="I318" t="n">
+        <v>6</v>
+      </c>
+      <c r="J318" t="n">
+        <v>22</v>
+      </c>
+      <c r="K318" t="n">
+        <v>19</v>
+      </c>
+      <c r="L318" t="n">
         <v>23</v>
       </c>
-      <c r="H318" t="n">
-        <v>53</v>
-      </c>
-      <c r="I318" t="n">
-        <v>3</v>
-      </c>
-      <c r="J318" t="n">
-        <v>16</v>
-      </c>
-      <c r="K318" t="n">
-        <v>15</v>
-      </c>
-      <c r="L318" t="n">
-        <v>25</v>
-      </c>
       <c r="M318" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="N318" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="O318" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="P318" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="Q318" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="R318" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="S318" t="n">
         <v>18</v>
       </c>
       <c r="T318" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
-          <t>2487741</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V318" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="W318" t="n">
-        <v>92</v>
+        <v>100.12</v>
       </c>
       <c r="X318" t="n">
-        <v>0.7608695652173914</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="Y318" t="n">
-        <v>81</v>
+        <v>92.12</v>
       </c>
       <c r="Z318" t="n">
-        <v>86.41975308641975</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AA318" t="n">
-        <v>1.026361279170268</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="AB318" t="n">
-        <v>113.6907611297271</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AC318" t="n">
-        <v>0.25</v>
+        <v>0.2162162162162162</v>
       </c>
       <c r="AD318" t="n">
-        <v>0.7352941176470589</v>
+        <v>0.525</v>
       </c>
       <c r="AE318" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="AF318" t="n">
-        <v>-27.27100804330739</v>
+        <v>2.698912865946681</v>
       </c>
       <c r="AG318" t="inlineStr">
         <is>
-          <t>ADC BOADILLA</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH318" t="inlineStr">
         <is>
-          <t>GRUPO EGIDO PINTOBASKET</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI318" t="b">
@@ -38335,116 +38335,116 @@
         </is>
       </c>
       <c r="B319" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E319" t="n">
         <v>200</v>
       </c>
       <c r="F319" t="n">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="G319" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="H319" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I319" t="n">
         <v>4</v>
       </c>
       <c r="J319" t="n">
+        <v>19</v>
+      </c>
+      <c r="K319" t="n">
         <v>29</v>
       </c>
-      <c r="K319" t="n">
+      <c r="L319" t="n">
+        <v>40</v>
+      </c>
+      <c r="M319" t="n">
+        <v>8</v>
+      </c>
+      <c r="N319" t="n">
+        <v>27</v>
+      </c>
+      <c r="O319" t="n">
+        <v>11</v>
+      </c>
+      <c r="P319" t="n">
         <v>10</v>
       </c>
-      <c r="L319" t="n">
-        <v>13</v>
-      </c>
-      <c r="M319" t="n">
-        <v>15</v>
-      </c>
-      <c r="N319" t="n">
-        <v>18</v>
-      </c>
-      <c r="O319" t="n">
-        <v>14</v>
-      </c>
-      <c r="P319" t="n">
-        <v>8</v>
-      </c>
       <c r="Q319" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R319" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="S319" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="T319" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U319" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487731</t>
         </is>
       </c>
       <c r="V319" t="n">
         <v>77</v>
       </c>
       <c r="W319" t="n">
-        <v>89.72</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="X319" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.8465011286681716</v>
       </c>
       <c r="Y319" t="n">
-        <v>74.72</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="Z319" t="n">
-        <v>85.65310492505354</v>
+        <v>93.05210918114145</v>
       </c>
       <c r="AA319" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.7302731411229135</v>
       </c>
       <c r="AB319" t="n">
-        <v>107.2423398328691</v>
+        <v>96.92849949647533</v>
       </c>
       <c r="AC319" t="n">
-        <v>0.3658536585365854</v>
+        <v>0.25</v>
       </c>
       <c r="AD319" t="n">
-        <v>0.5625</v>
+        <v>0.5094339622641509</v>
       </c>
       <c r="AE319" t="n">
-        <v>0.4520547945205479</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="AF319" t="n">
-        <v>-21.58923490781554</v>
+        <v>-3.876390315333879</v>
       </c>
       <c r="AG319" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>LUJISA GUADALAJARA BASKET</t>
         </is>
       </c>
       <c r="AH319" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AI319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -38454,112 +38454,112 @@
         </is>
       </c>
       <c r="B320" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="E320" t="n">
         <v>200</v>
       </c>
       <c r="F320" t="n">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="G320" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H320" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I320" t="n">
+        <v>12</v>
+      </c>
+      <c r="J320" t="n">
+        <v>25</v>
+      </c>
+      <c r="K320" t="n">
+        <v>18</v>
+      </c>
+      <c r="L320" t="n">
+        <v>26</v>
+      </c>
+      <c r="M320" t="n">
         <v>9</v>
       </c>
-      <c r="J320" t="n">
+      <c r="N320" t="n">
+        <v>23</v>
+      </c>
+      <c r="O320" t="n">
+        <v>18</v>
+      </c>
+      <c r="P320" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>8</v>
+      </c>
+      <c r="R320" t="n">
         <v>26</v>
       </c>
-      <c r="K320" t="n">
-        <v>8</v>
-      </c>
-      <c r="L320" t="n">
-        <v>16</v>
-      </c>
-      <c r="M320" t="n">
-        <v>4</v>
-      </c>
-      <c r="N320" t="n">
-        <v>27</v>
-      </c>
-      <c r="O320" t="n">
-        <v>20</v>
-      </c>
-      <c r="P320" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q320" t="n">
-        <v>9</v>
-      </c>
-      <c r="R320" t="n">
-        <v>16</v>
-      </c>
       <c r="S320" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="T320" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
-          <t>2487740</t>
+          <t>2487732</t>
         </is>
       </c>
       <c r="V320" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="W320" t="n">
-        <v>85.03999999999999</v>
+        <v>91.44</v>
       </c>
       <c r="X320" t="n">
-        <v>0.8819379115710255</v>
+        <v>1.049868766404199</v>
       </c>
       <c r="Y320" t="n">
-        <v>81.03999999999999</v>
+        <v>82.44</v>
       </c>
       <c r="Z320" t="n">
-        <v>92.54689042448175</v>
+        <v>116.448326055313</v>
       </c>
       <c r="AA320" t="n">
-        <v>0.8535582064993829</v>
+        <v>0.9143717728055076</v>
       </c>
       <c r="AB320" t="n">
-        <v>96.24304267161409</v>
+        <v>106.3031515757879</v>
       </c>
       <c r="AC320" t="n">
-        <v>0.1</v>
+        <v>0.2903225806451613</v>
       </c>
       <c r="AD320" t="n">
-        <v>0.7105263157894737</v>
+        <v>0.6388888888888888</v>
       </c>
       <c r="AE320" t="n">
-        <v>0.3974358974358974</v>
+        <v>0.4776119402985075</v>
       </c>
       <c r="AF320" t="n">
-        <v>-3.696152247132346</v>
+        <v>10.14517447952508</v>
       </c>
       <c r="AG320" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>CB ARIDANE</t>
         </is>
       </c>
       <c r="AH320" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>REAL CANOE N.C.</t>
         </is>
       </c>
       <c r="AI320" t="b">
@@ -38573,112 +38573,112 @@
         </is>
       </c>
       <c r="B321" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="E321" t="n">
         <v>200</v>
       </c>
       <c r="F321" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="G321" t="n">
+        <v>10</v>
+      </c>
+      <c r="H321" t="n">
+        <v>26</v>
+      </c>
+      <c r="I321" t="n">
+        <v>6</v>
+      </c>
+      <c r="J321" t="n">
+        <v>26</v>
+      </c>
+      <c r="K321" t="n">
         <v>13</v>
       </c>
-      <c r="H321" t="n">
-        <v>34</v>
-      </c>
-      <c r="I321" t="n">
-        <v>9</v>
-      </c>
-      <c r="J321" t="n">
+      <c r="L321" t="n">
+        <v>20</v>
+      </c>
+      <c r="M321" t="n">
+        <v>6</v>
+      </c>
+      <c r="N321" t="n">
         <v>30</v>
       </c>
-      <c r="K321" t="n">
-        <v>15</v>
-      </c>
-      <c r="L321" t="n">
-        <v>31</v>
-      </c>
-      <c r="M321" t="n">
+      <c r="O321" t="n">
+        <v>6</v>
+      </c>
+      <c r="P321" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>11</v>
+      </c>
+      <c r="R321" t="n">
+        <v>24</v>
+      </c>
+      <c r="S321" t="n">
         <v>19</v>
-      </c>
-      <c r="N321" t="n">
-        <v>23</v>
-      </c>
-      <c r="O321" t="n">
-        <v>10</v>
-      </c>
-      <c r="P321" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q321" t="n">
-        <v>16</v>
-      </c>
-      <c r="R321" t="n">
-        <v>21</v>
-      </c>
-      <c r="S321" t="n">
-        <v>24</v>
       </c>
       <c r="T321" t="n">
         <v>2</v>
       </c>
       <c r="U321" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V321" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="W321" t="n">
-        <v>93.64</v>
+        <v>71.8</v>
       </c>
       <c r="X321" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="Y321" t="n">
-        <v>74.64</v>
+        <v>65.8</v>
       </c>
       <c r="Z321" t="n">
-        <v>91.10396570203645</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AA321" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="AB321" t="n">
-        <v>66.44085461177697</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AC321" t="n">
-        <v>0.475</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="AD321" t="n">
-        <v>0.6216216216216216</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="AE321" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5</v>
       </c>
       <c r="AF321" t="n">
-        <v>24.66311109025948</v>
+        <v>-28.02577257918253</v>
       </c>
       <c r="AG321" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH321" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI321" t="b">
@@ -38692,116 +38692,116 @@
         </is>
       </c>
       <c r="B322" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E322" t="n">
         <v>200</v>
       </c>
       <c r="F322" t="n">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="G322" t="n">
+        <v>13</v>
+      </c>
+      <c r="H322" t="n">
         <v>29</v>
       </c>
-      <c r="H322" t="n">
-        <v>45</v>
-      </c>
       <c r="I322" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J322" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="K322" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L322" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="M322" t="n">
         <v>9</v>
       </c>
       <c r="N322" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="O322" t="n">
+        <v>13</v>
+      </c>
+      <c r="P322" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>10</v>
+      </c>
+      <c r="R322" t="n">
         <v>19</v>
       </c>
-      <c r="P322" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q322" t="n">
-        <v>19</v>
-      </c>
-      <c r="R322" t="n">
-        <v>15</v>
-      </c>
       <c r="S322" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="T322" t="n">
         <v>1</v>
       </c>
       <c r="U322" t="inlineStr">
         <is>
-          <t>2487744</t>
+          <t>2487733</t>
         </is>
       </c>
       <c r="V322" t="n">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="W322" t="n">
-        <v>94.28</v>
+        <v>79.12</v>
       </c>
       <c r="X322" t="n">
-        <v>0.9227831989817564</v>
+        <v>0.935288169868554</v>
       </c>
       <c r="Y322" t="n">
-        <v>85.28</v>
+        <v>70.12</v>
       </c>
       <c r="Z322" t="n">
-        <v>102.0168855534709</v>
+        <v>105.5333713633771</v>
       </c>
       <c r="AA322" t="n">
-        <v>0.7312996239030506</v>
+        <v>0.7103064066852368</v>
       </c>
       <c r="AB322" t="n">
-        <v>83.61204013377926</v>
+        <v>77.50759878419453</v>
       </c>
       <c r="AC322" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.2307692307692308</v>
       </c>
       <c r="AD322" t="n">
-        <v>0.6470588235294118</v>
+        <v>0.8181818181818182</v>
       </c>
       <c r="AE322" t="n">
-        <v>0.4626865671641791</v>
+        <v>0.5</v>
       </c>
       <c r="AF322" t="n">
-        <v>18.40484541969165</v>
+        <v>28.02577257918253</v>
       </c>
       <c r="AG322" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>UROS DE RIVAS</t>
         </is>
       </c>
       <c r="AH322" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AI322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -38811,116 +38811,116 @@
         </is>
       </c>
       <c r="B323" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="E323" t="n">
         <v>200</v>
       </c>
       <c r="F323" t="n">
-        <v>51</v>
+        <v>88</v>
       </c>
       <c r="G323" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="H323" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="I323" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J323" t="n">
         <v>24</v>
       </c>
       <c r="K323" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="L323" t="n">
+        <v>18</v>
+      </c>
+      <c r="M323" t="n">
+        <v>19</v>
+      </c>
+      <c r="N323" t="n">
         <v>29</v>
       </c>
-      <c r="M323" t="n">
-        <v>14</v>
-      </c>
-      <c r="N323" t="n">
-        <v>21</v>
-      </c>
       <c r="O323" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P323" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="Q323" t="n">
+        <v>31</v>
+      </c>
+      <c r="R323" t="n">
         <v>19</v>
       </c>
-      <c r="R323" t="n">
-        <v>25</v>
-      </c>
       <c r="S323" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="T323" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U323" t="inlineStr">
         <is>
-          <t>2487739</t>
+          <t>2487735</t>
         </is>
       </c>
       <c r="V323" t="n">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="W323" t="n">
-        <v>90.75999999999999</v>
+        <v>114.92</v>
       </c>
       <c r="X323" t="n">
-        <v>0.5619215513442045</v>
+        <v>0.7657500870170554</v>
       </c>
       <c r="Y323" t="n">
-        <v>76.75999999999999</v>
+        <v>95.92</v>
       </c>
       <c r="Z323" t="n">
-        <v>66.44085461177697</v>
+        <v>91.74311926605505</v>
       </c>
       <c r="AA323" t="n">
-        <v>0.7261853908586074</v>
+        <v>0.8689572512984418</v>
       </c>
       <c r="AB323" t="n">
-        <v>91.10396570203645</v>
+        <v>94.44203213200173</v>
       </c>
       <c r="AC323" t="n">
-        <v>0.3783783783783784</v>
+        <v>0.475</v>
       </c>
       <c r="AD323" t="n">
-        <v>0.525</v>
+        <v>0.7837837837837838</v>
       </c>
       <c r="AE323" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.6233766233766234</v>
       </c>
       <c r="AF323" t="n">
-        <v>-24.66311109025948</v>
+        <v>-2.698912865946681</v>
       </c>
       <c r="AG323" t="inlineStr">
         <is>
-          <t>EB FELIPE ANTÓN</t>
+          <t>GRUPO EGIDO PINTOBASKET</t>
         </is>
       </c>
       <c r="AH323" t="inlineStr">
         <is>
-          <t>C.B. TRES CANTOS</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AI323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -38934,99 +38934,99 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
           <t>GRUPO EGIDO PINTOBASKET</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>ADC BOADILLA</t>
         </is>
       </c>
       <c r="E324" t="n">
         <v>200</v>
       </c>
       <c r="F324" t="n">
+        <v>70</v>
+      </c>
+      <c r="G324" t="n">
+        <v>23</v>
+      </c>
+      <c r="H324" t="n">
+        <v>53</v>
+      </c>
+      <c r="I324" t="n">
+        <v>3</v>
+      </c>
+      <c r="J324" t="n">
+        <v>16</v>
+      </c>
+      <c r="K324" t="n">
+        <v>15</v>
+      </c>
+      <c r="L324" t="n">
+        <v>25</v>
+      </c>
+      <c r="M324" t="n">
+        <v>11</v>
+      </c>
+      <c r="N324" t="n">
+        <v>25</v>
+      </c>
+      <c r="O324" t="n">
+        <v>15</v>
+      </c>
+      <c r="P324" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>12</v>
+      </c>
+      <c r="R324" t="n">
+        <v>20</v>
+      </c>
+      <c r="S324" t="n">
+        <v>18</v>
+      </c>
+      <c r="T324" t="n">
+        <v>3</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
         <v>95</v>
       </c>
-      <c r="G324" t="n">
-        <v>27</v>
-      </c>
-      <c r="H324" t="n">
-        <v>51</v>
-      </c>
-      <c r="I324" t="n">
-        <v>8</v>
-      </c>
-      <c r="J324" t="n">
-        <v>20</v>
-      </c>
-      <c r="K324" t="n">
-        <v>17</v>
-      </c>
-      <c r="L324" t="n">
-        <v>24</v>
-      </c>
-      <c r="M324" t="n">
-        <v>9</v>
-      </c>
-      <c r="N324" t="n">
-        <v>33</v>
-      </c>
-      <c r="O324" t="n">
-        <v>23</v>
-      </c>
-      <c r="P324" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q324" t="n">
-        <v>11</v>
-      </c>
-      <c r="R324" t="n">
-        <v>18</v>
-      </c>
-      <c r="S324" t="n">
-        <v>20</v>
-      </c>
-      <c r="T324" t="n">
-        <v>2</v>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>2487741</t>
-        </is>
-      </c>
-      <c r="V324" t="n">
-        <v>70</v>
-      </c>
       <c r="W324" t="n">
-        <v>92.56</v>
+        <v>92</v>
       </c>
       <c r="X324" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>86.41975308641975</v>
+      </c>
+      <c r="AA324" t="n">
         <v>1.026361279170268</v>
       </c>
-      <c r="Y324" t="n">
-        <v>83.56</v>
-      </c>
-      <c r="Z324" t="n">
+      <c r="AB324" t="n">
         <v>113.6907611297271</v>
       </c>
-      <c r="AA324" t="n">
-        <v>0.7608695652173914</v>
-      </c>
-      <c r="AB324" t="n">
-        <v>86.41975308641975</v>
-      </c>
       <c r="AC324" t="n">
-        <v>0.2647058823529412</v>
+        <v>0.25</v>
       </c>
       <c r="AD324" t="n">
-        <v>0.75</v>
+        <v>0.7352941176470589</v>
       </c>
       <c r="AE324" t="n">
-        <v>0.5384615384615384</v>
+        <v>0.4615384615384616</v>
       </c>
       <c r="AF324" t="n">
-        <v>27.27100804330739</v>
+        <v>-27.27100804330739</v>
       </c>
       <c r="AG324" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         </is>
       </c>
       <c r="AI324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
@@ -39053,22 +39053,22 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="E325" t="n">
         <v>200</v>
       </c>
       <c r="F325" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G325" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="H325" t="n">
         <v>41</v>
@@ -39077,88 +39077,88 @@
         <v>4</v>
       </c>
       <c r="J325" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K325" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L325" t="n">
         <v>13</v>
       </c>
       <c r="M325" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N325" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="O325" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="P325" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Q325" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="R325" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="S325" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="T325" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U325" t="inlineStr">
         <is>
-          <t>2487744</t>
+          <t>2487742</t>
         </is>
       </c>
       <c r="V325" t="n">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="W325" t="n">
-        <v>95.72</v>
+        <v>89.72</v>
       </c>
       <c r="X325" t="n">
-        <v>0.7312996239030506</v>
+        <v>0.7133303611234953</v>
       </c>
       <c r="Y325" t="n">
-        <v>83.72</v>
+        <v>74.72</v>
       </c>
       <c r="Z325" t="n">
-        <v>83.61204013377926</v>
+        <v>85.65310492505354</v>
       </c>
       <c r="AA325" t="n">
-        <v>0.9227831989817564</v>
+        <v>0.8974358974358975</v>
       </c>
       <c r="AB325" t="n">
-        <v>102.0168855534709</v>
+        <v>107.2423398328691</v>
       </c>
       <c r="AC325" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3658536585365854</v>
       </c>
       <c r="AD325" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.5625</v>
       </c>
       <c r="AE325" t="n">
-        <v>0.5373134328358209</v>
+        <v>0.4520547945205479</v>
       </c>
       <c r="AF325" t="n">
-        <v>-18.40484541969165</v>
+        <v>-21.58923490781554</v>
       </c>
       <c r="AG325" t="inlineStr">
         <is>
-          <t>LUJISA GUADALAJARA BASKET</t>
+          <t>RECUCYM BAZU</t>
         </is>
       </c>
       <c r="AH325" t="inlineStr">
         <is>
-          <t>CB ARIDANE</t>
+          <t>AUTOCARES RODRÍGUEZ</t>
         </is>
       </c>
       <c r="AI325" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -39172,108 +39172,108 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="E326" t="n">
         <v>200</v>
       </c>
       <c r="F326" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="G326" t="n">
+        <v>20</v>
+      </c>
+      <c r="H326" t="n">
+        <v>45</v>
+      </c>
+      <c r="I326" t="n">
+        <v>8</v>
+      </c>
+      <c r="J326" t="n">
+        <v>26</v>
+      </c>
+      <c r="K326" t="n">
         <v>12</v>
       </c>
-      <c r="H326" t="n">
-        <v>29</v>
-      </c>
-      <c r="I326" t="n">
-        <v>6</v>
-      </c>
-      <c r="J326" t="n">
-        <v>21</v>
-      </c>
-      <c r="K326" t="n">
-        <v>11</v>
-      </c>
       <c r="L326" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="M326" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="N326" t="n">
         <v>27</v>
       </c>
       <c r="O326" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="P326" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="Q326" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R326" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="S326" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="T326" t="n">
         <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>2487743</t>
+          <t>2487738</t>
         </is>
       </c>
       <c r="V326" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="W326" t="n">
-        <v>83.59999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="X326" t="n">
-        <v>0.6339712918660287</v>
+        <v>0.8179078777442962</v>
       </c>
       <c r="Y326" t="n">
-        <v>79.59999999999999</v>
+        <v>79.92</v>
       </c>
       <c r="Z326" t="n">
-        <v>66.58291457286433</v>
+        <v>95.09509509509509</v>
       </c>
       <c r="AA326" t="n">
-        <v>0.9238138686131386</v>
+        <v>0.8848566308243727</v>
       </c>
       <c r="AB326" t="n">
-        <v>101.6566265060241</v>
+        <v>98.40558046836074</v>
       </c>
       <c r="AC326" t="n">
-        <v>0.1290322580645161</v>
+        <v>0.3170731707317073</v>
       </c>
       <c r="AD326" t="n">
-        <v>0.7714285714285715</v>
+        <v>0.75</v>
       </c>
       <c r="AE326" t="n">
-        <v>0.4696969696969697</v>
+        <v>0.5194805194805194</v>
       </c>
       <c r="AF326" t="n">
-        <v>-35.07371193315976</v>
+        <v>-3.310485373265649</v>
       </c>
       <c r="AG326" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AH326" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI326" t="b">
@@ -39291,112 +39291,112 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="E327" t="n">
         <v>200</v>
       </c>
       <c r="F327" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G327" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H327" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I327" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="J327" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K327" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L327" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="M327" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="N327" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="O327" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P327" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q327" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R327" t="n">
         <v>20</v>
       </c>
       <c r="S327" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="T327" t="n">
         <v>3</v>
       </c>
       <c r="U327" t="inlineStr">
         <is>
-          <t>2487742</t>
+          <t>2487738</t>
         </is>
       </c>
       <c r="V327" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="W327" t="n">
-        <v>85.8</v>
+        <v>89.28</v>
       </c>
       <c r="X327" t="n">
-        <v>0.8974358974358975</v>
+        <v>0.8848566308243727</v>
       </c>
       <c r="Y327" t="n">
-        <v>71.8</v>
+        <v>80.28</v>
       </c>
       <c r="Z327" t="n">
-        <v>107.2423398328691</v>
+        <v>98.40558046836074</v>
       </c>
       <c r="AA327" t="n">
-        <v>0.7133303611234953</v>
+        <v>0.8179078777442962</v>
       </c>
       <c r="AB327" t="n">
-        <v>85.65310492505354</v>
+        <v>95.09509509509509</v>
       </c>
       <c r="AC327" t="n">
-        <v>0.4375</v>
+        <v>0.25</v>
       </c>
       <c r="AD327" t="n">
-        <v>0.6341463414634146</v>
+        <v>0.6829268292682927</v>
       </c>
       <c r="AE327" t="n">
-        <v>0.547945205479452</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="AF327" t="n">
-        <v>21.58923490781554</v>
+        <v>3.310485373265649</v>
       </c>
       <c r="AG327" t="inlineStr">
         <is>
-          <t>RECUCYM BAZU</t>
+          <t>BALONCESTO TALAVERA</t>
         </is>
       </c>
       <c r="AH327" t="inlineStr">
         <is>
-          <t>AUTOCARES RODRÍGUEZ</t>
+          <t>BALONCESTO TELDE</t>
         </is>
       </c>
       <c r="AI327" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -39410,108 +39410,108 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="E328" t="n">
         <v>200</v>
       </c>
       <c r="F328" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G328" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H328" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I328" t="n">
         <v>9</v>
       </c>
       <c r="J328" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K328" t="n">
+        <v>8</v>
+      </c>
+      <c r="L328" t="n">
         <v>16</v>
       </c>
-      <c r="L328" t="n">
-        <v>22</v>
-      </c>
       <c r="M328" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N328" t="n">
         <v>27</v>
       </c>
       <c r="O328" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="P328" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="Q328" t="n">
+        <v>9</v>
+      </c>
+      <c r="R328" t="n">
         <v>16</v>
       </c>
-      <c r="R328" t="n">
-        <v>20</v>
-      </c>
       <c r="S328" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T328" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>2487743</t>
+          <t>2487740</t>
         </is>
       </c>
       <c r="V328" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="W328" t="n">
-        <v>87.68000000000001</v>
+        <v>85.03999999999999</v>
       </c>
       <c r="X328" t="n">
-        <v>0.9238138686131386</v>
+        <v>0.8819379115710255</v>
       </c>
       <c r="Y328" t="n">
-        <v>79.68000000000001</v>
+        <v>81.03999999999999</v>
       </c>
       <c r="Z328" t="n">
-        <v>101.6566265060241</v>
+        <v>92.54689042448175</v>
       </c>
       <c r="AA328" t="n">
-        <v>0.6339712918660287</v>
+        <v>0.8535582064993829</v>
       </c>
       <c r="AB328" t="n">
-        <v>66.58291457286433</v>
+        <v>96.24304267161409</v>
       </c>
       <c r="AC328" t="n">
-        <v>0.2285714285714286</v>
+        <v>0.1</v>
       </c>
       <c r="AD328" t="n">
-        <v>0.8709677419354839</v>
+        <v>0.7105263157894737</v>
       </c>
       <c r="AE328" t="n">
-        <v>0.5303030303030303</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="AF328" t="n">
-        <v>35.07371193315976</v>
+        <v>-3.696152247132346</v>
       </c>
       <c r="AG328" t="inlineStr">
         <is>
-          <t>REAL CANOE N.C.</t>
+          <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
       <c r="AH328" t="inlineStr">
         <is>
-          <t>UROS DE RIVAS</t>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
       <c r="AI328" t="b">
@@ -39529,25 +39529,25 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>ZENTRO BASKET MADRID</t>
+          <t>C.B. TRES CANTOS</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+          <t>EB FELIPE ANTÓN</t>
         </is>
       </c>
       <c r="E329" t="n">
         <v>200</v>
       </c>
       <c r="F329" t="n">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="G329" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="H329" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I329" t="n">
         <v>9</v>
@@ -39556,84 +39556,4368 @@
         <v>30</v>
       </c>
       <c r="K329" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L329" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="M329" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="N329" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="O329" t="n">
         <v>10</v>
       </c>
       <c r="P329" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>16</v>
+      </c>
+      <c r="R329" t="n">
+        <v>21</v>
+      </c>
+      <c r="S329" t="n">
+        <v>24</v>
+      </c>
+      <c r="T329" t="n">
+        <v>2</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487739</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>51</v>
+      </c>
+      <c r="W329" t="n">
+        <v>93.64</v>
+      </c>
+      <c r="X329" t="n">
+        <v>0.7261853908586074</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>74.64</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>91.10396570203645</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.5619215513442045</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>66.44085461177697</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.5454545454545454</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>24.66311109025948</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>24</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>200</v>
+      </c>
+      <c r="F330" t="n">
+        <v>87</v>
+      </c>
+      <c r="G330" t="n">
+        <v>29</v>
+      </c>
+      <c r="H330" t="n">
+        <v>45</v>
+      </c>
+      <c r="I330" t="n">
         <v>8</v>
       </c>
-      <c r="Q329" t="n">
+      <c r="J330" t="n">
+        <v>25</v>
+      </c>
+      <c r="K330" t="n">
+        <v>5</v>
+      </c>
+      <c r="L330" t="n">
+        <v>12</v>
+      </c>
+      <c r="M330" t="n">
+        <v>9</v>
+      </c>
+      <c r="N330" t="n">
+        <v>22</v>
+      </c>
+      <c r="O330" t="n">
         <v>19</v>
       </c>
-      <c r="R329" t="n">
+      <c r="P330" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>19</v>
+      </c>
+      <c r="R330" t="n">
         <v>15</v>
       </c>
-      <c r="S329" t="n">
+      <c r="S330" t="n">
+        <v>15</v>
+      </c>
+      <c r="T330" t="n">
+        <v>1</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>70</v>
+      </c>
+      <c r="W330" t="n">
+        <v>94.28</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>85.28</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>0.6470588235294118</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>0.4626865671641791</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>18.40484541969165</v>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI330" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>24</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" t="n">
+        <v>51</v>
+      </c>
+      <c r="G331" t="n">
+        <v>12</v>
+      </c>
+      <c r="H331" t="n">
+        <v>35</v>
+      </c>
+      <c r="I331" t="n">
+        <v>2</v>
+      </c>
+      <c r="J331" t="n">
+        <v>24</v>
+      </c>
+      <c r="K331" t="n">
+        <v>21</v>
+      </c>
+      <c r="L331" t="n">
+        <v>29</v>
+      </c>
+      <c r="M331" t="n">
+        <v>14</v>
+      </c>
+      <c r="N331" t="n">
+        <v>21</v>
+      </c>
+      <c r="O331" t="n">
+        <v>7</v>
+      </c>
+      <c r="P331" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>19</v>
+      </c>
+      <c r="R331" t="n">
+        <v>25</v>
+      </c>
+      <c r="S331" t="n">
+        <v>20</v>
+      </c>
+      <c r="T331" t="n">
+        <v>3</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2487739</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>68</v>
+      </c>
+      <c r="W331" t="n">
+        <v>90.75999999999999</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0.5619215513442045</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>76.75999999999999</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>66.44085461177697</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>0.7261853908586074</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>91.10396570203645</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0.4545454545454545</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>-24.66311109025948</v>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI331" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>24</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>200</v>
+      </c>
+      <c r="F332" t="n">
+        <v>95</v>
+      </c>
+      <c r="G332" t="n">
+        <v>27</v>
+      </c>
+      <c r="H332" t="n">
+        <v>51</v>
+      </c>
+      <c r="I332" t="n">
+        <v>8</v>
+      </c>
+      <c r="J332" t="n">
+        <v>20</v>
+      </c>
+      <c r="K332" t="n">
+        <v>17</v>
+      </c>
+      <c r="L332" t="n">
+        <v>24</v>
+      </c>
+      <c r="M332" t="n">
+        <v>9</v>
+      </c>
+      <c r="N332" t="n">
+        <v>33</v>
+      </c>
+      <c r="O332" t="n">
+        <v>23</v>
+      </c>
+      <c r="P332" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>11</v>
+      </c>
+      <c r="R332" t="n">
+        <v>18</v>
+      </c>
+      <c r="S332" t="n">
+        <v>20</v>
+      </c>
+      <c r="T332" t="n">
+        <v>2</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2487741</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>70</v>
+      </c>
+      <c r="W332" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="X332" t="n">
+        <v>1.026361279170268</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>113.6907611297271</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>0.7608695652173914</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>86.41975308641975</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>0.2647058823529412</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>27.27100804330739</v>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI332" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>24</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>70</v>
+      </c>
+      <c r="G333" t="n">
+        <v>25</v>
+      </c>
+      <c r="H333" t="n">
+        <v>41</v>
+      </c>
+      <c r="I333" t="n">
+        <v>4</v>
+      </c>
+      <c r="J333" t="n">
+        <v>27</v>
+      </c>
+      <c r="K333" t="n">
+        <v>8</v>
+      </c>
+      <c r="L333" t="n">
+        <v>13</v>
+      </c>
+      <c r="M333" t="n">
+        <v>12</v>
+      </c>
+      <c r="N333" t="n">
+        <v>24</v>
+      </c>
+      <c r="O333" t="n">
+        <v>13</v>
+      </c>
+      <c r="P333" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>22</v>
+      </c>
+      <c r="R333" t="n">
+        <v>15</v>
+      </c>
+      <c r="S333" t="n">
+        <v>15</v>
+      </c>
+      <c r="T333" t="n">
+        <v>2</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>2487744</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>87</v>
+      </c>
+      <c r="W333" t="n">
+        <v>95.72</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0.7312996239030506</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>83.72</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>83.61204013377926</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>0.9227831989817564</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>102.0168855534709</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>0.3529411764705883</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>-18.40484541969165</v>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI333" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>24</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>200</v>
+      </c>
+      <c r="F334" t="n">
+        <v>53</v>
+      </c>
+      <c r="G334" t="n">
+        <v>12</v>
+      </c>
+      <c r="H334" t="n">
+        <v>29</v>
+      </c>
+      <c r="I334" t="n">
+        <v>6</v>
+      </c>
+      <c r="J334" t="n">
+        <v>21</v>
+      </c>
+      <c r="K334" t="n">
+        <v>11</v>
+      </c>
+      <c r="L334" t="n">
+        <v>15</v>
+      </c>
+      <c r="M334" t="n">
+        <v>4</v>
+      </c>
+      <c r="N334" t="n">
+        <v>27</v>
+      </c>
+      <c r="O334" t="n">
+        <v>13</v>
+      </c>
+      <c r="P334" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>27</v>
+      </c>
+      <c r="R334" t="n">
+        <v>21</v>
+      </c>
+      <c r="S334" t="n">
+        <v>20</v>
+      </c>
+      <c r="T334" t="n">
+        <v>1</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>81</v>
+      </c>
+      <c r="W334" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>0.1290322580645161</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>0.4696969696969697</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>-35.07371193315976</v>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI334" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>24</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>200</v>
+      </c>
+      <c r="F335" t="n">
+        <v>77</v>
+      </c>
+      <c r="G335" t="n">
+        <v>24</v>
+      </c>
+      <c r="H335" t="n">
+        <v>43</v>
+      </c>
+      <c r="I335" t="n">
+        <v>6</v>
+      </c>
+      <c r="J335" t="n">
+        <v>19</v>
+      </c>
+      <c r="K335" t="n">
+        <v>11</v>
+      </c>
+      <c r="L335" t="n">
+        <v>20</v>
+      </c>
+      <c r="M335" t="n">
+        <v>14</v>
+      </c>
+      <c r="N335" t="n">
+        <v>26</v>
+      </c>
+      <c r="O335" t="n">
+        <v>13</v>
+      </c>
+      <c r="P335" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>15</v>
+      </c>
+      <c r="R335" t="n">
+        <v>20</v>
+      </c>
+      <c r="S335" t="n">
+        <v>20</v>
+      </c>
+      <c r="T335" t="n">
+        <v>3</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2487742</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>64</v>
+      </c>
+      <c r="W335" t="n">
+        <v>85.8</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0.8974358974358975</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>71.8</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>107.2423398328691</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>0.7133303611234953</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>85.65310492505354</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0.6341463414634146</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>0.547945205479452</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>21.58923490781554</v>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>24</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>200</v>
+      </c>
+      <c r="F336" t="n">
+        <v>81</v>
+      </c>
+      <c r="G336" t="n">
+        <v>19</v>
+      </c>
+      <c r="H336" t="n">
+        <v>39</v>
+      </c>
+      <c r="I336" t="n">
+        <v>9</v>
+      </c>
+      <c r="J336" t="n">
+        <v>23</v>
+      </c>
+      <c r="K336" t="n">
         <v>16</v>
       </c>
-      <c r="T329" t="n">
+      <c r="L336" t="n">
+        <v>22</v>
+      </c>
+      <c r="M336" t="n">
+        <v>8</v>
+      </c>
+      <c r="N336" t="n">
+        <v>27</v>
+      </c>
+      <c r="O336" t="n">
+        <v>24</v>
+      </c>
+      <c r="P336" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>16</v>
+      </c>
+      <c r="R336" t="n">
+        <v>20</v>
+      </c>
+      <c r="S336" t="n">
+        <v>21</v>
+      </c>
+      <c r="T336" t="n">
+        <v>0</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>2487743</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>53</v>
+      </c>
+      <c r="W336" t="n">
+        <v>87.68000000000001</v>
+      </c>
+      <c r="X336" t="n">
+        <v>0.9238138686131386</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>79.68000000000001</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>101.6566265060241</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>0.6339712918660287</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>66.58291457286433</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>0.8709677419354839</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>35.07371193315976</v>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI336" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>24</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>200</v>
+      </c>
+      <c r="F337" t="n">
+        <v>83</v>
+      </c>
+      <c r="G337" t="n">
+        <v>21</v>
+      </c>
+      <c r="H337" t="n">
+        <v>39</v>
+      </c>
+      <c r="I337" t="n">
+        <v>9</v>
+      </c>
+      <c r="J337" t="n">
+        <v>30</v>
+      </c>
+      <c r="K337" t="n">
+        <v>14</v>
+      </c>
+      <c r="L337" t="n">
+        <v>21</v>
+      </c>
+      <c r="M337" t="n">
+        <v>11</v>
+      </c>
+      <c r="N337" t="n">
+        <v>36</v>
+      </c>
+      <c r="O337" t="n">
+        <v>10</v>
+      </c>
+      <c r="P337" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>19</v>
+      </c>
+      <c r="R337" t="n">
+        <v>15</v>
+      </c>
+      <c r="S337" t="n">
+        <v>16</v>
+      </c>
+      <c r="T337" t="n">
         <v>3</v>
       </c>
-      <c r="U329" t="inlineStr">
+      <c r="U337" t="inlineStr">
         <is>
           <t>2487740</t>
         </is>
       </c>
-      <c r="V329" t="n">
+      <c r="V337" t="n">
         <v>75</v>
       </c>
-      <c r="W329" t="n">
+      <c r="W337" t="n">
         <v>97.24000000000001</v>
       </c>
-      <c r="X329" t="n">
+      <c r="X337" t="n">
         <v>0.8535582064993829</v>
       </c>
-      <c r="Y329" t="n">
+      <c r="Y337" t="n">
         <v>86.24000000000001</v>
       </c>
-      <c r="Z329" t="n">
+      <c r="Z337" t="n">
         <v>96.24304267161409</v>
       </c>
-      <c r="AA329" t="n">
+      <c r="AA337" t="n">
         <v>0.8819379115710255</v>
       </c>
-      <c r="AB329" t="n">
+      <c r="AB337" t="n">
         <v>92.54689042448175</v>
       </c>
-      <c r="AC329" t="n">
+      <c r="AC337" t="n">
         <v>0.2894736842105263</v>
       </c>
-      <c r="AD329" t="n">
+      <c r="AD337" t="n">
         <v>0.9</v>
       </c>
-      <c r="AE329" t="n">
+      <c r="AE337" t="n">
         <v>0.6025641025641025</v>
       </c>
-      <c r="AF329" t="n">
+      <c r="AF337" t="n">
         <v>3.696152247132346</v>
       </c>
-      <c r="AG329" t="inlineStr">
+      <c r="AG337" t="inlineStr">
         <is>
           <t>ZENTRO BASKET MADRID</t>
         </is>
       </c>
-      <c r="AH329" t="inlineStr">
+      <c r="AH337" t="inlineStr">
         <is>
           <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
         </is>
       </c>
-      <c r="AI329" t="b">
+      <c r="AI337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>25</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>200</v>
+      </c>
+      <c r="F338" t="n">
+        <v>80</v>
+      </c>
+      <c r="G338" t="n">
+        <v>20</v>
+      </c>
+      <c r="H338" t="n">
+        <v>35</v>
+      </c>
+      <c r="I338" t="n">
+        <v>8</v>
+      </c>
+      <c r="J338" t="n">
+        <v>34</v>
+      </c>
+      <c r="K338" t="n">
+        <v>16</v>
+      </c>
+      <c r="L338" t="n">
+        <v>24</v>
+      </c>
+      <c r="M338" t="n">
+        <v>8</v>
+      </c>
+      <c r="N338" t="n">
+        <v>22</v>
+      </c>
+      <c r="O338" t="n">
+        <v>21</v>
+      </c>
+      <c r="P338" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>8</v>
+      </c>
+      <c r="R338" t="n">
+        <v>26</v>
+      </c>
+      <c r="S338" t="n">
+        <v>25</v>
+      </c>
+      <c r="T338" t="n">
+        <v>2</v>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>70</v>
+      </c>
+      <c r="W338" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="X338" t="n">
+        <v>0.9136592051164916</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>79.56</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>100.5530417295123</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>0.1951219512195122</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>13.05304172951232</v>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AI338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>25</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>200</v>
+      </c>
+      <c r="F339" t="n">
+        <v>61</v>
+      </c>
+      <c r="G339" t="n">
+        <v>13</v>
+      </c>
+      <c r="H339" t="n">
+        <v>39</v>
+      </c>
+      <c r="I339" t="n">
+        <v>7</v>
+      </c>
+      <c r="J339" t="n">
+        <v>25</v>
+      </c>
+      <c r="K339" t="n">
+        <v>14</v>
+      </c>
+      <c r="L339" t="n">
+        <v>23</v>
+      </c>
+      <c r="M339" t="n">
+        <v>13</v>
+      </c>
+      <c r="N339" t="n">
+        <v>20</v>
+      </c>
+      <c r="O339" t="n">
+        <v>10</v>
+      </c>
+      <c r="P339" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>23</v>
+      </c>
+      <c r="R339" t="n">
+        <v>18</v>
+      </c>
+      <c r="S339" t="n">
+        <v>18</v>
+      </c>
+      <c r="T339" t="n">
+        <v>2</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>2487747</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>91</v>
+      </c>
+      <c r="W339" t="n">
+        <v>97.12</v>
+      </c>
+      <c r="X339" t="n">
+        <v>0.6280889621087314</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>72.51545411317166</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>1.028481012658228</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>111.6838487972509</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>0.3095238095238095</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>0.7407407407407407</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>0.4782608695652174</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>-39.1683946840792</v>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AI339" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>25</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>200</v>
+      </c>
+      <c r="F340" t="n">
+        <v>74</v>
+      </c>
+      <c r="G340" t="n">
+        <v>18</v>
+      </c>
+      <c r="H340" t="n">
+        <v>40</v>
+      </c>
+      <c r="I340" t="n">
+        <v>9</v>
+      </c>
+      <c r="J340" t="n">
+        <v>29</v>
+      </c>
+      <c r="K340" t="n">
+        <v>11</v>
+      </c>
+      <c r="L340" t="n">
+        <v>21</v>
+      </c>
+      <c r="M340" t="n">
+        <v>18</v>
+      </c>
+      <c r="N340" t="n">
+        <v>23</v>
+      </c>
+      <c r="O340" t="n">
+        <v>18</v>
+      </c>
+      <c r="P340" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>18</v>
+      </c>
+      <c r="R340" t="n">
+        <v>19</v>
+      </c>
+      <c r="S340" t="n">
+        <v>19</v>
+      </c>
+      <c r="T340" t="n">
+        <v>1</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>2487745</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>107</v>
+      </c>
+      <c r="W340" t="n">
+        <v>96.24000000000001</v>
+      </c>
+      <c r="X340" t="n">
+        <v>0.768911055694098</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>78.24000000000001</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>94.5807770961145</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>1.156006914433881</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>132.8202581926514</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>0.4090909090909091</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>0.5189873417721519</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>-38.23948109653693</v>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI340" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>25</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>200</v>
+      </c>
+      <c r="F341" t="n">
+        <v>74</v>
+      </c>
+      <c r="G341" t="n">
+        <v>23</v>
+      </c>
+      <c r="H341" t="n">
+        <v>44</v>
+      </c>
+      <c r="I341" t="n">
+        <v>4</v>
+      </c>
+      <c r="J341" t="n">
+        <v>24</v>
+      </c>
+      <c r="K341" t="n">
+        <v>16</v>
+      </c>
+      <c r="L341" t="n">
+        <v>26</v>
+      </c>
+      <c r="M341" t="n">
+        <v>11</v>
+      </c>
+      <c r="N341" t="n">
+        <v>26</v>
+      </c>
+      <c r="O341" t="n">
+        <v>12</v>
+      </c>
+      <c r="P341" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>16</v>
+      </c>
+      <c r="R341" t="n">
+        <v>20</v>
+      </c>
+      <c r="S341" t="n">
+        <v>23</v>
+      </c>
+      <c r="T341" t="n">
+        <v>1</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>82</v>
+      </c>
+      <c r="W341" t="n">
+        <v>95.44</v>
+      </c>
+      <c r="X341" t="n">
+        <v>0.7753562447611064</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>84.44</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>87.63619137849361</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>0.8570234113712374</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>99.17755200774067</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>0.2619047619047619</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>0.4567901234567901</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>-11.54136062924707</v>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AI341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>25</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>200</v>
+      </c>
+      <c r="F342" t="n">
+        <v>70</v>
+      </c>
+      <c r="G342" t="n">
+        <v>20</v>
+      </c>
+      <c r="H342" t="n">
+        <v>32</v>
+      </c>
+      <c r="I342" t="n">
+        <v>5</v>
+      </c>
+      <c r="J342" t="n">
+        <v>21</v>
+      </c>
+      <c r="K342" t="n">
+        <v>15</v>
+      </c>
+      <c r="L342" t="n">
+        <v>25</v>
+      </c>
+      <c r="M342" t="n">
+        <v>6</v>
+      </c>
+      <c r="N342" t="n">
+        <v>33</v>
+      </c>
+      <c r="O342" t="n">
+        <v>13</v>
+      </c>
+      <c r="P342" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>22</v>
+      </c>
+      <c r="R342" t="n">
+        <v>27</v>
+      </c>
+      <c r="S342" t="n">
+        <v>24</v>
+      </c>
+      <c r="T342" t="n">
+        <v>2</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>2487749</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>80</v>
+      </c>
+      <c r="W342" t="n">
+        <v>86</v>
+      </c>
+      <c r="X342" t="n">
+        <v>0.813953488372093</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>80</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>87.5</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>0.9136592051164916</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>100.5530417295123</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>0.2142857142857143</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>0.8048780487804879</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>-13.05304172951232</v>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AI342" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>25</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>225</v>
+      </c>
+      <c r="F343" t="n">
+        <v>69</v>
+      </c>
+      <c r="G343" t="n">
+        <v>16</v>
+      </c>
+      <c r="H343" t="n">
+        <v>43</v>
+      </c>
+      <c r="I343" t="n">
+        <v>10</v>
+      </c>
+      <c r="J343" t="n">
+        <v>34</v>
+      </c>
+      <c r="K343" t="n">
+        <v>7</v>
+      </c>
+      <c r="L343" t="n">
+        <v>14</v>
+      </c>
+      <c r="M343" t="n">
+        <v>16</v>
+      </c>
+      <c r="N343" t="n">
+        <v>37</v>
+      </c>
+      <c r="O343" t="n">
+        <v>15</v>
+      </c>
+      <c r="P343" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>18</v>
+      </c>
+      <c r="R343" t="n">
+        <v>25</v>
+      </c>
+      <c r="S343" t="n">
+        <v>20</v>
+      </c>
+      <c r="T343" t="n">
+        <v>7</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>71</v>
+      </c>
+      <c r="W343" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="X343" t="n">
+        <v>0.6820877817319099</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>85.16</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>81.0239549084077</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>0.6501831501831502</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>77.85087719298245</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>0.6727272727272727</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>0.5047619047619047</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>3.173077715425251</v>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AI343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>25</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>200</v>
+      </c>
+      <c r="F344" t="n">
+        <v>107</v>
+      </c>
+      <c r="G344" t="n">
+        <v>26</v>
+      </c>
+      <c r="H344" t="n">
+        <v>38</v>
+      </c>
+      <c r="I344" t="n">
+        <v>14</v>
+      </c>
+      <c r="J344" t="n">
+        <v>36</v>
+      </c>
+      <c r="K344" t="n">
+        <v>13</v>
+      </c>
+      <c r="L344" t="n">
+        <v>24</v>
+      </c>
+      <c r="M344" t="n">
+        <v>12</v>
+      </c>
+      <c r="N344" t="n">
+        <v>26</v>
+      </c>
+      <c r="O344" t="n">
+        <v>28</v>
+      </c>
+      <c r="P344" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>8</v>
+      </c>
+      <c r="R344" t="n">
+        <v>21</v>
+      </c>
+      <c r="S344" t="n">
+        <v>19</v>
+      </c>
+      <c r="T344" t="n">
+        <v>5</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>2487745</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>74</v>
+      </c>
+      <c r="W344" t="n">
+        <v>92.56</v>
+      </c>
+      <c r="X344" t="n">
+        <v>1.156006914433881</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>80.56</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>132.8202581926514</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>0.768911055694098</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>94.5807770961145</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>0.5909090909090909</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>0.4810126582278481</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>38.23948109653693</v>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AI344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>25</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>200</v>
+      </c>
+      <c r="F345" t="n">
+        <v>82</v>
+      </c>
+      <c r="G345" t="n">
+        <v>19</v>
+      </c>
+      <c r="H345" t="n">
+        <v>44</v>
+      </c>
+      <c r="I345" t="n">
+        <v>10</v>
+      </c>
+      <c r="J345" t="n">
+        <v>28</v>
+      </c>
+      <c r="K345" t="n">
+        <v>14</v>
+      </c>
+      <c r="L345" t="n">
+        <v>22</v>
+      </c>
+      <c r="M345" t="n">
+        <v>13</v>
+      </c>
+      <c r="N345" t="n">
+        <v>31</v>
+      </c>
+      <c r="O345" t="n">
+        <v>14</v>
+      </c>
+      <c r="P345" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>14</v>
+      </c>
+      <c r="R345" t="n">
+        <v>24</v>
+      </c>
+      <c r="S345" t="n">
+        <v>20</v>
+      </c>
+      <c r="T345" t="n">
+        <v>4</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>2487751</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>74</v>
+      </c>
+      <c r="W345" t="n">
+        <v>95.68000000000001</v>
+      </c>
+      <c r="X345" t="n">
+        <v>0.8570234113712374</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>82.68000000000001</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>99.17755200774067</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>0.7753562447611064</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>87.63619137849361</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD345" t="n">
+        <v>0.7380952380952381</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>0.5432098765432098</v>
+      </c>
+      <c r="AF345" t="n">
+        <v>11.54136062924707</v>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AI345" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>25</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>200</v>
+      </c>
+      <c r="F346" t="n">
+        <v>51</v>
+      </c>
+      <c r="G346" t="n">
+        <v>13</v>
+      </c>
+      <c r="H346" t="n">
+        <v>41</v>
+      </c>
+      <c r="I346" t="n">
+        <v>4</v>
+      </c>
+      <c r="J346" t="n">
+        <v>26</v>
+      </c>
+      <c r="K346" t="n">
+        <v>13</v>
+      </c>
+      <c r="L346" t="n">
+        <v>30</v>
+      </c>
+      <c r="M346" t="n">
+        <v>13</v>
+      </c>
+      <c r="N346" t="n">
+        <v>21</v>
+      </c>
+      <c r="O346" t="n">
+        <v>9</v>
+      </c>
+      <c r="P346" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>10</v>
+      </c>
+      <c r="R346" t="n">
+        <v>24</v>
+      </c>
+      <c r="S346" t="n">
+        <v>25</v>
+      </c>
+      <c r="T346" t="n">
+        <v>1</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>62</v>
+      </c>
+      <c r="W346" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="X346" t="n">
+        <v>0.565410199556541</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>66.06217616580311</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>0.6837229819144243</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>81.92389006342493</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>0.2549019607843137</v>
+      </c>
+      <c r="AD346" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>0.3908045977011494</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>-15.86171389762183</v>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AI346" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>25</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>200</v>
+      </c>
+      <c r="F347" t="n">
+        <v>63</v>
+      </c>
+      <c r="G347" t="n">
+        <v>14</v>
+      </c>
+      <c r="H347" t="n">
+        <v>36</v>
+      </c>
+      <c r="I347" t="n">
+        <v>8</v>
+      </c>
+      <c r="J347" t="n">
+        <v>26</v>
+      </c>
+      <c r="K347" t="n">
+        <v>11</v>
+      </c>
+      <c r="L347" t="n">
+        <v>14</v>
+      </c>
+      <c r="M347" t="n">
+        <v>7</v>
+      </c>
+      <c r="N347" t="n">
+        <v>26</v>
+      </c>
+      <c r="O347" t="n">
+        <v>10</v>
+      </c>
+      <c r="P347" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>19</v>
+      </c>
+      <c r="R347" t="n">
+        <v>23</v>
+      </c>
+      <c r="S347" t="n">
+        <v>19</v>
+      </c>
+      <c r="T347" t="n">
+        <v>2</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>70</v>
+      </c>
+      <c r="W347" t="n">
+        <v>87.16</v>
+      </c>
+      <c r="X347" t="n">
+        <v>0.7228086278109225</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>80.16</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>78.59281437125749</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>0.8549096238397655</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>91.05098855359002</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>0.8387096774193549</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>0.559322033898305</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>-12.45817418233253</v>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AI347" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>25</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>200</v>
+      </c>
+      <c r="F348" t="n">
+        <v>91</v>
+      </c>
+      <c r="G348" t="n">
+        <v>27</v>
+      </c>
+      <c r="H348" t="n">
+        <v>43</v>
+      </c>
+      <c r="I348" t="n">
+        <v>9</v>
+      </c>
+      <c r="J348" t="n">
+        <v>23</v>
+      </c>
+      <c r="K348" t="n">
+        <v>10</v>
+      </c>
+      <c r="L348" t="n">
+        <v>17</v>
+      </c>
+      <c r="M348" t="n">
+        <v>7</v>
+      </c>
+      <c r="N348" t="n">
+        <v>29</v>
+      </c>
+      <c r="O348" t="n">
+        <v>29</v>
+      </c>
+      <c r="P348" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>15</v>
+      </c>
+      <c r="R348" t="n">
+        <v>18</v>
+      </c>
+      <c r="S348" t="n">
+        <v>18</v>
+      </c>
+      <c r="T348" t="n">
+        <v>4</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>2487747</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>61</v>
+      </c>
+      <c r="W348" t="n">
+        <v>88.48</v>
+      </c>
+      <c r="X348" t="n">
+        <v>1.028481012658228</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>111.6838487972509</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>0.6280889621087314</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>72.51545411317166</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>0.2592592592592592</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>0.6904761904761905</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>0.5217391304347826</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>39.1683946840792</v>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AI348" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>25</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>200</v>
+      </c>
+      <c r="F349" t="n">
+        <v>62</v>
+      </c>
+      <c r="G349" t="n">
+        <v>20</v>
+      </c>
+      <c r="H349" t="n">
+        <v>37</v>
+      </c>
+      <c r="I349" t="n">
+        <v>3</v>
+      </c>
+      <c r="J349" t="n">
+        <v>27</v>
+      </c>
+      <c r="K349" t="n">
+        <v>13</v>
+      </c>
+      <c r="L349" t="n">
+        <v>22</v>
+      </c>
+      <c r="M349" t="n">
+        <v>15</v>
+      </c>
+      <c r="N349" t="n">
+        <v>38</v>
+      </c>
+      <c r="O349" t="n">
+        <v>11</v>
+      </c>
+      <c r="P349" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>17</v>
+      </c>
+      <c r="R349" t="n">
+        <v>25</v>
+      </c>
+      <c r="S349" t="n">
+        <v>23</v>
+      </c>
+      <c r="T349" t="n">
+        <v>2</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>2487748</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>51</v>
+      </c>
+      <c r="W349" t="n">
+        <v>90.68000000000001</v>
+      </c>
+      <c r="X349" t="n">
+        <v>0.6837229819144243</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>75.68000000000001</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>81.92389006342493</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>0.565410199556541</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>66.06217616580311</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>0.7450980392156863</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>0.6091954022988506</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>15.86171389762183</v>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AI349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>25</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>200</v>
+      </c>
+      <c r="F350" t="n">
+        <v>70</v>
+      </c>
+      <c r="G350" t="n">
+        <v>15</v>
+      </c>
+      <c r="H350" t="n">
+        <v>35</v>
+      </c>
+      <c r="I350" t="n">
+        <v>6</v>
+      </c>
+      <c r="J350" t="n">
+        <v>22</v>
+      </c>
+      <c r="K350" t="n">
+        <v>22</v>
+      </c>
+      <c r="L350" t="n">
+        <v>27</v>
+      </c>
+      <c r="M350" t="n">
+        <v>5</v>
+      </c>
+      <c r="N350" t="n">
+        <v>21</v>
+      </c>
+      <c r="O350" t="n">
+        <v>8</v>
+      </c>
+      <c r="P350" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>13</v>
+      </c>
+      <c r="R350" t="n">
+        <v>19</v>
+      </c>
+      <c r="S350" t="n">
+        <v>23</v>
+      </c>
+      <c r="T350" t="n">
+        <v>2</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>2487746</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>63</v>
+      </c>
+      <c r="W350" t="n">
+        <v>81.88</v>
+      </c>
+      <c r="X350" t="n">
+        <v>0.8549096238397655</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>91.05098855359002</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>0.7228086278109225</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>78.59281437125749</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>0.4406779661016949</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>12.45817418233253</v>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AI350" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>25</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>225</v>
+      </c>
+      <c r="F351" t="n">
+        <v>71</v>
+      </c>
+      <c r="G351" t="n">
+        <v>15</v>
+      </c>
+      <c r="H351" t="n">
+        <v>48</v>
+      </c>
+      <c r="I351" t="n">
+        <v>6</v>
+      </c>
+      <c r="J351" t="n">
+        <v>31</v>
+      </c>
+      <c r="K351" t="n">
+        <v>23</v>
+      </c>
+      <c r="L351" t="n">
+        <v>30</v>
+      </c>
+      <c r="M351" t="n">
+        <v>18</v>
+      </c>
+      <c r="N351" t="n">
+        <v>34</v>
+      </c>
+      <c r="O351" t="n">
+        <v>13</v>
+      </c>
+      <c r="P351" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>17</v>
+      </c>
+      <c r="R351" t="n">
+        <v>20</v>
+      </c>
+      <c r="S351" t="n">
+        <v>25</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>2487750</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>69</v>
+      </c>
+      <c r="W351" t="n">
+        <v>109.2</v>
+      </c>
+      <c r="X351" t="n">
+        <v>0.6501831501831502</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>77.85087719298245</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>0.6820877817319099</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>81.0239549084077</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>0.3272727272727273</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>0.4952380952380953</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>-3.173077715425251</v>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AI351" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>26</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>200</v>
+      </c>
+      <c r="F352" t="n">
+        <v>79</v>
+      </c>
+      <c r="G352" t="n">
+        <v>19</v>
+      </c>
+      <c r="H352" t="n">
+        <v>36</v>
+      </c>
+      <c r="I352" t="n">
+        <v>7</v>
+      </c>
+      <c r="J352" t="n">
+        <v>20</v>
+      </c>
+      <c r="K352" t="n">
+        <v>20</v>
+      </c>
+      <c r="L352" t="n">
+        <v>33</v>
+      </c>
+      <c r="M352" t="n">
+        <v>4</v>
+      </c>
+      <c r="N352" t="n">
+        <v>29</v>
+      </c>
+      <c r="O352" t="n">
+        <v>14</v>
+      </c>
+      <c r="P352" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>21</v>
+      </c>
+      <c r="R352" t="n">
+        <v>23</v>
+      </c>
+      <c r="S352" t="n">
+        <v>23</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>82</v>
+      </c>
+      <c r="W352" t="n">
+        <v>91.52</v>
+      </c>
+      <c r="X352" t="n">
+        <v>0.8631993006993007</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>87.52</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>90.26508226691043</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>0.8979413053000439</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>98.41574651944312</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>0.1379310344827586</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>0.7837837837837838</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>-8.150664252532692</v>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI352" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>26</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>200</v>
+      </c>
+      <c r="F353" t="n">
+        <v>71</v>
+      </c>
+      <c r="G353" t="n">
+        <v>19</v>
+      </c>
+      <c r="H353" t="n">
+        <v>42</v>
+      </c>
+      <c r="I353" t="n">
+        <v>7</v>
+      </c>
+      <c r="J353" t="n">
+        <v>31</v>
+      </c>
+      <c r="K353" t="n">
+        <v>12</v>
+      </c>
+      <c r="L353" t="n">
+        <v>16</v>
+      </c>
+      <c r="M353" t="n">
+        <v>8</v>
+      </c>
+      <c r="N353" t="n">
+        <v>26</v>
+      </c>
+      <c r="O353" t="n">
+        <v>16</v>
+      </c>
+      <c r="P353" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>6</v>
+      </c>
+      <c r="R353" t="n">
+        <v>17</v>
+      </c>
+      <c r="S353" t="n">
+        <v>20</v>
+      </c>
+      <c r="T353" t="n">
+        <v>0</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>2487757</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>81</v>
+      </c>
+      <c r="W353" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X353" t="n">
+        <v>0.8251975825197583</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>78.03999999999999</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>90.97898513582778</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>101.9124308002013</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>0.7647058823529411</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>-10.93344566437352</v>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI353" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>26</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>200</v>
+      </c>
+      <c r="F354" t="n">
+        <v>86</v>
+      </c>
+      <c r="G354" t="n">
+        <v>22</v>
+      </c>
+      <c r="H354" t="n">
+        <v>40</v>
+      </c>
+      <c r="I354" t="n">
+        <v>7</v>
+      </c>
+      <c r="J354" t="n">
+        <v>28</v>
+      </c>
+      <c r="K354" t="n">
+        <v>21</v>
+      </c>
+      <c r="L354" t="n">
+        <v>36</v>
+      </c>
+      <c r="M354" t="n">
+        <v>14</v>
+      </c>
+      <c r="N354" t="n">
+        <v>24</v>
+      </c>
+      <c r="O354" t="n">
+        <v>12</v>
+      </c>
+      <c r="P354" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>17</v>
+      </c>
+      <c r="R354" t="n">
+        <v>21</v>
+      </c>
+      <c r="S354" t="n">
+        <v>26</v>
+      </c>
+      <c r="T354" t="n">
+        <v>0</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>94</v>
+      </c>
+      <c r="W354" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="X354" t="n">
+        <v>0.852836176120587</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>86.84</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>99.03270382312299</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>1.026649191786806</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>119.6537678207739</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>0.6486486486486487</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>0.5205479452054794</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>-20.62106399765094</v>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AI354" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>26</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>200</v>
+      </c>
+      <c r="F355" t="n">
+        <v>82</v>
+      </c>
+      <c r="G355" t="n">
+        <v>18</v>
+      </c>
+      <c r="H355" t="n">
+        <v>35</v>
+      </c>
+      <c r="I355" t="n">
+        <v>7</v>
+      </c>
+      <c r="J355" t="n">
+        <v>23</v>
+      </c>
+      <c r="K355" t="n">
+        <v>25</v>
+      </c>
+      <c r="L355" t="n">
+        <v>28</v>
+      </c>
+      <c r="M355" t="n">
+        <v>5</v>
+      </c>
+      <c r="N355" t="n">
+        <v>22</v>
+      </c>
+      <c r="O355" t="n">
+        <v>12</v>
+      </c>
+      <c r="P355" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>24</v>
+      </c>
+      <c r="R355" t="n">
+        <v>28</v>
+      </c>
+      <c r="S355" t="n">
+        <v>26</v>
+      </c>
+      <c r="T355" t="n">
+        <v>2</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>2487753</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>102</v>
+      </c>
+      <c r="W355" t="n">
+        <v>94.31999999999999</v>
+      </c>
+      <c r="X355" t="n">
+        <v>0.8693808312128923</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>89.31999999999999</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>91.80474697716078</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>1.043371522094926</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>121.7765042979943</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>0.3970588235294117</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>-29.9717573208335</v>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AI355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>26</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>200</v>
+      </c>
+      <c r="F356" t="n">
+        <v>65</v>
+      </c>
+      <c r="G356" t="n">
+        <v>14</v>
+      </c>
+      <c r="H356" t="n">
+        <v>28</v>
+      </c>
+      <c r="I356" t="n">
+        <v>11</v>
+      </c>
+      <c r="J356" t="n">
+        <v>34</v>
+      </c>
+      <c r="K356" t="n">
+        <v>4</v>
+      </c>
+      <c r="L356" t="n">
+        <v>13</v>
+      </c>
+      <c r="M356" t="n">
+        <v>10</v>
+      </c>
+      <c r="N356" t="n">
+        <v>27</v>
+      </c>
+      <c r="O356" t="n">
+        <v>12</v>
+      </c>
+      <c r="P356" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>12</v>
+      </c>
+      <c r="R356" t="n">
+        <v>18</v>
+      </c>
+      <c r="S356" t="n">
+        <v>15</v>
+      </c>
+      <c r="T356" t="n">
+        <v>5</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>2487755</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>47</v>
+      </c>
+      <c r="W356" t="n">
+        <v>79.72</v>
+      </c>
+      <c r="X356" t="n">
+        <v>0.8153537380832915</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>69.72</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>93.23006310958118</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>0.5831265508684864</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>67.52873563218391</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>0.7105263157894737</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>0.4805194805194805</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>25.70132747739727</v>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AI356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>26</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>200</v>
+      </c>
+      <c r="F357" t="n">
+        <v>82</v>
+      </c>
+      <c r="G357" t="n">
+        <v>19</v>
+      </c>
+      <c r="H357" t="n">
+        <v>43</v>
+      </c>
+      <c r="I357" t="n">
+        <v>9</v>
+      </c>
+      <c r="J357" t="n">
+        <v>25</v>
+      </c>
+      <c r="K357" t="n">
+        <v>17</v>
+      </c>
+      <c r="L357" t="n">
+        <v>28</v>
+      </c>
+      <c r="M357" t="n">
+        <v>8</v>
+      </c>
+      <c r="N357" t="n">
+        <v>25</v>
+      </c>
+      <c r="O357" t="n">
+        <v>16</v>
+      </c>
+      <c r="P357" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>11</v>
+      </c>
+      <c r="R357" t="n">
+        <v>23</v>
+      </c>
+      <c r="S357" t="n">
+        <v>22</v>
+      </c>
+      <c r="T357" t="n">
+        <v>5</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>2487754</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>79</v>
+      </c>
+      <c r="W357" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="X357" t="n">
+        <v>0.8979413053000439</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>83.31999999999999</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>98.41574651944312</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>0.8631993006993007</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>90.26508226691043</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>0.2162162162162162</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>8.150664252532692</v>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>ADC BOADILLA</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>C.B. TRES CANTOS</t>
+        </is>
+      </c>
+      <c r="AI357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>26</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>200</v>
+      </c>
+      <c r="F358" t="n">
+        <v>77</v>
+      </c>
+      <c r="G358" t="n">
+        <v>17</v>
+      </c>
+      <c r="H358" t="n">
+        <v>38</v>
+      </c>
+      <c r="I358" t="n">
+        <v>6</v>
+      </c>
+      <c r="J358" t="n">
+        <v>27</v>
+      </c>
+      <c r="K358" t="n">
+        <v>25</v>
+      </c>
+      <c r="L358" t="n">
+        <v>36</v>
+      </c>
+      <c r="M358" t="n">
+        <v>18</v>
+      </c>
+      <c r="N358" t="n">
+        <v>34</v>
+      </c>
+      <c r="O358" t="n">
+        <v>10</v>
+      </c>
+      <c r="P358" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>15</v>
+      </c>
+      <c r="R358" t="n">
+        <v>16</v>
+      </c>
+      <c r="S358" t="n">
+        <v>25</v>
+      </c>
+      <c r="T358" t="n">
+        <v>1</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>74</v>
+      </c>
+      <c r="W358" t="n">
+        <v>95.84</v>
+      </c>
+      <c r="X358" t="n">
+        <v>0.8034223706176962</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>77.84</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>98.92086330935251</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>0.780261493040911</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>96.30400832899531</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>2.616854980357203</v>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI358" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>26</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>200</v>
+      </c>
+      <c r="F359" t="n">
+        <v>94</v>
+      </c>
+      <c r="G359" t="n">
+        <v>19</v>
+      </c>
+      <c r="H359" t="n">
+        <v>37</v>
+      </c>
+      <c r="I359" t="n">
+        <v>12</v>
+      </c>
+      <c r="J359" t="n">
+        <v>32</v>
+      </c>
+      <c r="K359" t="n">
+        <v>20</v>
+      </c>
+      <c r="L359" t="n">
+        <v>24</v>
+      </c>
+      <c r="M359" t="n">
+        <v>13</v>
+      </c>
+      <c r="N359" t="n">
+        <v>22</v>
+      </c>
+      <c r="O359" t="n">
+        <v>13</v>
+      </c>
+      <c r="P359" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>12</v>
+      </c>
+      <c r="R359" t="n">
+        <v>32</v>
+      </c>
+      <c r="S359" t="n">
+        <v>19</v>
+      </c>
+      <c r="T359" t="n">
+        <v>0</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>2487752</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>86</v>
+      </c>
+      <c r="W359" t="n">
+        <v>91.56</v>
+      </c>
+      <c r="X359" t="n">
+        <v>1.026649191786806</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>78.56</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>119.6537678207739</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>0.852836176120587</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>99.03270382312299</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>0.4794520547945205</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>20.62106399765094</v>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>EB FELIPE ANTÓN</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>BALONCESTO TALAVERA</t>
+        </is>
+      </c>
+      <c r="AI359" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>26</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>200</v>
+      </c>
+      <c r="F360" t="n">
+        <v>75</v>
+      </c>
+      <c r="G360" t="n">
+        <v>18</v>
+      </c>
+      <c r="H360" t="n">
+        <v>40</v>
+      </c>
+      <c r="I360" t="n">
+        <v>7</v>
+      </c>
+      <c r="J360" t="n">
+        <v>21</v>
+      </c>
+      <c r="K360" t="n">
+        <v>18</v>
+      </c>
+      <c r="L360" t="n">
+        <v>24</v>
+      </c>
+      <c r="M360" t="n">
+        <v>7</v>
+      </c>
+      <c r="N360" t="n">
+        <v>23</v>
+      </c>
+      <c r="O360" t="n">
+        <v>17</v>
+      </c>
+      <c r="P360" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>17</v>
+      </c>
+      <c r="R360" t="n">
+        <v>23</v>
+      </c>
+      <c r="S360" t="n">
+        <v>20</v>
+      </c>
+      <c r="T360" t="n">
+        <v>3</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>76</v>
+      </c>
+      <c r="W360" t="n">
+        <v>88.56</v>
+      </c>
+      <c r="X360" t="n">
+        <v>0.8468834688346883</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>81.56</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>91.95684158901422</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>0.7923269391159299</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>91.65460684997588</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>0.6388888888888888</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>0.4054054054054054</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>0.3022347390383402</v>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI360" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>26</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>200</v>
+      </c>
+      <c r="F361" t="n">
+        <v>81</v>
+      </c>
+      <c r="G361" t="n">
+        <v>24</v>
+      </c>
+      <c r="H361" t="n">
+        <v>46</v>
+      </c>
+      <c r="I361" t="n">
+        <v>8</v>
+      </c>
+      <c r="J361" t="n">
+        <v>21</v>
+      </c>
+      <c r="K361" t="n">
+        <v>9</v>
+      </c>
+      <c r="L361" t="n">
+        <v>17</v>
+      </c>
+      <c r="M361" t="n">
+        <v>8</v>
+      </c>
+      <c r="N361" t="n">
+        <v>34</v>
+      </c>
+      <c r="O361" t="n">
+        <v>15</v>
+      </c>
+      <c r="P361" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>13</v>
+      </c>
+      <c r="R361" t="n">
+        <v>20</v>
+      </c>
+      <c r="S361" t="n">
+        <v>17</v>
+      </c>
+      <c r="T361" t="n">
+        <v>3</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>2487757</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>71</v>
+      </c>
+      <c r="W361" t="n">
+        <v>87.48</v>
+      </c>
+      <c r="X361" t="n">
+        <v>0.9259259259259259</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>79.48</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>101.9124308002013</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>0.8251975825197583</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>90.97898513582778</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>0.5526315789473685</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>10.93344566437352</v>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>LUJISA GUADALAJARA BASKET</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>AUTOCARES RODRÍGUEZ</t>
+        </is>
+      </c>
+      <c r="AI361" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>26</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>200</v>
+      </c>
+      <c r="F362" t="n">
+        <v>76</v>
+      </c>
+      <c r="G362" t="n">
+        <v>19</v>
+      </c>
+      <c r="H362" t="n">
+        <v>37</v>
+      </c>
+      <c r="I362" t="n">
+        <v>9</v>
+      </c>
+      <c r="J362" t="n">
+        <v>33</v>
+      </c>
+      <c r="K362" t="n">
+        <v>11</v>
+      </c>
+      <c r="L362" t="n">
+        <v>18</v>
+      </c>
+      <c r="M362" t="n">
+        <v>13</v>
+      </c>
+      <c r="N362" t="n">
+        <v>31</v>
+      </c>
+      <c r="O362" t="n">
+        <v>17</v>
+      </c>
+      <c r="P362" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>18</v>
+      </c>
+      <c r="R362" t="n">
+        <v>21</v>
+      </c>
+      <c r="S362" t="n">
+        <v>22</v>
+      </c>
+      <c r="T362" t="n">
+        <v>2</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>2487756</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>75</v>
+      </c>
+      <c r="W362" t="n">
+        <v>95.92</v>
+      </c>
+      <c r="X362" t="n">
+        <v>0.7923269391159299</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>91.65460684997588</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>0.8468834688346883</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>91.95684158901422</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>0.3611111111111111</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>0.5945945945945946</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>-0.3022347390383402</v>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>REAL CANOE N.C.</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>GRUPO EGIDO PINTOBASKET</t>
+        </is>
+      </c>
+      <c r="AI362" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>26</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>200</v>
+      </c>
+      <c r="F363" t="n">
+        <v>47</v>
+      </c>
+      <c r="G363" t="n">
+        <v>15</v>
+      </c>
+      <c r="H363" t="n">
+        <v>36</v>
+      </c>
+      <c r="I363" t="n">
+        <v>3</v>
+      </c>
+      <c r="J363" t="n">
+        <v>21</v>
+      </c>
+      <c r="K363" t="n">
+        <v>8</v>
+      </c>
+      <c r="L363" t="n">
+        <v>15</v>
+      </c>
+      <c r="M363" t="n">
+        <v>11</v>
+      </c>
+      <c r="N363" t="n">
+        <v>29</v>
+      </c>
+      <c r="O363" t="n">
+        <v>7</v>
+      </c>
+      <c r="P363" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>17</v>
+      </c>
+      <c r="R363" t="n">
+        <v>15</v>
+      </c>
+      <c r="S363" t="n">
+        <v>18</v>
+      </c>
+      <c r="T363" t="n">
+        <v>0</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2487755</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>65</v>
+      </c>
+      <c r="W363" t="n">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="X363" t="n">
+        <v>0.5831265508684864</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>67.52873563218391</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>0.8153537380832915</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>93.23006310958118</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>0.5194805194805194</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>-25.70132747739727</v>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>RECUCYM BAZU</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>C. D. MENSAJERO ISLA DE LA PALMA</t>
+        </is>
+      </c>
+      <c r="AI363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>26</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>200</v>
+      </c>
+      <c r="F364" t="n">
+        <v>74</v>
+      </c>
+      <c r="G364" t="n">
+        <v>20</v>
+      </c>
+      <c r="H364" t="n">
+        <v>45</v>
+      </c>
+      <c r="I364" t="n">
+        <v>9</v>
+      </c>
+      <c r="J364" t="n">
+        <v>42</v>
+      </c>
+      <c r="K364" t="n">
+        <v>7</v>
+      </c>
+      <c r="L364" t="n">
+        <v>11</v>
+      </c>
+      <c r="M364" t="n">
+        <v>18</v>
+      </c>
+      <c r="N364" t="n">
+        <v>24</v>
+      </c>
+      <c r="O364" t="n">
+        <v>17</v>
+      </c>
+      <c r="P364" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>3</v>
+      </c>
+      <c r="R364" t="n">
+        <v>25</v>
+      </c>
+      <c r="S364" t="n">
+        <v>16</v>
+      </c>
+      <c r="T364" t="n">
+        <v>2</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>2487758</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>77</v>
+      </c>
+      <c r="W364" t="n">
+        <v>94.84</v>
+      </c>
+      <c r="X364" t="n">
+        <v>0.780261493040911</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>96.30400832899531</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>0.8034223706176962</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>98.92086330935251</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>-2.616854980357203</v>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>CB ARIDANE</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>UROS DE RIVAS</t>
+        </is>
+      </c>
+      <c r="AI364" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Liga Regular "B-B"</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>26</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>200</v>
+      </c>
+      <c r="F365" t="n">
+        <v>102</v>
+      </c>
+      <c r="G365" t="n">
+        <v>23</v>
+      </c>
+      <c r="H365" t="n">
+        <v>38</v>
+      </c>
+      <c r="I365" t="n">
+        <v>11</v>
+      </c>
+      <c r="J365" t="n">
+        <v>30</v>
+      </c>
+      <c r="K365" t="n">
+        <v>23</v>
+      </c>
+      <c r="L365" t="n">
+        <v>29</v>
+      </c>
+      <c r="M365" t="n">
+        <v>14</v>
+      </c>
+      <c r="N365" t="n">
+        <v>27</v>
+      </c>
+      <c r="O365" t="n">
+        <v>18</v>
+      </c>
+      <c r="P365" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>17</v>
+      </c>
+      <c r="R365" t="n">
+        <v>26</v>
+      </c>
+      <c r="S365" t="n">
+        <v>28</v>
+      </c>
+      <c r="T365" t="n">
+        <v>0</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>2487753</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>82</v>
+      </c>
+      <c r="W365" t="n">
+        <v>97.75999999999999</v>
+      </c>
+      <c r="X365" t="n">
+        <v>1.043371522094926</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>83.75999999999999</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>121.7765042979943</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>0.8693808312128923</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>91.80474697716078</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>0.84375</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>0.6029411764705882</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>29.9717573208335</v>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>ZENTRO BASKET MADRID</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>BALONCESTO TELDE</t>
+        </is>
+      </c>
+      <c r="AI365" t="b">
         <v>1</v>
       </c>
     </row>
